--- a/artfynd/A 60372-2024 artfynd.xlsx
+++ b/artfynd/A 60372-2024 artfynd.xlsx
@@ -8376,10 +8376,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122696014</v>
+        <v>122696471</v>
       </c>
       <c r="B59" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8392,37 +8392,47 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>479718</v>
+        <v>479681</v>
       </c>
       <c r="R59" t="n">
-        <v>7027277</v>
+        <v>7027123</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8454,6 +8464,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på stambasen.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -8480,12 +8495,12 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8503,7 +8518,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122698275</v>
+        <v>122696014</v>
       </c>
       <c r="B60" t="n">
         <v>78762</v>
@@ -8543,10 +8558,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>479734</v>
+        <v>479718</v>
       </c>
       <c r="R60" t="n">
-        <v>7027357</v>
+        <v>7027277</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8579,11 +8594,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8635,7 +8645,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122695752</v>
+        <v>122698275</v>
       </c>
       <c r="B61" t="n">
         <v>78762</v>
@@ -8675,13 +8685,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>479748</v>
+        <v>479734</v>
       </c>
       <c r="R61" t="n">
-        <v>7027283</v>
+        <v>7027357</v>
       </c>
       <c r="S61" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8711,6 +8721,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8762,10 +8777,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122696471</v>
+        <v>122695752</v>
       </c>
       <c r="B62" t="n">
-        <v>57478</v>
+        <v>78762</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8778,47 +8793,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>479681</v>
+        <v>479748</v>
       </c>
       <c r="R62" t="n">
-        <v>7027123</v>
+        <v>7027283</v>
       </c>
       <c r="S62" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8850,11 +8855,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på stambasen.</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -8881,12 +8881,12 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>

--- a/artfynd/A 60372-2024 artfynd.xlsx
+++ b/artfynd/A 60372-2024 artfynd.xlsx
@@ -5790,10 +5790,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122608090</v>
+        <v>122607746</v>
       </c>
       <c r="B40" t="n">
-        <v>79747</v>
+        <v>79751</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5824,19 +5824,26 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>479602</v>
+        <v>479627</v>
       </c>
       <c r="R40" t="n">
-        <v>7027640</v>
+        <v>7027656</v>
       </c>
       <c r="S40" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5868,18 +5875,29 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Skinnlav på asp där flertalet bålar är fertila med apothecier.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Flerskiktad kontinuitetsskog dominerad av gran och med återkommande inslag av asp.</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
@@ -5917,10 +5935,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122608974</v>
+        <v>122609140</v>
       </c>
       <c r="B41" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5953,7 +5971,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5962,13 +5980,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>479682</v>
+        <v>479723</v>
       </c>
       <c r="R41" t="n">
-        <v>7027484</v>
+        <v>7027396</v>
       </c>
       <c r="S41" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -6000,6 +6018,11 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ymnig påväxt av lunglav längs flera meter på en gammal sälg. Fertila bålar med apothecier.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -6016,12 +6039,12 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
@@ -6031,7 +6054,7 @@
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6049,10 +6072,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122613271</v>
+        <v>122607410</v>
       </c>
       <c r="B42" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6065,44 +6088,47 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>479628</v>
+        <v>479644</v>
       </c>
       <c r="R42" t="n">
-        <v>7027338</v>
+        <v>7027599</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6136,7 +6162,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Riklig påväxt av lunglavsbålar på en gammal sälg. Vissa bålar är fertila med apothecier. Här växer även rikligt med lunglav på gran.</t>
+          <t>Både äldre och färska ringhack på stambasen. I skogsbeståndet runt fyndplatsen finns medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6145,7 +6171,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -6154,34 +6179,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
-        </is>
-      </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL42" t="inlineStr">
-        <is>
-          <t>En gammal grov sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea # En gammal grov sälg.</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6199,10 +6214,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122609140</v>
+        <v>122613278</v>
       </c>
       <c r="B43" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6233,24 +6248,26 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>479723</v>
+        <v>479628</v>
       </c>
       <c r="R43" t="n">
-        <v>7027396</v>
+        <v>7027338</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6284,7 +6301,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ymnig påväxt av lunglav längs flera meter på en gammal sälg. Fertila bålar med apothecier.</t>
+          <t>Rikligt med lunglavsbålar på gran intill en gammal sälg med lunglav.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6293,6 +6310,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -6301,24 +6319,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+        </is>
+      </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6336,10 +6359,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122613280</v>
+        <v>122608090</v>
       </c>
       <c r="B44" t="n">
-        <v>79844</v>
+        <v>79751</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6348,48 +6371,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>479628</v>
+        <v>479602</v>
       </c>
       <c r="R44" t="n">
-        <v>7027338</v>
+        <v>7027640</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6421,18 +6437,12 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På renar av gran blandat med lunglav.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6441,29 +6451,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
-        </is>
-      </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6481,10 +6486,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122607410</v>
+        <v>122613281</v>
       </c>
       <c r="B45" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6497,47 +6502,40 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>479644</v>
+        <v>479628</v>
       </c>
       <c r="R45" t="n">
-        <v>7027599</v>
+        <v>7027338</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6571,7 +6569,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Både äldre och färska ringhack på stambasen. I skogsbeståndet runt fyndplatsen finns medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Med långväxta bålar och på flera granar.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6580,6 +6578,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6588,6 +6587,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+        </is>
+      </c>
       <c r="AJ45" t="inlineStr">
         <is>
           <t>gran</t>
@@ -6600,12 +6604,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6626,7 +6630,7 @@
         <v>122613145</v>
       </c>
       <c r="B46" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6773,10 +6777,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122613281</v>
+        <v>122608974</v>
       </c>
       <c r="B47" t="n">
-        <v>78762</v>
+        <v>79847</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6789,40 +6793,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>479628</v>
+        <v>479682</v>
       </c>
       <c r="R47" t="n">
-        <v>7027338</v>
+        <v>7027484</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6854,18 +6860,12 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Med långväxta bålar och på flera granar.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6874,29 +6874,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
-        </is>
-      </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6914,10 +6909,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122607746</v>
+        <v>122609714</v>
       </c>
       <c r="B48" t="n">
-        <v>79747</v>
+        <v>57631</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6926,32 +6921,37 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6456</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -6961,10 +6961,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>479627</v>
+        <v>479677</v>
       </c>
       <c r="R48" t="n">
-        <v>7027656</v>
+        <v>7027303</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -7001,7 +7001,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Skinnlav på asp där flertalet bålar är fertila med apothecier.</t>
+          <t>Observation i flerskiktad granskog med stående murkna björkhögstubbar som är gynnsamt för talltitans häckning.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7010,7 +7010,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -7021,27 +7020,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Flerskiktad kontinuitetsskog dominerad av gran och med återkommande inslag av asp.</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -7059,10 +7038,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122609714</v>
+        <v>122613280</v>
       </c>
       <c r="B49" t="n">
-        <v>57631</v>
+        <v>79848</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -7075,49 +7054,44 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>479677</v>
+        <v>479628</v>
       </c>
       <c r="R49" t="n">
-        <v>7027303</v>
+        <v>7027338</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -7151,7 +7125,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Observation i flerskiktad granskog med stående murkna björkhögstubbar som är gynnsamt för talltitans häckning.</t>
+          <t>På renar av gran blandat med lunglav.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7160,6 +7134,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -7171,6 +7146,26 @@
       <c r="AI49" t="inlineStr">
         <is>
           <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7191,7 +7186,7 @@
         <v>122609073</v>
       </c>
       <c r="B50" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7325,10 +7320,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122695322</v>
+        <v>122697534</v>
       </c>
       <c r="B51" t="n">
-        <v>79843</v>
+        <v>78766</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7341,39 +7336,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>479771</v>
+        <v>479644</v>
       </c>
       <c r="R51" t="n">
-        <v>7027387</v>
+        <v>7027243</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7408,11 +7398,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På en lutande krokig sälg.</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -7424,27 +7409,27 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7462,10 +7447,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122696876</v>
+        <v>122695492</v>
       </c>
       <c r="B52" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7478,32 +7463,27 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -7512,13 +7492,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>479628</v>
+        <v>479770</v>
       </c>
       <c r="R52" t="n">
-        <v>7027133</v>
+        <v>7027300</v>
       </c>
       <c r="S52" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7552,7 +7532,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen av en gran. I äldre granskog med minst medelhöga till höga livsmiljövärden för tretåig hackspett. Även gott om liggande död ved här. Finns även skalade döda granar här som indikerar potentiella födosökspår efter tretåig hackspett.</t>
+          <t>Växer på en lite smalare sälg intill lunglav.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7571,22 +7551,22 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7604,10 +7584,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122697352</v>
+        <v>122695011</v>
       </c>
       <c r="B53" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7644,10 +7624,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>479674</v>
+        <v>479729</v>
       </c>
       <c r="R53" t="n">
-        <v>7027178</v>
+        <v>7027486</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7680,6 +7660,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7731,10 +7716,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122697690</v>
+        <v>122698247</v>
       </c>
       <c r="B54" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7771,10 +7756,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>479640</v>
+        <v>479696</v>
       </c>
       <c r="R54" t="n">
-        <v>7027281</v>
+        <v>7027370</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7858,10 +7843,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122695075</v>
+        <v>122695322</v>
       </c>
       <c r="B55" t="n">
-        <v>78762</v>
+        <v>79847</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7874,34 +7859,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>479699</v>
+        <v>479771</v>
       </c>
       <c r="R55" t="n">
-        <v>7027521</v>
+        <v>7027387</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7938,7 +7928,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På en lutande krokig sälg.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7957,22 +7947,22 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7990,10 +7980,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122695669</v>
+        <v>122696876</v>
       </c>
       <c r="B56" t="n">
-        <v>79844</v>
+        <v>57478</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -8006,37 +7996,47 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>479761</v>
+        <v>479628</v>
       </c>
       <c r="R56" t="n">
-        <v>7027298</v>
+        <v>7027133</v>
       </c>
       <c r="S56" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -8068,6 +8068,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på stambasen av en gran. I äldre granskog med minst medelhöga till höga livsmiljövärden för tretåig hackspett. Även gott om liggande död ved här. Finns även skalade döda granar här som indikerar potentiella födosökspår efter tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -8094,12 +8099,12 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -8117,10 +8122,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122695011</v>
+        <v>122697882</v>
       </c>
       <c r="B57" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -8157,13 +8162,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>479729</v>
+        <v>479664</v>
       </c>
       <c r="R57" t="n">
-        <v>7027486</v>
+        <v>7027326</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -8249,10 +8254,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122696303</v>
+        <v>122697862</v>
       </c>
       <c r="B58" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8289,13 +8294,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>479685</v>
+        <v>479630</v>
       </c>
       <c r="R58" t="n">
-        <v>7027165</v>
+        <v>7027362</v>
       </c>
       <c r="S58" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8376,10 +8381,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122696471</v>
+        <v>122695655</v>
       </c>
       <c r="B59" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8392,32 +8397,27 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -8426,13 +8426,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>479681</v>
+        <v>479759</v>
       </c>
       <c r="R59" t="n">
-        <v>7027123</v>
+        <v>7027292</v>
       </c>
       <c r="S59" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen.</t>
+          <t>Växer på två granar intill en sälg med ymnig påväxt av lunglav.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8495,12 +8495,12 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8518,10 +8518,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122696014</v>
+        <v>122698232</v>
       </c>
       <c r="B60" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8558,10 +8558,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>479718</v>
+        <v>479698</v>
       </c>
       <c r="R60" t="n">
-        <v>7027277</v>
+        <v>7027368</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8645,10 +8645,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122698275</v>
+        <v>122695703</v>
       </c>
       <c r="B61" t="n">
-        <v>78762</v>
+        <v>79847</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8661,37 +8661,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>479734</v>
+        <v>479753</v>
       </c>
       <c r="R61" t="n">
-        <v>7027357</v>
+        <v>7027296</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8725,7 +8730,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Rikligt med lunglav på två knäckta sälgar.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8744,22 +8749,22 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8777,10 +8782,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122695752</v>
+        <v>122696290</v>
       </c>
       <c r="B62" t="n">
-        <v>78762</v>
+        <v>57631</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8793,37 +8798,51 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>479748</v>
+        <v>479695</v>
       </c>
       <c r="R62" t="n">
-        <v>7027283</v>
+        <v>7027185</v>
       </c>
       <c r="S62" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8855,6 +8874,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Observerad i flerskiktad äldre granskog.</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -8867,26 +8891,6 @@
       <c r="AH62" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8904,10 +8908,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122695101</v>
+        <v>122696426</v>
       </c>
       <c r="B63" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8920,37 +8924,47 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>479696</v>
+        <v>479685</v>
       </c>
       <c r="R63" t="n">
-        <v>7027544</v>
+        <v>7027127</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8984,7 +8998,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Färska och äldre ringhack/savhack.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -9013,12 +9027,12 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -9036,10 +9050,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122695682</v>
+        <v>122696303</v>
       </c>
       <c r="B64" t="n">
-        <v>79843</v>
+        <v>78766</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -9052,42 +9066,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>479763</v>
+        <v>479685</v>
       </c>
       <c r="R64" t="n">
-        <v>7027300</v>
+        <v>7027165</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -9119,11 +9128,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>På en smal krokig sälg.</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -9140,22 +9144,22 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -9173,10 +9177,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122697286</v>
+        <v>122697690</v>
       </c>
       <c r="B65" t="n">
-        <v>79843</v>
+        <v>78766</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9189,39 +9193,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>479663</v>
+        <v>479640</v>
       </c>
       <c r="R65" t="n">
-        <v>7027246</v>
+        <v>7027281</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -9272,22 +9271,22 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9305,10 +9304,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122695926</v>
+        <v>122695075</v>
       </c>
       <c r="B66" t="n">
-        <v>79843</v>
+        <v>78766</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9321,39 +9320,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>479752</v>
+        <v>479699</v>
       </c>
       <c r="R66" t="n">
-        <v>7027344</v>
+        <v>7027521</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9390,7 +9384,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ymnigt med lunglav på en gammal sälg.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9409,22 +9403,22 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9442,10 +9436,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122697773</v>
+        <v>122695669</v>
       </c>
       <c r="B67" t="n">
-        <v>79843</v>
+        <v>79848</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9458,21 +9452,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -9482,13 +9476,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>479617</v>
+        <v>479761</v>
       </c>
       <c r="R67" t="n">
-        <v>7027326</v>
+        <v>7027298</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -9520,11 +9514,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -9541,22 +9530,22 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9574,10 +9563,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122695943</v>
+        <v>122695926</v>
       </c>
       <c r="B68" t="n">
-        <v>78762</v>
+        <v>79847</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9590,34 +9579,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>479756</v>
+        <v>479752</v>
       </c>
       <c r="R68" t="n">
-        <v>7027364</v>
+        <v>7027344</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9652,6 +9646,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ymnigt med lunglav på en gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -9668,22 +9667,22 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9701,10 +9700,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122695492</v>
+        <v>122696537</v>
       </c>
       <c r="B69" t="n">
-        <v>79844</v>
+        <v>57478</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9717,27 +9716,32 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -9746,13 +9750,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>479770</v>
+        <v>479669</v>
       </c>
       <c r="R69" t="n">
-        <v>7027300</v>
+        <v>7027116</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9786,7 +9790,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Växer på en lite smalare sälg intill lunglav.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9805,22 +9809,22 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9838,10 +9842,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122695516</v>
+        <v>122695682</v>
       </c>
       <c r="B70" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9883,10 +9887,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>479766</v>
+        <v>479763</v>
       </c>
       <c r="R70" t="n">
-        <v>7027310</v>
+        <v>7027300</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9923,7 +9927,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Växer på en lite smalare sälg intill skrovellav.</t>
+          <t>På en smal krokig sälg.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9975,10 +9979,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122697882</v>
+        <v>122695752</v>
       </c>
       <c r="B71" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -10015,13 +10019,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>479664</v>
+        <v>479748</v>
       </c>
       <c r="R71" t="n">
-        <v>7027326</v>
+        <v>7027283</v>
       </c>
       <c r="S71" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -10051,11 +10055,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -10107,10 +10106,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122696290</v>
+        <v>122696111</v>
       </c>
       <c r="B72" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -10123,48 +10122,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>479695</v>
+        <v>479694</v>
       </c>
       <c r="R72" t="n">
-        <v>7027185</v>
+        <v>7027236</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -10199,11 +10184,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Observerad i flerskiktad äldre granskog.</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -10216,6 +10196,26 @@
       <c r="AH72" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM72" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -10233,10 +10233,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122695655</v>
+        <v>122697966</v>
       </c>
       <c r="B73" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -10278,13 +10278,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>479759</v>
+        <v>479660</v>
       </c>
       <c r="R73" t="n">
-        <v>7027292</v>
+        <v>7027363</v>
       </c>
       <c r="S73" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -10316,11 +10316,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Växer på två granar intill en sälg med ymnig påväxt av lunglav.</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -10337,22 +10332,22 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -10370,10 +10365,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122696111</v>
+        <v>122697286</v>
       </c>
       <c r="B74" t="n">
-        <v>78762</v>
+        <v>79847</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10386,34 +10381,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>479694</v>
+        <v>479663</v>
       </c>
       <c r="R74" t="n">
-        <v>7027236</v>
+        <v>7027246</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10464,22 +10464,22 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10497,10 +10497,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122697534</v>
+        <v>122695516</v>
       </c>
       <c r="B75" t="n">
-        <v>78762</v>
+        <v>79847</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10513,34 +10513,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>479644</v>
+        <v>479766</v>
       </c>
       <c r="R75" t="n">
-        <v>7027243</v>
+        <v>7027310</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10575,6 +10580,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Växer på en lite smalare sälg intill skrovellav.</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -10586,27 +10596,27 @@
       </c>
       <c r="AH75" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -10624,10 +10634,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122697862</v>
+        <v>122697773</v>
       </c>
       <c r="B76" t="n">
-        <v>78762</v>
+        <v>79847</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10640,21 +10650,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -10664,10 +10674,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>479630</v>
+        <v>479617</v>
       </c>
       <c r="R76" t="n">
-        <v>7027362</v>
+        <v>7027326</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10702,6 +10712,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Enstaka bålar.</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -10718,22 +10733,22 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -10751,10 +10766,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122698247</v>
+        <v>122695354</v>
       </c>
       <c r="B77" t="n">
-        <v>78762</v>
+        <v>79848</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10767,21 +10782,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -10791,10 +10806,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>479696</v>
+        <v>479765</v>
       </c>
       <c r="R77" t="n">
-        <v>7027370</v>
+        <v>7027389</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10829,6 +10844,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>På en lutande krokig sälg.</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -10845,22 +10865,22 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10878,10 +10898,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122697757</v>
+        <v>122696014</v>
       </c>
       <c r="B78" t="n">
-        <v>79844</v>
+        <v>78766</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10894,39 +10914,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>479615</v>
+        <v>479718</v>
       </c>
       <c r="R78" t="n">
-        <v>7027315</v>
+        <v>7027277</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10977,22 +10992,22 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -11010,10 +11025,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122696537</v>
+        <v>122697455</v>
       </c>
       <c r="B79" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -11026,16 +11041,16 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -11043,10 +11058,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -11060,13 +11079,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>479669</v>
+        <v>479680</v>
       </c>
       <c r="R79" t="n">
-        <v>7027116</v>
+        <v>7027206</v>
       </c>
       <c r="S79" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -11100,7 +11119,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Observation av en spillkråka som gav ifrån sig två olika lockläten. I gammal granskog med gott om asp och tall som utgör lämpliga substrat för bohål. Även bitvis relativt gott om död ved här.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -11115,26 +11134,6 @@
       <c r="AH79" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -11152,10 +11151,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122698232</v>
+        <v>122695273</v>
       </c>
       <c r="B80" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -11168,34 +11167,44 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>479698</v>
+        <v>479770</v>
       </c>
       <c r="R80" t="n">
-        <v>7027368</v>
+        <v>7027401</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -11230,6 +11239,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -11256,12 +11270,12 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -11279,10 +11293,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122696521</v>
+        <v>122697757</v>
       </c>
       <c r="B81" t="n">
-        <v>57494</v>
+        <v>79848</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -11295,32 +11309,27 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -11329,13 +11338,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>479674</v>
+        <v>479615</v>
       </c>
       <c r="R81" t="n">
-        <v>7027109</v>
+        <v>7027315</v>
       </c>
       <c r="S81" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -11367,11 +11376,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Färska hackspår i stambasen av en smal gran i granskog med stora mängder liggande död ved.</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -11388,22 +11392,22 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -11421,10 +11425,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122697455</v>
+        <v>122698275</v>
       </c>
       <c r="B82" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -11437,51 +11441,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>479680</v>
+        <v>479734</v>
       </c>
       <c r="R82" t="n">
-        <v>7027206</v>
+        <v>7027357</v>
       </c>
       <c r="S82" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -11515,7 +11505,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Observation av en spillkråka som gav ifrån sig två olika lockläten. I gammal granskog med gott om asp och tall som utgör lämpliga substrat för bohål. Även bitvis relativt gott om död ved här.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11530,6 +11520,26 @@
       <c r="AH82" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -11547,10 +11557,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122695354</v>
+        <v>122695602</v>
       </c>
       <c r="B83" t="n">
-        <v>79844</v>
+        <v>79847</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -11563,34 +11573,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>479765</v>
+        <v>479774</v>
       </c>
       <c r="R83" t="n">
-        <v>7027389</v>
+        <v>7027322</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11627,7 +11642,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>På en lutande krokig sälg.</t>
+          <t>Ymnigt med lunglav på en gammal sälg med fårad bark.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11679,10 +11694,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122698085</v>
+        <v>122695101</v>
       </c>
       <c r="B84" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11719,10 +11734,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>479659</v>
+        <v>479696</v>
       </c>
       <c r="R84" t="n">
-        <v>7027303</v>
+        <v>7027544</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11755,6 +11770,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11809,7 +11829,7 @@
         <v>122697666</v>
       </c>
       <c r="B85" t="n">
-        <v>90958</v>
+        <v>90962</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11947,10 +11967,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122695703</v>
+        <v>122695943</v>
       </c>
       <c r="B86" t="n">
-        <v>79843</v>
+        <v>78766</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11963,42 +11983,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>479753</v>
+        <v>479756</v>
       </c>
       <c r="R86" t="n">
-        <v>7027296</v>
+        <v>7027364</v>
       </c>
       <c r="S86" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -12030,11 +12045,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglav på två knäckta sälgar.</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -12051,22 +12061,22 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -12084,10 +12094,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122696426</v>
+        <v>122696057</v>
       </c>
       <c r="B87" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -12100,32 +12110,27 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -12134,13 +12139,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>479685</v>
+        <v>479675</v>
       </c>
       <c r="R87" t="n">
-        <v>7027127</v>
+        <v>7027261</v>
       </c>
       <c r="S87" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -12174,7 +12179,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack/savhack.</t>
+          <t>På flera aspar.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -12193,22 +12198,22 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -12226,10 +12231,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122695602</v>
+        <v>122696471</v>
       </c>
       <c r="B88" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -12242,27 +12247,32 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -12271,13 +12281,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>479774</v>
+        <v>479681</v>
       </c>
       <c r="R88" t="n">
-        <v>7027322</v>
+        <v>7027123</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -12311,7 +12321,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Ymnigt med lunglav på en gammal sälg med fårad bark.</t>
+          <t>Äldre ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -12330,22 +12340,22 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -12363,10 +12373,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122696057</v>
+        <v>122696521</v>
       </c>
       <c r="B89" t="n">
-        <v>79843</v>
+        <v>57494</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -12379,27 +12389,32 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -12408,13 +12423,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>479675</v>
+        <v>479674</v>
       </c>
       <c r="R89" t="n">
-        <v>7027261</v>
+        <v>7027109</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -12448,7 +12463,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>På flera aspar.</t>
+          <t>Färska hackspår i stambasen av en smal gran i granskog med stora mängder liggande död ved.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -12467,22 +12482,22 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -12500,10 +12515,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122697966</v>
+        <v>122697352</v>
       </c>
       <c r="B90" t="n">
-        <v>79843</v>
+        <v>78766</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -12516,39 +12531,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>479660</v>
+        <v>479674</v>
       </c>
       <c r="R90" t="n">
-        <v>7027363</v>
+        <v>7027178</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -12599,22 +12609,22 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -12632,10 +12642,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122695273</v>
+        <v>122698085</v>
       </c>
       <c r="B91" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -12648,44 +12658,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>479770</v>
+        <v>479659</v>
       </c>
       <c r="R91" t="n">
-        <v>7027401</v>
+        <v>7027303</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12720,11 +12720,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
@@ -12751,12 +12746,12 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>

--- a/artfynd/A 60372-2024 artfynd.xlsx
+++ b/artfynd/A 60372-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122606026</v>
+        <v>122606649</v>
       </c>
       <c r="B2" t="n">
-        <v>90958</v>
+        <v>79883</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>479756</v>
+        <v>479715</v>
       </c>
       <c r="R2" t="n">
-        <v>7027477</v>
+        <v>7027462</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,6 +758,11 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>En samling bålar på ca 2 meters höjd på aspens stam.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -774,22 +779,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -807,10 +812,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122607879</v>
+        <v>122607162</v>
       </c>
       <c r="B3" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -847,13 +852,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479622</v>
+        <v>479650</v>
       </c>
       <c r="R3" t="n">
-        <v>7027648</v>
+        <v>7027549</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -939,10 +944,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122609496</v>
+        <v>122606273</v>
       </c>
       <c r="B4" t="n">
-        <v>79843</v>
+        <v>79848</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -955,21 +960,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -984,10 +989,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479735</v>
+        <v>479698</v>
       </c>
       <c r="R4" t="n">
-        <v>7027318</v>
+        <v>7027398</v>
       </c>
       <c r="S4" t="n">
         <v>7</v>
@@ -1022,6 +1027,11 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Skrovellav på en undertryck gran intill en gammal grov sälg.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1033,7 +1043,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1071,10 +1081,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122606431</v>
+        <v>122607246</v>
       </c>
       <c r="B5" t="n">
-        <v>78762</v>
+        <v>57631</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1087,34 +1097,48 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>479711</v>
+        <v>479659</v>
       </c>
       <c r="R5" t="n">
-        <v>7027387</v>
+        <v>7027556</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1151,7 +1175,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Observerades i flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1165,27 +1189,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1203,10 +1207,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122607620</v>
+        <v>122607124</v>
       </c>
       <c r="B6" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1219,34 +1223,44 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>479635</v>
+        <v>479654</v>
       </c>
       <c r="R6" t="n">
-        <v>7027621</v>
+        <v>7027561</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1283,7 +1297,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Både äldre och färska ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1312,12 +1326,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1338,7 +1352,7 @@
         <v>122607263</v>
       </c>
       <c r="B7" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1462,10 +1476,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122612982</v>
+        <v>122608509</v>
       </c>
       <c r="B8" t="n">
-        <v>79843</v>
+        <v>79751</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1474,45 +1488,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>479738</v>
+        <v>479617</v>
       </c>
       <c r="R8" t="n">
-        <v>7027319</v>
+        <v>7027598</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1547,18 +1554,12 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Grova gamla lunglavsbålar på en lutande sälg.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1567,24 +1568,14 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
-        </is>
-      </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>En smal lutande sälg.</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -1594,7 +1585,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En smal lutande sälg.</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1612,10 +1603,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122606649</v>
+        <v>122609837</v>
       </c>
       <c r="B9" t="n">
-        <v>79879</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1624,43 +1615,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>479715</v>
+        <v>479643</v>
       </c>
       <c r="R9" t="n">
-        <v>7027462</v>
+        <v>7027326</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1697,7 +1683,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>En samling bålar på ca 2 meters höjd på aspens stam.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1716,22 +1702,22 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1749,10 +1735,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122608509</v>
+        <v>122613032</v>
       </c>
       <c r="B10" t="n">
-        <v>79747</v>
+        <v>79847</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1761,41 +1747,48 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>479617</v>
+        <v>479731</v>
       </c>
       <c r="R10" t="n">
-        <v>7027598</v>
+        <v>7027291</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1827,12 +1820,18 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>En hel del bålar på en skadad sälg.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1841,14 +1840,19 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+        </is>
+      </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -1858,7 +1862,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1876,10 +1880,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122606169</v>
+        <v>122609252</v>
       </c>
       <c r="B11" t="n">
-        <v>79843</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1892,42 +1896,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>479698</v>
+        <v>479714</v>
       </c>
       <c r="R11" t="n">
-        <v>7027398</v>
+        <v>7027356</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1959,11 +1958,6 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglav där vissa bålar är fertila med apothecier. På en gammal grovbarkad sälg med 54 cm i brösthöjdsdiameter.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1975,27 +1969,27 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2013,10 +2007,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122605930</v>
+        <v>122609496</v>
       </c>
       <c r="B12" t="n">
-        <v>78762</v>
+        <v>79847</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2029,37 +2023,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>479743</v>
+        <v>479735</v>
       </c>
       <c r="R12" t="n">
-        <v>7027472</v>
+        <v>7027318</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2089,11 +2088,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flera träd.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2145,10 +2139,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122609281</v>
+        <v>122607620</v>
       </c>
       <c r="B13" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2185,13 +2179,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>479698</v>
+        <v>479635</v>
       </c>
       <c r="R13" t="n">
-        <v>7027342</v>
+        <v>7027621</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2225,7 +2219,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2277,10 +2271,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122606280</v>
+        <v>122609386</v>
       </c>
       <c r="B14" t="n">
-        <v>79844</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2293,34 +2287,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>479693</v>
+        <v>479699</v>
       </c>
       <c r="R14" t="n">
-        <v>7027399</v>
+        <v>7027340</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2357,7 +2356,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Skrovellav på en gammal grov sälg med 54 cm i brösthöjdsdiameter.</t>
+          <t>Äldre ringhack på stambasen av en stående död gran. Volym stående död ved här som ger medelhögt till högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2371,27 +2370,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2409,10 +2408,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122609837</v>
+        <v>122606280</v>
       </c>
       <c r="B15" t="n">
-        <v>78762</v>
+        <v>79848</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2425,21 +2424,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2449,10 +2448,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>479643</v>
+        <v>479693</v>
       </c>
       <c r="R15" t="n">
-        <v>7027326</v>
+        <v>7027399</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2489,7 +2488,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Skrovellav på en gammal grov sälg med 54 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2503,17 +2502,17 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -2523,7 +2522,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Branch on living tree # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2541,10 +2540,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122613055</v>
+        <v>122606868</v>
       </c>
       <c r="B16" t="n">
-        <v>79843</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2557,40 +2556,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>479722</v>
+        <v>479661</v>
       </c>
       <c r="R16" t="n">
-        <v>7027290</v>
+        <v>7027516</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2622,49 +2618,38 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Enstaka små bålar på en grov gammal asp.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2682,10 +2667,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122608462</v>
+        <v>122613090</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2698,47 +2683,44 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kvarnbäcken, Kvarnbäcken, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>479583</v>
+        <v>479694</v>
       </c>
       <c r="R17" t="n">
-        <v>7027629</v>
+        <v>7027295</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2772,7 +2754,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Äldre ringhack som bedöms vara 5-10 år gamla. På en gran med tydliga kådaflöden. Hyfsat gott om död ved här.</t>
+          <t>Ett gäng "knippen" med stora lunglavsbålar på en asp.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2781,6 +2763,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2789,24 +2772,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+        </is>
+      </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2824,10 +2812,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122609252</v>
+        <v>122613066</v>
       </c>
       <c r="B18" t="n">
-        <v>78762</v>
+        <v>79847</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2840,37 +2828,44 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>479714</v>
+        <v>479702</v>
       </c>
       <c r="R18" t="n">
-        <v>7027356</v>
+        <v>7027288</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2902,12 +2897,18 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Lunglav på en grovbarkad asp.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2916,24 +2917,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+        </is>
+      </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Populus tremula</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2951,10 +2957,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122609424</v>
+        <v>122608462</v>
       </c>
       <c r="B19" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2967,42 +2973,47 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Kvarnbäcken, Kvarnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>479729</v>
+        <v>479583</v>
       </c>
       <c r="R19" t="n">
-        <v>7027353</v>
+        <v>7027629</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3036,7 +3047,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Fertila bålar på en smal böjd sälg.</t>
+          <t>Äldre ringhack som bedöms vara 5-10 år gamla. På en gran med tydliga kådaflöden. Hyfsat gott om död ved här.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3055,22 +3066,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3088,10 +3099,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122608343</v>
+        <v>122609468</v>
       </c>
       <c r="B20" t="n">
-        <v>78762</v>
+        <v>79847</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3104,37 +3115,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kvarnbäcken, Kvarnbäcken, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>479569</v>
+        <v>479731</v>
       </c>
       <c r="R20" t="n">
-        <v>7027674</v>
+        <v>7027323</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3168,7 +3184,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ymnigt med lunglav längs 7 meter på en något smalare sälg.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3187,22 +3203,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3220,7 +3236,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122609386</v>
+        <v>122607115</v>
       </c>
       <c r="B21" t="n">
         <v>57478</v>
@@ -3256,7 +3272,12 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3265,13 +3286,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>479699</v>
+        <v>479652</v>
       </c>
       <c r="R21" t="n">
-        <v>7027340</v>
+        <v>7027551</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3305,7 +3326,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen av en stående död gran. Volym stående död ved här som ger medelhögt till högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Både färska och äldre ringhack på stambasen. I skogsbeståndet runt fyndplatsen finns medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3334,12 +3355,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3357,10 +3378,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122607246</v>
+        <v>122606232</v>
       </c>
       <c r="B22" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3373,36 +3394,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3411,10 +3423,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>479659</v>
+        <v>479707</v>
       </c>
       <c r="R22" t="n">
-        <v>7027556</v>
+        <v>7027397</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3451,7 +3463,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Observerades i flerskiktad granskog.</t>
+          <t>Fertil lunglav på en undertryck gran intill en gammal grov sälg.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3465,7 +3477,27 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3483,10 +3515,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122607115</v>
+        <v>122608343</v>
       </c>
       <c r="B23" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3499,47 +3531,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Kvarnbäcken, Kvarnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>479652</v>
+        <v>479569</v>
       </c>
       <c r="R23" t="n">
-        <v>7027551</v>
+        <v>7027674</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3573,7 +3595,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Både färska och äldre ringhack på stambasen. I skogsbeståndet runt fyndplatsen finns medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3602,12 +3624,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3625,10 +3647,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122607124</v>
+        <v>122607879</v>
       </c>
       <c r="B24" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3641,47 +3663,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>479654</v>
+        <v>479622</v>
       </c>
       <c r="R24" t="n">
-        <v>7027561</v>
+        <v>7027648</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3715,7 +3727,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Både äldre och färska ringhack på stambasen.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3744,12 +3756,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3767,10 +3779,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122606232</v>
+        <v>122606334</v>
       </c>
       <c r="B25" t="n">
-        <v>79843</v>
+        <v>78766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3783,39 +3795,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>479707</v>
+        <v>479692</v>
       </c>
       <c r="R25" t="n">
-        <v>7027397</v>
+        <v>7027424</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3848,11 +3855,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på en undertryck gran intill en gammal grov sälg.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3904,10 +3906,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122606696</v>
+        <v>122606026</v>
       </c>
       <c r="B26" t="n">
-        <v>78762</v>
+        <v>90962</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3920,34 +3922,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>479678</v>
+        <v>479756</v>
       </c>
       <c r="R26" t="n">
-        <v>7027508</v>
+        <v>7027477</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -4008,12 +4015,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4031,10 +4038,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122613090</v>
+        <v>122606169</v>
       </c>
       <c r="B27" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4065,26 +4072,24 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>479694</v>
+        <v>479698</v>
       </c>
       <c r="R27" t="n">
-        <v>7027295</v>
+        <v>7027398</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4118,7 +4123,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ett gäng "knippen" med stora lunglavsbålar på en asp.</t>
+          <t>Rikligt med lunglav där vissa bålar är fertila med apothecier. På en gammal grovbarkad sälg med 54 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4127,28 +4132,22 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
@@ -4158,7 +4157,7 @@
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4176,10 +4175,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122607565</v>
+        <v>122605930</v>
       </c>
       <c r="B28" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4216,10 +4215,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>479638</v>
+        <v>479743</v>
       </c>
       <c r="R28" t="n">
-        <v>7027601</v>
+        <v>7027472</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4256,7 +4255,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>Långväxta bålar på flera träd.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4308,10 +4307,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122613066</v>
+        <v>122609424</v>
       </c>
       <c r="B29" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4342,26 +4341,24 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>479702</v>
+        <v>479729</v>
       </c>
       <c r="R29" t="n">
-        <v>7027288</v>
+        <v>7027353</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4395,7 +4392,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Lunglav på en grovbarkad asp.</t>
+          <t>Fertila bålar på en smal böjd sälg.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4404,7 +4401,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4413,19 +4409,14 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
-        </is>
-      </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
@@ -4435,7 +4426,7 @@
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4453,10 +4444,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122606631</v>
+        <v>122606431</v>
       </c>
       <c r="B30" t="n">
-        <v>79843</v>
+        <v>78766</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4469,29 +4460,24 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
@@ -4501,7 +4487,7 @@
         <v>479711</v>
       </c>
       <c r="R30" t="n">
-        <v>7027473</v>
+        <v>7027387</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4538,7 +4524,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en asp.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4552,27 +4538,27 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4590,10 +4576,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122606273</v>
+        <v>122607565</v>
       </c>
       <c r="B31" t="n">
-        <v>79844</v>
+        <v>78766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4606,42 +4592,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>479698</v>
+        <v>479638</v>
       </c>
       <c r="R31" t="n">
-        <v>7027398</v>
+        <v>7027601</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4675,7 +4656,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Skrovellav på en undertryck gran intill en gammal grov sälg.</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4689,7 +4670,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -4727,10 +4708,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122613058</v>
+        <v>122612982</v>
       </c>
       <c r="B32" t="n">
-        <v>78762</v>
+        <v>79847</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4743,26 +4724,30 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4770,13 +4755,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>479722</v>
+        <v>479738</v>
       </c>
       <c r="R32" t="n">
-        <v>7027290</v>
+        <v>7027319</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4806,6 +4791,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Grova gamla lunglavsbålar på en lutande sälg.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4830,22 +4820,27 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>En smal lutande sälg.</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En smal lutande sälg.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4863,10 +4858,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122609468</v>
+        <v>122606696</v>
       </c>
       <c r="B33" t="n">
-        <v>79843</v>
+        <v>78766</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4879,39 +4874,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>479731</v>
+        <v>479678</v>
       </c>
       <c r="R33" t="n">
-        <v>7027323</v>
+        <v>7027508</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4946,11 +4936,6 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ymnigt med lunglav längs 7 meter på en något smalare sälg.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4967,22 +4952,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5000,10 +4985,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122607162</v>
+        <v>122606631</v>
       </c>
       <c r="B34" t="n">
-        <v>78762</v>
+        <v>79847</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5016,34 +5001,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>479650</v>
+        <v>479711</v>
       </c>
       <c r="R34" t="n">
-        <v>7027549</v>
+        <v>7027473</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5080,7 +5070,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Enstaka bålar på en asp.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5099,22 +5089,22 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5132,10 +5122,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122606334</v>
+        <v>122613058</v>
       </c>
       <c r="B35" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5166,19 +5156,22 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>479692</v>
+        <v>479722</v>
       </c>
       <c r="R35" t="n">
-        <v>7027424</v>
+        <v>7027290</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5216,12 +5209,18 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -5259,10 +5258,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122608228</v>
+        <v>122613055</v>
       </c>
       <c r="B36" t="n">
-        <v>78762</v>
+        <v>79847</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5275,37 +5274,40 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kvarnbäcken, Kvarnbäcken, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>479594</v>
+        <v>479722</v>
       </c>
       <c r="R36" t="n">
-        <v>7027696</v>
+        <v>7027290</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5339,7 +5341,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Enstaka små bålar på en grov gammal asp.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5348,6 +5350,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -5356,24 +5359,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+        </is>
+      </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Populus tremula</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5391,10 +5399,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122606868</v>
+        <v>122609281</v>
       </c>
       <c r="B37" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5431,13 +5439,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>479661</v>
+        <v>479698</v>
       </c>
       <c r="R37" t="n">
-        <v>7027516</v>
+        <v>7027342</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5469,6 +5477,11 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flera granar.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5480,7 +5493,7 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -5518,10 +5531,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122613032</v>
+        <v>122608228</v>
       </c>
       <c r="B38" t="n">
-        <v>79843</v>
+        <v>78766</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5534,44 +5547,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Kvarnbäcken, Kvarnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>479731</v>
+        <v>479594</v>
       </c>
       <c r="R38" t="n">
-        <v>7027291</v>
+        <v>7027696</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5605,7 +5611,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>En hel del bålar på en skadad sälg.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5614,7 +5620,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5623,29 +5628,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
-        </is>
-      </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5666,7 +5666,7 @@
         <v>122609753</v>
       </c>
       <c r="B39" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -6072,10 +6072,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122607410</v>
+        <v>122613278</v>
       </c>
       <c r="B42" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6088,47 +6088,44 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>479644</v>
+        <v>479628</v>
       </c>
       <c r="R42" t="n">
-        <v>7027599</v>
+        <v>7027338</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6162,7 +6159,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Både äldre och färska ringhack på stambasen. I skogsbeståndet runt fyndplatsen finns medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Rikligt med lunglavsbålar på gran intill en gammal sälg med lunglav.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6171,6 +6168,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -6179,6 +6177,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+        </is>
+      </c>
       <c r="AJ42" t="inlineStr">
         <is>
           <t>gran</t>
@@ -6191,12 +6194,12 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6214,10 +6217,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122613278</v>
+        <v>122607410</v>
       </c>
       <c r="B43" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6230,44 +6233,47 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>479628</v>
+        <v>479644</v>
       </c>
       <c r="R43" t="n">
-        <v>7027338</v>
+        <v>7027599</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6301,7 +6307,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Rikligt med lunglavsbålar på gran intill en gammal sälg med lunglav.</t>
+          <t>Både äldre och färska ringhack på stambasen. I skogsbeståndet runt fyndplatsen finns medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6310,7 +6316,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -6319,11 +6324,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
-        </is>
-      </c>
       <c r="AJ43" t="inlineStr">
         <is>
           <t>gran</t>
@@ -6336,12 +6336,12 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -7447,10 +7447,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122695492</v>
+        <v>122695011</v>
       </c>
       <c r="B52" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7463,39 +7463,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>479770</v>
+        <v>479729</v>
       </c>
       <c r="R52" t="n">
-        <v>7027300</v>
+        <v>7027486</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7532,7 +7527,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Växer på en lite smalare sälg intill lunglav.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7551,22 +7546,22 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7584,7 +7579,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122695011</v>
+        <v>122698247</v>
       </c>
       <c r="B53" t="n">
         <v>78766</v>
@@ -7624,10 +7619,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>479729</v>
+        <v>479696</v>
       </c>
       <c r="R53" t="n">
-        <v>7027486</v>
+        <v>7027370</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7660,11 +7655,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7716,10 +7706,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122698247</v>
+        <v>122695322</v>
       </c>
       <c r="B54" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7732,34 +7722,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>479696</v>
+        <v>479771</v>
       </c>
       <c r="R54" t="n">
-        <v>7027370</v>
+        <v>7027387</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7794,6 +7789,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>På en lutande krokig sälg.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -7810,22 +7810,22 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7843,10 +7843,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122695322</v>
+        <v>122695492</v>
       </c>
       <c r="B55" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7859,21 +7859,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7888,10 +7888,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>479771</v>
+        <v>479770</v>
       </c>
       <c r="R55" t="n">
-        <v>7027387</v>
+        <v>7027300</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7928,7 +7928,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På en lutande krokig sälg.</t>
+          <t>Växer på en lite smalare sälg intill lunglav.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8254,10 +8254,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122697862</v>
+        <v>122695655</v>
       </c>
       <c r="B58" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8270,37 +8270,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>479630</v>
+        <v>479759</v>
       </c>
       <c r="R58" t="n">
-        <v>7027362</v>
+        <v>7027292</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8330,6 +8335,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Växer på två granar intill en sälg med ymnig påväxt av lunglav.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8381,10 +8391,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122695655</v>
+        <v>122697862</v>
       </c>
       <c r="B59" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8397,42 +8407,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>479759</v>
+        <v>479630</v>
       </c>
       <c r="R59" t="n">
-        <v>7027292</v>
+        <v>7027362</v>
       </c>
       <c r="S59" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8462,11 +8467,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Växer på två granar intill en sälg med ymnig påväxt av lunglav.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -10233,7 +10233,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122697966</v>
+        <v>122697286</v>
       </c>
       <c r="B73" t="n">
         <v>79847</v>
@@ -10278,10 +10278,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>479660</v>
+        <v>479663</v>
       </c>
       <c r="R73" t="n">
-        <v>7027363</v>
+        <v>7027246</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -10365,7 +10365,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122697286</v>
+        <v>122695516</v>
       </c>
       <c r="B74" t="n">
         <v>79847</v>
@@ -10410,10 +10410,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>479663</v>
+        <v>479766</v>
       </c>
       <c r="R74" t="n">
-        <v>7027246</v>
+        <v>7027310</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10448,6 +10448,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Växer på en lite smalare sälg intill skrovellav.</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -10464,12 +10469,12 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM74" t="inlineStr">
@@ -10479,7 +10484,7 @@
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10497,7 +10502,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122695516</v>
+        <v>122697966</v>
       </c>
       <c r="B75" t="n">
         <v>79847</v>
@@ -10542,10 +10547,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>479766</v>
+        <v>479660</v>
       </c>
       <c r="R75" t="n">
-        <v>7027310</v>
+        <v>7027363</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10580,11 +10585,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Växer på en lite smalare sälg intill skrovellav.</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -10601,12 +10601,12 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM75" t="inlineStr">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -12373,10 +12373,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122696521</v>
+        <v>122697352</v>
       </c>
       <c r="B89" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -12389,34 +12389,24 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
@@ -12426,10 +12416,10 @@
         <v>479674</v>
       </c>
       <c r="R89" t="n">
-        <v>7027109</v>
+        <v>7027178</v>
       </c>
       <c r="S89" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -12461,11 +12451,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Färska hackspår i stambasen av en smal gran i granskog med stora mängder liggande död ved.</t>
-        </is>
-      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
@@ -12492,12 +12477,12 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -12515,7 +12500,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122697352</v>
+        <v>122698085</v>
       </c>
       <c r="B90" t="n">
         <v>78766</v>
@@ -12555,10 +12540,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>479674</v>
+        <v>479659</v>
       </c>
       <c r="R90" t="n">
-        <v>7027178</v>
+        <v>7027303</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -12642,10 +12627,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122698085</v>
+        <v>122696521</v>
       </c>
       <c r="B91" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -12658,37 +12643,47 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>479659</v>
+        <v>479674</v>
       </c>
       <c r="R91" t="n">
-        <v>7027303</v>
+        <v>7027109</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -12720,6 +12715,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Färska hackspår i stambasen av en smal gran i granskog med stora mängder liggande död ved.</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
@@ -12746,12 +12746,12 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>

--- a/artfynd/A 60372-2024 artfynd.xlsx
+++ b/artfynd/A 60372-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122606649</v>
+        <v>122607124</v>
       </c>
       <c r="B2" t="n">
-        <v>79883</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,36 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +725,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>479715</v>
+        <v>479654</v>
       </c>
       <c r="R2" t="n">
-        <v>7027462</v>
+        <v>7027561</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,7 +765,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>En samling bålar på ca 2 meters höjd på aspens stam.</t>
+          <t>Både äldre och färska ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,22 +784,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -812,7 +817,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122607162</v>
+        <v>122608343</v>
       </c>
       <c r="B3" t="n">
         <v>78766</v>
@@ -848,17 +853,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Kvarnbäcken, Kvarnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479650</v>
+        <v>479569</v>
       </c>
       <c r="R3" t="n">
-        <v>7027549</v>
+        <v>7027674</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -892,7 +897,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -944,10 +949,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122606273</v>
+        <v>122607162</v>
       </c>
       <c r="B4" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -960,42 +965,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479698</v>
+        <v>479650</v>
       </c>
       <c r="R4" t="n">
-        <v>7027398</v>
+        <v>7027549</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Skrovellav på en undertryck gran intill en gammal grov sälg.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1081,10 +1081,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122607246</v>
+        <v>122613032</v>
       </c>
       <c r="B5" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1097,51 +1097,44 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>479659</v>
+        <v>479731</v>
       </c>
       <c r="R5" t="n">
-        <v>7027556</v>
+        <v>7027291</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1175,7 +1168,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Observerades i flerskiktad granskog.</t>
+          <t>En hel del bålar på en skadad sälg.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1184,12 +1177,38 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1207,10 +1226,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122607124</v>
+        <v>122609252</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1223,44 +1242,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>479654</v>
+        <v>479714</v>
       </c>
       <c r="R6" t="n">
-        <v>7027561</v>
+        <v>7027356</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1295,11 +1304,6 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Både äldre och färska ringhack på stambasen.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1326,12 +1330,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1349,10 +1353,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122607263</v>
+        <v>122607246</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1365,34 +1369,48 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>479655</v>
+        <v>479659</v>
       </c>
       <c r="R7" t="n">
-        <v>7027573</v>
+        <v>7027556</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1427,6 +1445,11 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Observerades i flerskiktad granskog.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1439,26 +1462,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1476,10 +1479,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122608509</v>
+        <v>122608228</v>
       </c>
       <c r="B8" t="n">
-        <v>79751</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1488,38 +1491,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Kvarnbäcken, Kvarnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>479617</v>
+        <v>479594</v>
       </c>
       <c r="R8" t="n">
-        <v>7027598</v>
+        <v>7027696</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1554,6 +1557,11 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1570,22 +1578,22 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1603,10 +1611,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122609837</v>
+        <v>122606232</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1619,34 +1627,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>479643</v>
+        <v>479707</v>
       </c>
       <c r="R9" t="n">
-        <v>7027326</v>
+        <v>7027397</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1683,7 +1696,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Fertil lunglav på en undertryck gran intill en gammal grov sälg.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1697,7 +1710,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1735,7 +1748,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122613032</v>
+        <v>122609424</v>
       </c>
       <c r="B10" t="n">
         <v>79847</v>
@@ -1769,26 +1782,24 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>479731</v>
+        <v>479729</v>
       </c>
       <c r="R10" t="n">
-        <v>7027291</v>
+        <v>7027353</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1822,7 +1833,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>En hel del bålar på en skadad sälg.</t>
+          <t>Fertila bålar på en smal böjd sälg.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1831,18 +1842,12 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1880,10 +1885,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122609252</v>
+        <v>122608509</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>79751</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1892,25 +1897,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1920,10 +1925,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>479714</v>
+        <v>479617</v>
       </c>
       <c r="R11" t="n">
-        <v>7027356</v>
+        <v>7027598</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1974,22 +1979,22 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2007,10 +2012,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122609496</v>
+        <v>122607115</v>
       </c>
       <c r="B12" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2023,27 +2028,32 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2052,13 +2062,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>479735</v>
+        <v>479652</v>
       </c>
       <c r="R12" t="n">
-        <v>7027318</v>
+        <v>7027551</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2090,6 +2100,11 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Både färska och äldre ringhack på stambasen. I skogsbeståndet runt fyndplatsen finns medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2116,12 +2131,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2139,10 +2154,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122607620</v>
+        <v>122606026</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2155,34 +2170,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>479635</v>
+        <v>479756</v>
       </c>
       <c r="R13" t="n">
-        <v>7027621</v>
+        <v>7027477</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2217,11 +2237,6 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2248,12 +2263,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2271,10 +2286,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122609386</v>
+        <v>122613090</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2287,42 +2302,44 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>479699</v>
+        <v>479694</v>
       </c>
       <c r="R14" t="n">
-        <v>7027340</v>
+        <v>7027295</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2356,7 +2373,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen av en stående död gran. Volym stående död ved här som ger medelhögt till högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ett gäng "knippen" med stora lunglavsbålar på en asp.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2365,6 +2382,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2373,24 +2391,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+        </is>
+      </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2408,10 +2431,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122606280</v>
+        <v>122607565</v>
       </c>
       <c r="B15" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2424,21 +2447,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2448,10 +2471,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>479693</v>
+        <v>479638</v>
       </c>
       <c r="R15" t="n">
-        <v>7027399</v>
+        <v>7027601</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2488,7 +2511,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Skrovellav på en gammal grov sälg med 54 cm i brösthöjdsdiameter.</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2502,17 +2525,17 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -2522,7 +2545,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2540,7 +2563,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122606868</v>
+        <v>122606431</v>
       </c>
       <c r="B16" t="n">
         <v>78766</v>
@@ -2580,10 +2603,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>479661</v>
+        <v>479711</v>
       </c>
       <c r="R16" t="n">
-        <v>7027516</v>
+        <v>7027387</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2616,6 +2639,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2667,7 +2695,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122613090</v>
+        <v>122606631</v>
       </c>
       <c r="B17" t="n">
         <v>79847</v>
@@ -2701,26 +2729,24 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>med soral</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>479694</v>
+        <v>479711</v>
       </c>
       <c r="R17" t="n">
-        <v>7027295</v>
+        <v>7027473</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2754,7 +2780,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ett gäng "knippen" med stora lunglavsbålar på en asp.</t>
+          <t>Enstaka bålar på en asp.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2763,18 +2789,12 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -2812,10 +2832,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122613066</v>
+        <v>122609753</v>
       </c>
       <c r="B18" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2828,44 +2848,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>479702</v>
+        <v>479670</v>
       </c>
       <c r="R18" t="n">
-        <v>7027288</v>
+        <v>7027294</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2897,18 +2910,12 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Lunglav på en grovbarkad asp.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2917,29 +2924,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
-        </is>
-      </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2957,10 +2959,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122608462</v>
+        <v>122609468</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2973,47 +2975,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kvarnbäcken, Kvarnbäcken, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>479583</v>
+        <v>479731</v>
       </c>
       <c r="R19" t="n">
-        <v>7027629</v>
+        <v>7027323</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3047,7 +3044,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Äldre ringhack som bedöms vara 5-10 år gamla. På en gran med tydliga kådaflöden. Hyfsat gott om död ved här.</t>
+          <t>Ymnigt med lunglav längs 7 meter på en något smalare sälg.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3066,22 +3063,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3099,10 +3096,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122609468</v>
+        <v>122605930</v>
       </c>
       <c r="B20" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3115,39 +3112,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>479731</v>
+        <v>479743</v>
       </c>
       <c r="R20" t="n">
-        <v>7027323</v>
+        <v>7027472</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3184,7 +3176,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ymnigt med lunglav längs 7 meter på en något smalare sälg.</t>
+          <t>Långväxta bålar på flera träd.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3203,22 +3195,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3236,10 +3228,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122607115</v>
+        <v>122606649</v>
       </c>
       <c r="B21" t="n">
-        <v>57478</v>
+        <v>79883</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3248,36 +3240,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3286,13 +3273,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>479652</v>
+        <v>479715</v>
       </c>
       <c r="R21" t="n">
-        <v>7027551</v>
+        <v>7027462</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3326,7 +3313,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Både färska och äldre ringhack på stambasen. I skogsbeståndet runt fyndplatsen finns medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>En samling bålar på ca 2 meters höjd på aspens stam.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3345,22 +3332,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3378,7 +3365,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122606232</v>
+        <v>122613055</v>
       </c>
       <c r="B22" t="n">
         <v>79847</v>
@@ -3412,24 +3399,22 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>479707</v>
+        <v>479722</v>
       </c>
       <c r="R22" t="n">
-        <v>7027397</v>
+        <v>7027290</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3463,7 +3448,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Fertil lunglav på en undertryck gran intill en gammal grov sälg.</t>
+          <t>Enstaka små bålar på en grov gammal asp.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3472,32 +3457,38 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Populus tremula</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3515,10 +3506,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122608343</v>
+        <v>122606280</v>
       </c>
       <c r="B23" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3531,37 +3522,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kvarnbäcken, Kvarnbäcken, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>479569</v>
+        <v>479693</v>
       </c>
       <c r="R23" t="n">
-        <v>7027674</v>
+        <v>7027399</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3595,7 +3586,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Skrovellav på en gammal grov sälg med 54 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3609,17 +3600,17 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
@@ -3629,7 +3620,7 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Branch on living tree # Salix caprea</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3647,7 +3638,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122607879</v>
+        <v>122609837</v>
       </c>
       <c r="B24" t="n">
         <v>78766</v>
@@ -3687,13 +3678,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>479622</v>
+        <v>479643</v>
       </c>
       <c r="R24" t="n">
-        <v>7027648</v>
+        <v>7027326</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3779,10 +3770,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122606334</v>
+        <v>122609496</v>
       </c>
       <c r="B25" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3795,37 +3786,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>479692</v>
+        <v>479735</v>
       </c>
       <c r="R25" t="n">
-        <v>7027424</v>
+        <v>7027318</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3868,7 +3864,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
@@ -3906,10 +3902,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122606026</v>
+        <v>122612982</v>
       </c>
       <c r="B26" t="n">
-        <v>90962</v>
+        <v>79847</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3922,39 +3918,41 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>479756</v>
+        <v>479738</v>
       </c>
       <c r="R26" t="n">
-        <v>7027477</v>
+        <v>7027319</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3989,12 +3987,18 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Grova gamla lunglavsbålar på en lutande sälg.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -4003,24 +4007,34 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+        </is>
+      </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>En smal lutande sälg.</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En smal lutande sälg.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4038,10 +4052,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122606169</v>
+        <v>122606696</v>
       </c>
       <c r="B27" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4054,42 +4068,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>479698</v>
+        <v>479678</v>
       </c>
       <c r="R27" t="n">
-        <v>7027398</v>
+        <v>7027508</v>
       </c>
       <c r="S27" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4121,11 +4130,6 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglav där vissa bålar är fertila med apothecier. På en gammal grovbarkad sälg med 54 cm i brösthöjdsdiameter.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -4137,27 +4141,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4175,7 +4179,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122605930</v>
+        <v>122606868</v>
       </c>
       <c r="B28" t="n">
         <v>78766</v>
@@ -4215,10 +4219,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>479743</v>
+        <v>479661</v>
       </c>
       <c r="R28" t="n">
-        <v>7027472</v>
+        <v>7027516</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4253,11 +4257,6 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flera träd.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4269,7 +4268,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -4307,10 +4306,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122609424</v>
+        <v>122608462</v>
       </c>
       <c r="B29" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4323,42 +4322,47 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Kvarnbäcken, Kvarnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>479729</v>
+        <v>479583</v>
       </c>
       <c r="R29" t="n">
-        <v>7027353</v>
+        <v>7027629</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4392,7 +4396,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Fertila bålar på en smal böjd sälg.</t>
+          <t>Äldre ringhack som bedöms vara 5-10 år gamla. På en gran med tydliga kådaflöden. Hyfsat gott om död ved här.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4411,22 +4415,22 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4444,7 +4448,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122606431</v>
+        <v>122606334</v>
       </c>
       <c r="B30" t="n">
         <v>78766</v>
@@ -4484,10 +4488,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>479711</v>
+        <v>479692</v>
       </c>
       <c r="R30" t="n">
-        <v>7027387</v>
+        <v>7027424</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4520,11 +4524,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4576,7 +4575,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122607565</v>
+        <v>122607263</v>
       </c>
       <c r="B31" t="n">
         <v>78766</v>
@@ -4616,10 +4615,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>479638</v>
+        <v>479655</v>
       </c>
       <c r="R31" t="n">
-        <v>7027601</v>
+        <v>7027573</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4652,11 +4651,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4708,10 +4702,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122612982</v>
+        <v>122609386</v>
       </c>
       <c r="B32" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4724,41 +4718,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>479738</v>
+        <v>479699</v>
       </c>
       <c r="R32" t="n">
-        <v>7027319</v>
+        <v>7027340</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4795,7 +4787,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Grova gamla lunglavsbålar på en lutande sälg.</t>
+          <t>Äldre ringhack på stambasen av en stående död gran. Volym stående död ved här som ger medelhögt till högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4804,7 +4796,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4813,34 +4804,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
-        </is>
-      </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL32" t="inlineStr">
-        <is>
-          <t>En smal lutande sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En smal lutande sälg.</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4858,10 +4839,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122606696</v>
+        <v>122613066</v>
       </c>
       <c r="B33" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4874,37 +4855,44 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>479678</v>
+        <v>479702</v>
       </c>
       <c r="R33" t="n">
-        <v>7027508</v>
+        <v>7027288</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4936,12 +4924,18 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Lunglav på en grovbarkad asp.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4950,24 +4944,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+        </is>
+      </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Populus tremula</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4985,10 +4984,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122606631</v>
+        <v>122606273</v>
       </c>
       <c r="B34" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5001,21 +5000,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -5030,13 +5029,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>479711</v>
+        <v>479698</v>
       </c>
       <c r="R34" t="n">
-        <v>7027473</v>
+        <v>7027398</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5070,7 +5069,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en asp.</t>
+          <t>Skrovellav på en undertryck gran intill en gammal grov sälg.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5084,27 +5083,27 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5258,7 +5257,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122613055</v>
+        <v>122606169</v>
       </c>
       <c r="B36" t="n">
         <v>79847</v>
@@ -5292,22 +5291,24 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>479722</v>
+        <v>479698</v>
       </c>
       <c r="R36" t="n">
-        <v>7027290</v>
+        <v>7027398</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5341,7 +5342,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Enstaka små bålar på en grov gammal asp.</t>
+          <t>Rikligt med lunglav där vissa bålar är fertila med apothecier. På en gammal grovbarkad sälg med 54 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5350,28 +5351,22 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
@@ -5381,7 +5376,7 @@
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5531,7 +5526,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122608228</v>
+        <v>122607879</v>
       </c>
       <c r="B38" t="n">
         <v>78766</v>
@@ -5567,17 +5562,17 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kvarnbäcken, Kvarnbäcken, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>479594</v>
+        <v>479622</v>
       </c>
       <c r="R38" t="n">
-        <v>7027696</v>
+        <v>7027648</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5663,7 +5658,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122609753</v>
+        <v>122607620</v>
       </c>
       <c r="B39" t="n">
         <v>78766</v>
@@ -5703,10 +5698,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>479670</v>
+        <v>479635</v>
       </c>
       <c r="R39" t="n">
-        <v>7027294</v>
+        <v>7027621</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5739,6 +5734,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5790,10 +5790,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122607746</v>
+        <v>122609073</v>
       </c>
       <c r="B40" t="n">
-        <v>79751</v>
+        <v>79847</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5802,48 +5802,46 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>479627</v>
+        <v>479738</v>
       </c>
       <c r="R40" t="n">
-        <v>7027656</v>
+        <v>7027404</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5877,7 +5875,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Skinnlav på asp där flertalet bålar är fertila med apothecier.</t>
+          <t>På en smal sälg.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5886,7 +5884,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5895,19 +5892,14 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>Flerskiktad kontinuitetsskog dominerad av gran och med återkommande inslag av asp.</t>
-        </is>
-      </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
@@ -5917,7 +5909,7 @@
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5935,10 +5927,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122609140</v>
+        <v>122613280</v>
       </c>
       <c r="B41" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5951,42 +5943,44 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>479723</v>
+        <v>479628</v>
       </c>
       <c r="R41" t="n">
-        <v>7027396</v>
+        <v>7027338</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -6020,7 +6014,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ymnig påväxt av lunglav längs flera meter på en gammal sälg. Fertila bålar med apothecier.</t>
+          <t>På renar av gran blandat med lunglav.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6029,6 +6023,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -6037,24 +6032,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+        </is>
+      </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6072,10 +6072,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122613278</v>
+        <v>122607746</v>
       </c>
       <c r="B42" t="n">
-        <v>79847</v>
+        <v>79751</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6084,48 +6084,48 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>479628</v>
+        <v>479627</v>
       </c>
       <c r="R42" t="n">
-        <v>7027338</v>
+        <v>7027656</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Rikligt med lunglavsbålar på gran intill en gammal sälg med lunglav.</t>
+          <t>Skinnlav på asp där flertalet bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6179,27 +6179,27 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+          <t>Flerskiktad kontinuitetsskog dominerad av gran och med återkommande inslag av asp.</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6217,10 +6217,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122607410</v>
+        <v>122613145</v>
       </c>
       <c r="B43" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6233,44 +6233,41 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>479644</v>
+        <v>479634</v>
       </c>
       <c r="R43" t="n">
-        <v>7027599</v>
+        <v>7027302</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6307,7 +6304,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Både äldre och färska ringhack på stambasen. I skogsbeståndet runt fyndplatsen finns medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Ymnig påväxt av lunglav längs flera meter på en sälgstam. Vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6316,6 +6313,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -6324,24 +6322,34 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+        </is>
+      </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL43" t="inlineStr">
+        <is>
+          <t>En svagt lutande sälg.</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En svagt lutande sälg.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6359,10 +6367,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122608090</v>
+        <v>122608974</v>
       </c>
       <c r="B44" t="n">
-        <v>79751</v>
+        <v>79847</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6371,41 +6379,46 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>479602</v>
+        <v>479682</v>
       </c>
       <c r="R44" t="n">
-        <v>7027640</v>
+        <v>7027484</v>
       </c>
       <c r="S44" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6486,10 +6499,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122613281</v>
+        <v>122613271</v>
       </c>
       <c r="B45" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6502,26 +6515,30 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6569,7 +6586,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Med långväxta bålar och på flera granar.</t>
+          <t>Riklig påväxt av lunglavsbålar på en gammal sälg. Vissa bålar är fertila med apothecier. Här växer även rikligt med lunglav på gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6594,22 +6611,27 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL45" t="inlineStr">
+        <is>
+          <t>En gammal grov sälg.</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea # En gammal grov sälg.</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6627,10 +6649,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122613145</v>
+        <v>122613281</v>
       </c>
       <c r="B46" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6643,30 +6665,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6674,13 +6692,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>479634</v>
+        <v>479628</v>
       </c>
       <c r="R46" t="n">
-        <v>7027302</v>
+        <v>7027338</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6714,7 +6732,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ymnig påväxt av lunglav längs flera meter på en sälgstam. Vissa bålar är fertila med apothecier.</t>
+          <t>Med långväxta bålar och på flera granar.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6739,27 +6757,22 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL46" t="inlineStr">
-        <is>
-          <t>En svagt lutande sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En svagt lutande sälg.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6777,10 +6790,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122608974</v>
+        <v>122609714</v>
       </c>
       <c r="B47" t="n">
-        <v>79847</v>
+        <v>57631</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6793,42 +6806,49 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>479682</v>
+        <v>479677</v>
       </c>
       <c r="R47" t="n">
-        <v>7027484</v>
+        <v>7027303</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6860,6 +6880,11 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Observation i flerskiktad granskog med stående murkna björkhögstubbar som är gynnsamt för talltitans häckning.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6874,24 +6899,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6909,10 +6919,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122609714</v>
+        <v>122609140</v>
       </c>
       <c r="B48" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6925,46 +6935,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>479677</v>
+        <v>479723</v>
       </c>
       <c r="R48" t="n">
-        <v>7027303</v>
+        <v>7027396</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -7001,7 +7004,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Observation i flerskiktad granskog med stående murkna björkhögstubbar som är gynnsamt för talltitans häckning.</t>
+          <t>Ymnig påväxt av lunglav längs flera meter på en gammal sälg. Fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7018,9 +7021,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -7038,10 +7056,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122613280</v>
+        <v>122608090</v>
       </c>
       <c r="B49" t="n">
-        <v>79848</v>
+        <v>79751</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -7050,48 +7068,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>479628</v>
+        <v>479602</v>
       </c>
       <c r="R49" t="n">
-        <v>7027338</v>
+        <v>7027640</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -7123,18 +7134,12 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På renar av gran blandat med lunglav.</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -7143,29 +7148,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
-        </is>
-      </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7183,10 +7183,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122609073</v>
+        <v>122607364</v>
       </c>
       <c r="B50" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7199,27 +7199,27 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -7228,13 +7228,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>479738</v>
+        <v>479644</v>
       </c>
       <c r="R50" t="n">
-        <v>7027404</v>
+        <v>7027599</v>
       </c>
       <c r="S50" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På en smal sälg.</t>
+          <t>Både färska och äldre ringhack på stambasen. I skogsbeståndet runt fyndplatsen finns medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7287,22 +7287,22 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7320,7 +7320,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122697534</v>
+        <v>122697882</v>
       </c>
       <c r="B51" t="n">
         <v>78766</v>
@@ -7360,13 +7360,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>479644</v>
+        <v>479664</v>
       </c>
       <c r="R51" t="n">
-        <v>7027243</v>
+        <v>7027326</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7398,6 +7398,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -7409,7 +7414,7 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
@@ -7447,10 +7452,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122695011</v>
+        <v>122695322</v>
       </c>
       <c r="B52" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7463,34 +7468,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>479729</v>
+        <v>479771</v>
       </c>
       <c r="R52" t="n">
-        <v>7027486</v>
+        <v>7027387</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7527,7 +7537,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På en lutande krokig sälg.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7546,22 +7556,22 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7579,7 +7589,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122698247</v>
+        <v>122698275</v>
       </c>
       <c r="B53" t="n">
         <v>78766</v>
@@ -7619,10 +7629,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>479696</v>
+        <v>479734</v>
       </c>
       <c r="R53" t="n">
-        <v>7027370</v>
+        <v>7027357</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7655,6 +7665,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7706,7 +7721,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122695322</v>
+        <v>122695516</v>
       </c>
       <c r="B54" t="n">
         <v>79847</v>
@@ -7751,10 +7766,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>479771</v>
+        <v>479766</v>
       </c>
       <c r="R54" t="n">
-        <v>7027387</v>
+        <v>7027310</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7791,7 +7806,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På en lutande krokig sälg.</t>
+          <t>Växer på en lite smalare sälg intill skrovellav.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7843,10 +7858,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122695492</v>
+        <v>122695943</v>
       </c>
       <c r="B55" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7859,39 +7874,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>479770</v>
+        <v>479756</v>
       </c>
       <c r="R55" t="n">
-        <v>7027300</v>
+        <v>7027364</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7926,11 +7936,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Växer på en lite smalare sälg intill lunglav.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -7947,22 +7952,22 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7980,10 +7985,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122696876</v>
+        <v>122695602</v>
       </c>
       <c r="B56" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7996,32 +8001,27 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -8030,13 +8030,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>479628</v>
+        <v>479774</v>
       </c>
       <c r="R56" t="n">
-        <v>7027133</v>
+        <v>7027322</v>
       </c>
       <c r="S56" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen av en gran. I äldre granskog med minst medelhöga till höga livsmiljövärden för tretåig hackspett. Även gott om liggande död ved här. Finns även skalade döda granar här som indikerar potentiella födosökspår efter tretåig hackspett.</t>
+          <t>Ymnigt med lunglav på en gammal sälg med fårad bark.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8089,22 +8089,22 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -8122,10 +8122,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122697882</v>
+        <v>122697286</v>
       </c>
       <c r="B57" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -8138,37 +8138,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>479664</v>
+        <v>479663</v>
       </c>
       <c r="R57" t="n">
-        <v>7027326</v>
+        <v>7027246</v>
       </c>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -8200,11 +8205,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -8221,22 +8221,22 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8254,10 +8254,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122695655</v>
+        <v>122695273</v>
       </c>
       <c r="B58" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8270,27 +8270,32 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -8299,13 +8304,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>479759</v>
+        <v>479770</v>
       </c>
       <c r="R58" t="n">
-        <v>7027292</v>
+        <v>7027401</v>
       </c>
       <c r="S58" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8339,7 +8344,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Växer på två granar intill en sälg med ymnig påväxt av lunglav.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8368,12 +8373,12 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8391,10 +8396,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122697862</v>
+        <v>122696876</v>
       </c>
       <c r="B59" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8407,37 +8412,47 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>479630</v>
+        <v>479628</v>
       </c>
       <c r="R59" t="n">
-        <v>7027362</v>
+        <v>7027133</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8469,6 +8484,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på stambasen av en gran. I äldre granskog med minst medelhöga till höga livsmiljövärden för tretåig hackspett. Även gott om liggande död ved här. Finns även skalade döda granar här som indikerar potentiella födosökspår efter tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -8495,12 +8515,12 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8518,7 +8538,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122698232</v>
+        <v>122698085</v>
       </c>
       <c r="B60" t="n">
         <v>78766</v>
@@ -8558,10 +8578,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>479698</v>
+        <v>479659</v>
       </c>
       <c r="R60" t="n">
-        <v>7027368</v>
+        <v>7027303</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8645,10 +8665,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122695703</v>
+        <v>122696014</v>
       </c>
       <c r="B61" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8661,42 +8681,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>479753</v>
+        <v>479718</v>
       </c>
       <c r="R61" t="n">
-        <v>7027296</v>
+        <v>7027277</v>
       </c>
       <c r="S61" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8728,11 +8743,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglav på två knäckta sälgar.</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -8749,22 +8759,22 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8782,10 +8792,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122696290</v>
+        <v>122698247</v>
       </c>
       <c r="B62" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8798,48 +8808,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>479695</v>
+        <v>479696</v>
       </c>
       <c r="R62" t="n">
-        <v>7027185</v>
+        <v>7027370</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8874,11 +8870,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Observerad i flerskiktad äldre granskog.</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -8891,6 +8882,26 @@
       <c r="AH62" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8908,10 +8919,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122696426</v>
+        <v>122697455</v>
       </c>
       <c r="B63" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8924,16 +8935,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -8941,10 +8952,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -8958,13 +8973,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>479685</v>
+        <v>479680</v>
       </c>
       <c r="R63" t="n">
-        <v>7027127</v>
+        <v>7027206</v>
       </c>
       <c r="S63" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8998,7 +9013,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack/savhack.</t>
+          <t>Observation av en spillkråka som gav ifrån sig två olika lockläten. I gammal granskog med gott om asp och tall som utgör lämpliga substrat för bohål. Även bitvis relativt gott om död ved här.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -9013,26 +9028,6 @@
       <c r="AH63" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -9050,7 +9045,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122696303</v>
+        <v>122695075</v>
       </c>
       <c r="B64" t="n">
         <v>78766</v>
@@ -9090,13 +9085,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>479685</v>
+        <v>479699</v>
       </c>
       <c r="R64" t="n">
-        <v>7027165</v>
+        <v>7027521</v>
       </c>
       <c r="S64" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -9126,6 +9121,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9177,10 +9177,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122697690</v>
+        <v>122695703</v>
       </c>
       <c r="B65" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9193,37 +9193,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>479640</v>
+        <v>479753</v>
       </c>
       <c r="R65" t="n">
-        <v>7027281</v>
+        <v>7027296</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -9255,6 +9260,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglav på två knäckta sälgar.</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -9271,22 +9281,22 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9304,7 +9314,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122695075</v>
+        <v>122697862</v>
       </c>
       <c r="B66" t="n">
         <v>78766</v>
@@ -9344,10 +9354,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>479699</v>
+        <v>479630</v>
       </c>
       <c r="R66" t="n">
-        <v>7027521</v>
+        <v>7027362</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9380,11 +9390,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9436,7 +9441,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122695669</v>
+        <v>122695354</v>
       </c>
       <c r="B67" t="n">
         <v>79848</v>
@@ -9476,13 +9481,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>479761</v>
+        <v>479765</v>
       </c>
       <c r="R67" t="n">
-        <v>7027298</v>
+        <v>7027389</v>
       </c>
       <c r="S67" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -9514,6 +9519,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På en lutande krokig sälg.</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -9530,22 +9540,22 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9563,7 +9573,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122695926</v>
+        <v>122697966</v>
       </c>
       <c r="B68" t="n">
         <v>79847</v>
@@ -9608,10 +9618,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>479752</v>
+        <v>479660</v>
       </c>
       <c r="R68" t="n">
-        <v>7027344</v>
+        <v>7027363</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9646,11 +9656,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ymnigt med lunglav på en gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -9667,12 +9672,12 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM68" t="inlineStr">
@@ -9682,7 +9687,7 @@
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9700,10 +9705,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122696537</v>
+        <v>122695492</v>
       </c>
       <c r="B69" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9716,32 +9721,27 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -9750,13 +9750,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>479669</v>
+        <v>479770</v>
       </c>
       <c r="R69" t="n">
-        <v>7027116</v>
+        <v>7027300</v>
       </c>
       <c r="S69" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9790,7 +9790,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Växer på en lite smalare sälg intill lunglav.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9809,22 +9809,22 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9842,10 +9842,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122695682</v>
+        <v>122695101</v>
       </c>
       <c r="B70" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9858,39 +9858,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>479763</v>
+        <v>479696</v>
       </c>
       <c r="R70" t="n">
-        <v>7027300</v>
+        <v>7027544</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9927,7 +9922,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På en smal krokig sälg.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9946,22 +9941,22 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9979,10 +9974,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122695752</v>
+        <v>122695682</v>
       </c>
       <c r="B71" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9995,37 +9990,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>479748</v>
+        <v>479763</v>
       </c>
       <c r="R71" t="n">
-        <v>7027283</v>
+        <v>7027300</v>
       </c>
       <c r="S71" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -10057,6 +10057,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>På en smal krokig sälg.</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -10073,22 +10078,22 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -10233,10 +10238,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122697286</v>
+        <v>122698232</v>
       </c>
       <c r="B73" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -10249,39 +10254,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>479663</v>
+        <v>479698</v>
       </c>
       <c r="R73" t="n">
-        <v>7027246</v>
+        <v>7027368</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -10332,22 +10332,22 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -10365,10 +10365,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122695516</v>
+        <v>122697534</v>
       </c>
       <c r="B74" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10381,39 +10381,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>479766</v>
+        <v>479644</v>
       </c>
       <c r="R74" t="n">
-        <v>7027310</v>
+        <v>7027243</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10448,11 +10443,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Växer på en lite smalare sälg intill skrovellav.</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -10464,27 +10454,27 @@
       </c>
       <c r="AH74" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10502,10 +10492,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122697966</v>
+        <v>122695011</v>
       </c>
       <c r="B75" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10518,39 +10508,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>479660</v>
+        <v>479729</v>
       </c>
       <c r="R75" t="n">
-        <v>7027363</v>
+        <v>7027486</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10585,6 +10570,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -10601,22 +10591,22 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -10634,7 +10624,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122697773</v>
+        <v>122695655</v>
       </c>
       <c r="B76" t="n">
         <v>79847</v>
@@ -10668,19 +10658,24 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>479617</v>
+        <v>479759</v>
       </c>
       <c r="R76" t="n">
-        <v>7027326</v>
+        <v>7027292</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -10714,7 +10709,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Enstaka bålar.</t>
+          <t>Växer på två granar intill en sälg med ymnig påväxt av lunglav.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10733,22 +10728,22 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -10766,10 +10761,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122695354</v>
+        <v>122696057</v>
       </c>
       <c r="B77" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10782,34 +10777,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>479765</v>
+        <v>479675</v>
       </c>
       <c r="R77" t="n">
-        <v>7027389</v>
+        <v>7027261</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10846,7 +10846,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>På en lutande krokig sälg.</t>
+          <t>På flera aspar.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM77" t="inlineStr">
@@ -10880,7 +10880,7 @@
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10898,10 +10898,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122696014</v>
+        <v>122697773</v>
       </c>
       <c r="B78" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10914,21 +10914,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10938,10 +10938,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>479718</v>
+        <v>479617</v>
       </c>
       <c r="R78" t="n">
-        <v>7027277</v>
+        <v>7027326</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10976,6 +10976,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Enstaka bålar.</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -10992,22 +10997,22 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -11025,10 +11030,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122697455</v>
+        <v>122696426</v>
       </c>
       <c r="B79" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -11041,16 +11046,16 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -11058,14 +11063,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -11079,13 +11080,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>479680</v>
+        <v>479685</v>
       </c>
       <c r="R79" t="n">
-        <v>7027206</v>
+        <v>7027127</v>
       </c>
       <c r="S79" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -11119,7 +11120,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Observation av en spillkråka som gav ifrån sig två olika lockläten. I gammal granskog med gott om asp och tall som utgör lämpliga substrat för bohål. Även bitvis relativt gott om död ved här.</t>
+          <t>Färska och äldre ringhack/savhack.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -11134,6 +11135,26 @@
       <c r="AH79" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -11151,10 +11172,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122695273</v>
+        <v>122696521</v>
       </c>
       <c r="B80" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -11167,16 +11188,16 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -11187,7 +11208,7 @@
       <c r="I80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -11201,13 +11222,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>479770</v>
+        <v>479674</v>
       </c>
       <c r="R80" t="n">
-        <v>7027401</v>
+        <v>7027109</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -11241,7 +11262,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Färska hackspår i stambasen av en smal gran i granskog med stora mängder liggande död ved.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -11425,10 +11446,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122698275</v>
+        <v>122696537</v>
       </c>
       <c r="B82" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -11441,37 +11462,47 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>479734</v>
+        <v>479669</v>
       </c>
       <c r="R82" t="n">
-        <v>7027357</v>
+        <v>7027116</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -11505,7 +11536,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11534,12 +11565,12 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -11557,10 +11588,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122695602</v>
+        <v>122696471</v>
       </c>
       <c r="B83" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -11573,27 +11604,32 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -11602,13 +11638,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>479774</v>
+        <v>479681</v>
       </c>
       <c r="R83" t="n">
-        <v>7027322</v>
+        <v>7027123</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -11642,7 +11678,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Ymnigt med lunglav på en gammal sälg med fårad bark.</t>
+          <t>Äldre ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11661,22 +11697,22 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -11694,10 +11730,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122695101</v>
+        <v>122695926</v>
       </c>
       <c r="B84" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11710,34 +11746,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>479696</v>
+        <v>479752</v>
       </c>
       <c r="R84" t="n">
-        <v>7027544</v>
+        <v>7027344</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11774,7 +11815,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ymnigt med lunglav på en gammal sälg.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11793,22 +11834,22 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -11826,10 +11867,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122697666</v>
+        <v>122696290</v>
       </c>
       <c r="B85" t="n">
-        <v>90962</v>
+        <v>57631</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11842,36 +11883,36 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -11880,13 +11921,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>479632</v>
+        <v>479695</v>
       </c>
       <c r="R85" t="n">
-        <v>7027297</v>
+        <v>7027185</v>
       </c>
       <c r="S85" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -11918,6 +11959,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Observerad i flerskiktad äldre granskog.</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -11930,26 +11976,6 @@
       <c r="AH85" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -11967,7 +11993,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122695943</v>
+        <v>122697352</v>
       </c>
       <c r="B86" t="n">
         <v>78766</v>
@@ -12007,10 +12033,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>479756</v>
+        <v>479674</v>
       </c>
       <c r="R86" t="n">
-        <v>7027364</v>
+        <v>7027178</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -12094,10 +12120,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122696057</v>
+        <v>122697690</v>
       </c>
       <c r="B87" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -12110,39 +12136,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>479675</v>
+        <v>479640</v>
       </c>
       <c r="R87" t="n">
-        <v>7027261</v>
+        <v>7027281</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -12177,11 +12198,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>På flera aspar.</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
@@ -12198,22 +12214,22 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -12231,10 +12247,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122696471</v>
+        <v>122695669</v>
       </c>
       <c r="B88" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -12247,47 +12263,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>479681</v>
+        <v>479761</v>
       </c>
       <c r="R88" t="n">
-        <v>7027123</v>
+        <v>7027298</v>
       </c>
       <c r="S88" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -12319,11 +12325,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på stambasen.</t>
-        </is>
-      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
@@ -12350,12 +12351,12 @@
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -12373,7 +12374,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122697352</v>
+        <v>122695752</v>
       </c>
       <c r="B89" t="n">
         <v>78766</v>
@@ -12413,13 +12414,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>479674</v>
+        <v>479748</v>
       </c>
       <c r="R89" t="n">
-        <v>7027178</v>
+        <v>7027283</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -12500,10 +12501,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122698085</v>
+        <v>122697666</v>
       </c>
       <c r="B90" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -12516,37 +12517,51 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>479659</v>
+        <v>479632</v>
       </c>
       <c r="R90" t="n">
-        <v>7027303</v>
+        <v>7027297</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -12604,12 +12619,12 @@
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -12627,10 +12642,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122696521</v>
+        <v>122696303</v>
       </c>
       <c r="B91" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -12643,47 +12658,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>479674</v>
+        <v>479685</v>
       </c>
       <c r="R91" t="n">
-        <v>7027109</v>
+        <v>7027165</v>
       </c>
       <c r="S91" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -12715,11 +12720,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Färska hackspår i stambasen av en smal gran i granskog med stora mängder liggande död ved.</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
@@ -12746,12 +12746,12 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>

--- a/artfynd/A 60372-2024 artfynd.xlsx
+++ b/artfynd/A 60372-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122607124</v>
+        <v>122607879</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,47 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>479654</v>
+        <v>479622</v>
       </c>
       <c r="R2" t="n">
-        <v>7027561</v>
+        <v>7027648</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Både äldre och färska ringhack på stambasen.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,12 +784,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -817,7 +807,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122608343</v>
+        <v>122613058</v>
       </c>
       <c r="B3" t="n">
         <v>78766</v>
@@ -851,19 +841,22 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kvarnbäcken, Kvarnbäcken, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479569</v>
+        <v>479722</v>
       </c>
       <c r="R3" t="n">
-        <v>7027674</v>
+        <v>7027290</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -895,23 +888,24 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -949,7 +943,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122607162</v>
+        <v>122609281</v>
       </c>
       <c r="B4" t="n">
         <v>78766</v>
@@ -989,13 +983,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479650</v>
+        <v>479698</v>
       </c>
       <c r="R4" t="n">
-        <v>7027549</v>
+        <v>7027342</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1029,7 +1023,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1081,10 +1075,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122613032</v>
+        <v>122606280</v>
       </c>
       <c r="B5" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1097,44 +1091,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>479731</v>
+        <v>479693</v>
       </c>
       <c r="R5" t="n">
-        <v>7027291</v>
+        <v>7027399</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1168,7 +1155,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>En hel del bålar på en skadad sälg.</t>
+          <t>Skrovellav på en gammal grov sälg med 54 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1177,18 +1164,12 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1203,12 +1184,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1226,10 +1207,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122609252</v>
+        <v>122608509</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>79751</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1238,25 +1219,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1266,10 +1247,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>479714</v>
+        <v>479617</v>
       </c>
       <c r="R6" t="n">
-        <v>7027356</v>
+        <v>7027598</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1320,22 +1301,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1353,10 +1334,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122607246</v>
+        <v>122606696</v>
       </c>
       <c r="B7" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1369,48 +1350,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>479659</v>
+        <v>479678</v>
       </c>
       <c r="R7" t="n">
-        <v>7027556</v>
+        <v>7027508</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1445,11 +1412,6 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Observerades i flerskiktad granskog.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1462,6 +1424,26 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1479,7 +1461,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122608228</v>
+        <v>122607620</v>
       </c>
       <c r="B8" t="n">
         <v>78766</v>
@@ -1515,14 +1497,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kvarnbäcken, Kvarnbäcken, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>479594</v>
+        <v>479635</v>
       </c>
       <c r="R8" t="n">
-        <v>7027696</v>
+        <v>7027621</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1611,7 +1593,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122606232</v>
+        <v>122612982</v>
       </c>
       <c r="B9" t="n">
         <v>79847</v>
@@ -1645,21 +1627,23 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>479707</v>
+        <v>479738</v>
       </c>
       <c r="R9" t="n">
-        <v>7027397</v>
+        <v>7027319</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1696,7 +1680,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Fertil lunglav på en undertryck gran intill en gammal grov sälg.</t>
+          <t>Grova gamla lunglavsbålar på en lutande sälg.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1705,32 +1689,43 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>En smal lutande sälg.</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En smal lutande sälg.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1748,10 +1743,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122609424</v>
+        <v>122605930</v>
       </c>
       <c r="B10" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1764,39 +1759,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>479729</v>
+        <v>479743</v>
       </c>
       <c r="R10" t="n">
-        <v>7027353</v>
+        <v>7027472</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1833,7 +1823,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Fertila bålar på en smal böjd sälg.</t>
+          <t>Långväxta bålar på flera träd.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1852,22 +1842,22 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1885,10 +1875,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122608509</v>
+        <v>122608228</v>
       </c>
       <c r="B11" t="n">
-        <v>79751</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1897,38 +1887,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Kvarnbäcken, Kvarnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>479617</v>
+        <v>479594</v>
       </c>
       <c r="R11" t="n">
-        <v>7027598</v>
+        <v>7027696</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1963,6 +1953,11 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1979,22 +1974,22 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2012,10 +2007,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122607115</v>
+        <v>122609753</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2028,47 +2023,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>479652</v>
+        <v>479670</v>
       </c>
       <c r="R12" t="n">
-        <v>7027551</v>
+        <v>7027294</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2100,11 +2085,6 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Både färska och äldre ringhack på stambasen. I skogsbeståndet runt fyndplatsen finns medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2131,12 +2111,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2286,7 +2266,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122613090</v>
+        <v>122609468</v>
       </c>
       <c r="B14" t="n">
         <v>79847</v>
@@ -2320,26 +2300,24 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>med soral</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>479694</v>
+        <v>479731</v>
       </c>
       <c r="R14" t="n">
-        <v>7027295</v>
+        <v>7027323</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2373,7 +2351,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ett gäng "knippen" med stora lunglavsbålar på en asp.</t>
+          <t>Ymnigt med lunglav längs 7 meter på en något smalare sälg.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2382,7 +2360,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2391,19 +2368,14 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
-        </is>
-      </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -2413,7 +2385,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2431,10 +2403,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122607565</v>
+        <v>122606169</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2447,37 +2419,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>479638</v>
+        <v>479698</v>
       </c>
       <c r="R15" t="n">
-        <v>7027601</v>
+        <v>7027398</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2511,7 +2488,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>Rikligt med lunglav där vissa bålar är fertila med apothecier. På en gammal grovbarkad sälg med 54 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2525,27 +2502,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2563,7 +2540,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122606431</v>
+        <v>122607162</v>
       </c>
       <c r="B16" t="n">
         <v>78766</v>
@@ -2603,10 +2580,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>479711</v>
+        <v>479650</v>
       </c>
       <c r="R16" t="n">
-        <v>7027387</v>
+        <v>7027549</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2643,7 +2620,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2657,7 +2634,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -2695,7 +2672,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122606631</v>
+        <v>122613032</v>
       </c>
       <c r="B17" t="n">
         <v>79847</v>
@@ -2729,24 +2706,26 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>med soral</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>479711</v>
+        <v>479731</v>
       </c>
       <c r="R17" t="n">
-        <v>7027473</v>
+        <v>7027291</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2780,7 +2759,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en asp.</t>
+          <t>En hel del bålar på en skadad sälg.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2789,6 +2768,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2797,14 +2777,19 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+        </is>
+      </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -2814,7 +2799,7 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2832,7 +2817,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122609753</v>
+        <v>122607263</v>
       </c>
       <c r="B18" t="n">
         <v>78766</v>
@@ -2872,10 +2857,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>479670</v>
+        <v>479655</v>
       </c>
       <c r="R18" t="n">
-        <v>7027294</v>
+        <v>7027573</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2959,10 +2944,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122609468</v>
+        <v>122609252</v>
       </c>
       <c r="B19" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2975,39 +2960,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>479731</v>
+        <v>479714</v>
       </c>
       <c r="R19" t="n">
-        <v>7027323</v>
+        <v>7027356</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3042,11 +3022,6 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ymnigt med lunglav längs 7 meter på en något smalare sälg.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -3063,22 +3038,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3096,10 +3071,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122605930</v>
+        <v>122609386</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3112,34 +3087,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>479743</v>
+        <v>479699</v>
       </c>
       <c r="R20" t="n">
-        <v>7027472</v>
+        <v>7027340</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3176,7 +3156,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera träd.</t>
+          <t>Äldre ringhack på stambasen av en stående död gran. Volym stående död ved här som ger medelhögt till högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3205,12 +3185,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3228,10 +3208,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122606649</v>
+        <v>122607246</v>
       </c>
       <c r="B21" t="n">
-        <v>79883</v>
+        <v>57631</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3240,31 +3220,40 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3273,10 +3262,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>479715</v>
+        <v>479659</v>
       </c>
       <c r="R21" t="n">
-        <v>7027462</v>
+        <v>7027556</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3313,7 +3302,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>En samling bålar på ca 2 meters höjd på aspens stam.</t>
+          <t>Observerades i flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3328,26 +3317,6 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3365,7 +3334,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122613055</v>
+        <v>122609424</v>
       </c>
       <c r="B22" t="n">
         <v>79847</v>
@@ -3399,22 +3368,24 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>479722</v>
+        <v>479729</v>
       </c>
       <c r="R22" t="n">
-        <v>7027290</v>
+        <v>7027353</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3448,7 +3419,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Enstaka små bålar på en grov gammal asp.</t>
+          <t>Fertila bålar på en smal böjd sälg.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3457,7 +3428,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3466,19 +3436,14 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
-        </is>
-      </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
@@ -3488,7 +3453,7 @@
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3506,10 +3471,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122606280</v>
+        <v>122607115</v>
       </c>
       <c r="B23" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3522,37 +3487,47 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>479693</v>
+        <v>479652</v>
       </c>
       <c r="R23" t="n">
-        <v>7027399</v>
+        <v>7027551</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3586,7 +3561,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Skrovellav på en gammal grov sälg med 54 cm i brösthöjdsdiameter.</t>
+          <t>Både färska och äldre ringhack på stambasen. I skogsbeståndet runt fyndplatsen finns medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3600,27 +3575,27 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Branch on living tree # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3638,10 +3613,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122609837</v>
+        <v>122607124</v>
       </c>
       <c r="B24" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3654,34 +3629,44 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>479643</v>
+        <v>479654</v>
       </c>
       <c r="R24" t="n">
-        <v>7027326</v>
+        <v>7027561</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3718,7 +3703,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Både äldre och färska ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3747,12 +3732,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3770,10 +3755,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122609496</v>
+        <v>122609837</v>
       </c>
       <c r="B25" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3786,42 +3771,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>479735</v>
+        <v>479643</v>
       </c>
       <c r="R25" t="n">
-        <v>7027318</v>
+        <v>7027326</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3851,6 +3831,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3902,10 +3887,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122612982</v>
+        <v>122606649</v>
       </c>
       <c r="B26" t="n">
-        <v>79847</v>
+        <v>79883</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3914,45 +3899,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>479738</v>
+        <v>479715</v>
       </c>
       <c r="R26" t="n">
-        <v>7027319</v>
+        <v>7027462</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3989,7 +3972,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Grova gamla lunglavsbålar på en lutande sälg.</t>
+          <t>En samling bålar på ca 2 meters höjd på aspens stam.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3998,7 +3981,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -4007,24 +3989,14 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
-        </is>
-      </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL26" t="inlineStr">
-        <is>
-          <t>En smal lutande sälg.</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
@@ -4034,7 +4006,7 @@
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En smal lutande sälg.</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4052,10 +4024,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122606696</v>
+        <v>122613090</v>
       </c>
       <c r="B27" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4068,37 +4040,44 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>479678</v>
+        <v>479694</v>
       </c>
       <c r="R27" t="n">
-        <v>7027508</v>
+        <v>7027295</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4130,12 +4109,18 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ett gäng "knippen" med stora lunglavsbålar på en asp.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -4144,24 +4129,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+        </is>
+      </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4179,10 +4169,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122606868</v>
+        <v>122609496</v>
       </c>
       <c r="B28" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4195,37 +4185,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>479661</v>
+        <v>479735</v>
       </c>
       <c r="R28" t="n">
-        <v>7027516</v>
+        <v>7027318</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4268,7 +4263,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -4306,10 +4301,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122608462</v>
+        <v>122606431</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4322,47 +4317,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kvarnbäcken, Kvarnbäcken, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>479583</v>
+        <v>479711</v>
       </c>
       <c r="R29" t="n">
-        <v>7027629</v>
+        <v>7027387</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4396,7 +4381,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Äldre ringhack som bedöms vara 5-10 år gamla. På en gran med tydliga kådaflöden. Hyfsat gott om död ved här.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4410,7 +4395,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4425,12 +4410,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4448,7 +4433,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122606334</v>
+        <v>122607565</v>
       </c>
       <c r="B30" t="n">
         <v>78766</v>
@@ -4488,10 +4473,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>479692</v>
+        <v>479638</v>
       </c>
       <c r="R30" t="n">
-        <v>7027424</v>
+        <v>7027601</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4526,6 +4511,11 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flera granar.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4537,7 +4527,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4575,10 +4565,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122607263</v>
+        <v>122606273</v>
       </c>
       <c r="B31" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4591,37 +4581,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>479655</v>
+        <v>479698</v>
       </c>
       <c r="R31" t="n">
-        <v>7027573</v>
+        <v>7027398</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4653,6 +4648,11 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Skrovellav på en undertryck gran intill en gammal grov sälg.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4664,7 +4664,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -4702,10 +4702,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122609386</v>
+        <v>122613066</v>
       </c>
       <c r="B32" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4718,42 +4718,44 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>479699</v>
+        <v>479702</v>
       </c>
       <c r="R32" t="n">
-        <v>7027340</v>
+        <v>7027288</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4787,7 +4789,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen av en stående död gran. Volym stående död ved här som ger medelhögt till högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Lunglav på en grovbarkad asp.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4796,6 +4798,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4804,24 +4807,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+        </is>
+      </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Populus tremula</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4839,7 +4847,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122613066</v>
+        <v>122606631</v>
       </c>
       <c r="B33" t="n">
         <v>79847</v>
@@ -4873,26 +4881,24 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
           <t>med soral</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>479702</v>
+        <v>479711</v>
       </c>
       <c r="R33" t="n">
-        <v>7027288</v>
+        <v>7027473</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4926,7 +4932,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Lunglav på en grovbarkad asp.</t>
+          <t>Enstaka bålar på en asp.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4935,7 +4941,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4944,11 +4949,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
-        </is>
-      </c>
       <c r="AJ33" t="inlineStr">
         <is>
           <t>asp</t>
@@ -4966,7 +4966,7 @@
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Populus tremula</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4984,10 +4984,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122606273</v>
+        <v>122606232</v>
       </c>
       <c r="B34" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5000,27 +5000,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -5029,13 +5029,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>479698</v>
+        <v>479707</v>
       </c>
       <c r="R34" t="n">
-        <v>7027398</v>
+        <v>7027397</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5069,7 +5069,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Skrovellav på en undertryck gran intill en gammal grov sälg.</t>
+          <t>Fertil lunglav på en undertryck gran intill en gammal grov sälg.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5121,7 +5121,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122613058</v>
+        <v>122606868</v>
       </c>
       <c r="B35" t="n">
         <v>78766</v>
@@ -5155,22 +5155,19 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>479722</v>
+        <v>479661</v>
       </c>
       <c r="R35" t="n">
-        <v>7027290</v>
+        <v>7027516</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5208,18 +5205,12 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -5257,7 +5248,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122606169</v>
+        <v>122613055</v>
       </c>
       <c r="B36" t="n">
         <v>79847</v>
@@ -5291,24 +5282,22 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>479698</v>
+        <v>479722</v>
       </c>
       <c r="R36" t="n">
-        <v>7027398</v>
+        <v>7027290</v>
       </c>
       <c r="S36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5342,7 +5331,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav där vissa bålar är fertila med apothecier. På en gammal grovbarkad sälg med 54 cm i brösthöjdsdiameter.</t>
+          <t>Enstaka små bålar på en grov gammal asp.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5351,22 +5340,28 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
@@ -5376,7 +5371,7 @@
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Grov bark. # Populus tremula</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5394,7 +5389,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122609281</v>
+        <v>122608343</v>
       </c>
       <c r="B37" t="n">
         <v>78766</v>
@@ -5430,17 +5425,17 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Kvarnbäcken, Kvarnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>479698</v>
+        <v>479569</v>
       </c>
       <c r="R37" t="n">
-        <v>7027342</v>
+        <v>7027674</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5474,7 +5469,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5526,7 +5521,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122607879</v>
+        <v>122606334</v>
       </c>
       <c r="B38" t="n">
         <v>78766</v>
@@ -5566,13 +5561,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>479622</v>
+        <v>479692</v>
       </c>
       <c r="R38" t="n">
-        <v>7027648</v>
+        <v>7027424</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5604,11 +5599,6 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5620,7 +5610,7 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
@@ -5658,10 +5648,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122607620</v>
+        <v>122608462</v>
       </c>
       <c r="B39" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5674,37 +5664,47 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Kvarnbäcken, Kvarnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>479635</v>
+        <v>479583</v>
       </c>
       <c r="R39" t="n">
-        <v>7027621</v>
+        <v>7027629</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre ringhack som bedöms vara 5-10 år gamla. På en gran med tydliga kådaflöden. Hyfsat gott om död ved här.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5790,7 +5790,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122609073</v>
+        <v>122613271</v>
       </c>
       <c r="B40" t="n">
         <v>79847</v>
@@ -5824,24 +5824,26 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>479738</v>
+        <v>479628</v>
       </c>
       <c r="R40" t="n">
-        <v>7027404</v>
+        <v>7027338</v>
       </c>
       <c r="S40" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5875,7 +5877,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På en smal sälg.</t>
+          <t>Riklig påväxt av lunglavsbålar på en gammal sälg. Vissa bålar är fertila med apothecier. Här växer även rikligt med lunglav på gran.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5884,6 +5886,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5892,6 +5895,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+        </is>
+      </c>
       <c r="AJ40" t="inlineStr">
         <is>
           <t>sälg</t>
@@ -5902,6 +5910,11 @@
           <t>Salix caprea</t>
         </is>
       </c>
+      <c r="AL40" t="inlineStr">
+        <is>
+          <t>En gammal grov sälg.</t>
+        </is>
+      </c>
       <c r="AM40" t="inlineStr">
         <is>
           <t>Bark på levande träd</t>
@@ -5909,7 +5922,7 @@
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea # En gammal grov sälg.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5927,10 +5940,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122613280</v>
+        <v>122609140</v>
       </c>
       <c r="B41" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5943,44 +5956,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>479628</v>
+        <v>479723</v>
       </c>
       <c r="R41" t="n">
-        <v>7027338</v>
+        <v>7027396</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -6014,7 +6025,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På renar av gran blandat med lunglav.</t>
+          <t>Ymnig påväxt av lunglav längs flera meter på en gammal sälg. Fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6023,7 +6034,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -6032,29 +6042,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
-        </is>
-      </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6072,10 +6077,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122607746</v>
+        <v>122609073</v>
       </c>
       <c r="B42" t="n">
-        <v>79751</v>
+        <v>79847</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6084,48 +6089,46 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>479627</v>
+        <v>479738</v>
       </c>
       <c r="R42" t="n">
-        <v>7027656</v>
+        <v>7027404</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6159,7 +6162,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Skinnlav på asp där flertalet bålar är fertila med apothecier.</t>
+          <t>På en smal sälg.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6168,7 +6171,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -6177,19 +6179,14 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>Flerskiktad kontinuitetsskog dominerad av gran och med återkommande inslag av asp.</t>
-        </is>
-      </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
@@ -6199,7 +6196,7 @@
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6217,10 +6214,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122613145</v>
+        <v>122607364</v>
       </c>
       <c r="B43" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6233,41 +6230,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>479634</v>
+        <v>479644</v>
       </c>
       <c r="R43" t="n">
-        <v>7027302</v>
+        <v>7027599</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6304,7 +6299,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ymnig påväxt av lunglav längs flera meter på en sälgstam. Vissa bålar är fertila med apothecier.</t>
+          <t>Både färska och äldre ringhack på stambasen. I skogsbeståndet runt fyndplatsen finns medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6313,7 +6308,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -6322,34 +6316,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
-        </is>
-      </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL43" t="inlineStr">
-        <is>
-          <t>En svagt lutande sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En svagt lutande sälg.</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6367,10 +6351,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122608974</v>
+        <v>122613281</v>
       </c>
       <c r="B44" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6383,42 +6367,40 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>479682</v>
+        <v>479628</v>
       </c>
       <c r="R44" t="n">
-        <v>7027484</v>
+        <v>7027338</v>
       </c>
       <c r="S44" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6450,12 +6432,18 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Med långväxta bålar och på flera granar.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6464,24 +6452,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+        </is>
+      </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6499,7 +6492,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122613271</v>
+        <v>122613145</v>
       </c>
       <c r="B45" t="n">
         <v>79847</v>
@@ -6546,13 +6539,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>479628</v>
+        <v>479634</v>
       </c>
       <c r="R45" t="n">
-        <v>7027338</v>
+        <v>7027302</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6586,7 +6579,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Riklig påväxt av lunglavsbålar på en gammal sälg. Vissa bålar är fertila med apothecier. Här växer även rikligt med lunglav på gran.</t>
+          <t>Ymnig påväxt av lunglav längs flera meter på en sälgstam. Vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6621,7 +6614,7 @@
       </c>
       <c r="AL45" t="inlineStr">
         <is>
-          <t>En gammal grov sälg.</t>
+          <t>En svagt lutande sälg.</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
@@ -6631,7 +6624,7 @@
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea # En gammal grov sälg.</t>
+          <t>Bark on living woody plant # Salix caprea # En svagt lutande sälg.</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6649,10 +6642,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122613281</v>
+        <v>122608974</v>
       </c>
       <c r="B46" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6665,40 +6658,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>479628</v>
+        <v>479682</v>
       </c>
       <c r="R46" t="n">
-        <v>7027338</v>
+        <v>7027484</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6730,18 +6725,12 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Med långväxta bålar och på flera granar.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6750,29 +6739,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
-        </is>
-      </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6790,10 +6774,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122609714</v>
+        <v>122613280</v>
       </c>
       <c r="B47" t="n">
-        <v>57631</v>
+        <v>79848</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6806,49 +6790,44 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>479677</v>
+        <v>479628</v>
       </c>
       <c r="R47" t="n">
-        <v>7027303</v>
+        <v>7027338</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6882,7 +6861,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Observation i flerskiktad granskog med stående murkna björkhögstubbar som är gynnsamt för talltitans häckning.</t>
+          <t>På renar av gran blandat med lunglav.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6891,6 +6870,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6902,6 +6882,26 @@
       <c r="AI47" t="inlineStr">
         <is>
           <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6919,10 +6919,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122609140</v>
+        <v>122607746</v>
       </c>
       <c r="B48" t="n">
-        <v>79847</v>
+        <v>79751</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6931,43 +6931,45 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
           <t>med apothecier</t>
         </is>
       </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>479723</v>
+        <v>479627</v>
       </c>
       <c r="R48" t="n">
-        <v>7027396</v>
+        <v>7027656</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -7004,7 +7006,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ymnig påväxt av lunglav längs flera meter på en gammal sälg. Fertila bålar med apothecier.</t>
+          <t>Skinnlav på asp där flertalet bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7013,6 +7015,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -7021,14 +7024,19 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Flerskiktad kontinuitetsskog dominerad av gran och med återkommande inslag av asp.</t>
+        </is>
+      </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
@@ -7038,7 +7046,7 @@
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -7056,10 +7064,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122608090</v>
+        <v>122609714</v>
       </c>
       <c r="B49" t="n">
-        <v>79751</v>
+        <v>57631</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -7068,41 +7076,53 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6456</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>479602</v>
+        <v>479677</v>
       </c>
       <c r="R49" t="n">
-        <v>7027640</v>
+        <v>7027303</v>
       </c>
       <c r="S49" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -7134,6 +7154,11 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Observation i flerskiktad granskog med stående murkna björkhögstubbar som är gynnsamt för talltitans häckning.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -7148,24 +7173,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7183,10 +7193,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122607364</v>
+        <v>122608090</v>
       </c>
       <c r="B50" t="n">
-        <v>57478</v>
+        <v>79751</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7195,46 +7205,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>479644</v>
+        <v>479602</v>
       </c>
       <c r="R50" t="n">
-        <v>7027599</v>
+        <v>7027640</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7266,11 +7271,6 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Både färska och äldre ringhack på stambasen. I skogsbeståndet runt fyndplatsen finns medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -7287,22 +7287,22 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7320,7 +7320,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122697882</v>
+        <v>122695943</v>
       </c>
       <c r="B51" t="n">
         <v>78766</v>
@@ -7360,13 +7360,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>479664</v>
+        <v>479756</v>
       </c>
       <c r="R51" t="n">
-        <v>7027326</v>
+        <v>7027364</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7396,11 +7396,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7589,10 +7584,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122698275</v>
+        <v>122697757</v>
       </c>
       <c r="B53" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7605,34 +7600,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>479734</v>
+        <v>479615</v>
       </c>
       <c r="R53" t="n">
-        <v>7027357</v>
+        <v>7027315</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7667,11 +7667,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -7688,22 +7683,22 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7721,10 +7716,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122695516</v>
+        <v>122697352</v>
       </c>
       <c r="B54" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7737,39 +7732,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>479766</v>
+        <v>479674</v>
       </c>
       <c r="R54" t="n">
-        <v>7027310</v>
+        <v>7027178</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7804,11 +7794,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Växer på en lite smalare sälg intill skrovellav.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -7825,22 +7810,22 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7858,10 +7843,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122695943</v>
+        <v>122695669</v>
       </c>
       <c r="B55" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7874,21 +7859,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7898,13 +7883,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>479756</v>
+        <v>479761</v>
       </c>
       <c r="R55" t="n">
-        <v>7027364</v>
+        <v>7027298</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7985,10 +7970,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122695602</v>
+        <v>122697455</v>
       </c>
       <c r="B56" t="n">
-        <v>79847</v>
+        <v>57494</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -8001,27 +7986,36 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>med soral</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -8030,13 +8024,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>479774</v>
+        <v>479680</v>
       </c>
       <c r="R56" t="n">
-        <v>7027322</v>
+        <v>7027206</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -8070,7 +8064,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ymnigt med lunglav på en gammal sälg med fårad bark.</t>
+          <t>Observation av en spillkråka som gav ifrån sig två olika lockläten. I gammal granskog med gott om asp och tall som utgör lämpliga substrat för bohål. Även bitvis relativt gott om död ved här.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8085,26 +8079,6 @@
       <c r="AH56" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -8122,7 +8096,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122697286</v>
+        <v>122697773</v>
       </c>
       <c r="B57" t="n">
         <v>79847</v>
@@ -8156,21 +8130,16 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>479663</v>
+        <v>479617</v>
       </c>
       <c r="R57" t="n">
-        <v>7027246</v>
+        <v>7027326</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -8205,6 +8174,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Enstaka bålar.</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -8221,12 +8195,12 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
@@ -8236,7 +8210,7 @@
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8254,10 +8228,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122695273</v>
+        <v>122695011</v>
       </c>
       <c r="B58" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8270,44 +8244,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>479770</v>
+        <v>479729</v>
       </c>
       <c r="R58" t="n">
-        <v>7027401</v>
+        <v>7027486</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8344,7 +8308,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8373,12 +8337,12 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8396,10 +8360,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122696876</v>
+        <v>122695682</v>
       </c>
       <c r="B59" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8412,32 +8376,27 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -8446,13 +8405,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>479628</v>
+        <v>479763</v>
       </c>
       <c r="R59" t="n">
-        <v>7027133</v>
+        <v>7027300</v>
       </c>
       <c r="S59" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8486,7 +8445,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen av en gran. I äldre granskog med minst medelhöga till höga livsmiljövärden för tretåig hackspett. Även gott om liggande död ved här. Finns även skalade döda granar här som indikerar potentiella födosökspår efter tretåig hackspett.</t>
+          <t>På en smal krokig sälg.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8505,22 +8464,22 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8538,7 +8497,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122698085</v>
+        <v>122698247</v>
       </c>
       <c r="B60" t="n">
         <v>78766</v>
@@ -8578,10 +8537,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>479659</v>
+        <v>479696</v>
       </c>
       <c r="R60" t="n">
-        <v>7027303</v>
+        <v>7027370</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8665,10 +8624,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122696014</v>
+        <v>122695602</v>
       </c>
       <c r="B61" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8681,34 +8640,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>479718</v>
+        <v>479774</v>
       </c>
       <c r="R61" t="n">
-        <v>7027277</v>
+        <v>7027322</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8743,6 +8707,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ymnigt med lunglav på en gammal sälg med fårad bark.</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -8759,22 +8728,22 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8792,10 +8761,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122698247</v>
+        <v>122696471</v>
       </c>
       <c r="B62" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8808,37 +8777,47 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>479696</v>
+        <v>479681</v>
       </c>
       <c r="R62" t="n">
-        <v>7027370</v>
+        <v>7027123</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8870,6 +8849,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på stambasen.</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -8896,12 +8880,12 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8919,10 +8903,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122697455</v>
+        <v>122696290</v>
       </c>
       <c r="B63" t="n">
-        <v>57494</v>
+        <v>57631</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8935,21 +8919,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -8959,7 +8943,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -8973,13 +8957,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>479680</v>
+        <v>479695</v>
       </c>
       <c r="R63" t="n">
-        <v>7027206</v>
+        <v>7027185</v>
       </c>
       <c r="S63" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -9013,7 +8997,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Observation av en spillkråka som gav ifrån sig två olika lockläten. I gammal granskog med gott om asp och tall som utgör lämpliga substrat för bohål. Även bitvis relativt gott om död ved här.</t>
+          <t>Observerad i flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -9177,7 +9161,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122695703</v>
+        <v>122696057</v>
       </c>
       <c r="B65" t="n">
         <v>79847</v>
@@ -9222,13 +9206,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>479753</v>
+        <v>479675</v>
       </c>
       <c r="R65" t="n">
-        <v>7027296</v>
+        <v>7027261</v>
       </c>
       <c r="S65" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -9262,7 +9246,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på två knäckta sälgar.</t>
+          <t>På flera aspar.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9281,12 +9265,12 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM65" t="inlineStr">
@@ -9296,7 +9280,7 @@
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9314,10 +9298,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122697862</v>
+        <v>122695926</v>
       </c>
       <c r="B66" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9330,34 +9314,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>479630</v>
+        <v>479752</v>
       </c>
       <c r="R66" t="n">
-        <v>7027362</v>
+        <v>7027344</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9392,6 +9381,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ymnigt med lunglav på en gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -9408,22 +9402,22 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9441,10 +9435,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122695354</v>
+        <v>122696426</v>
       </c>
       <c r="B67" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9457,37 +9451,47 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>479765</v>
+        <v>479685</v>
       </c>
       <c r="R67" t="n">
-        <v>7027389</v>
+        <v>7027127</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -9521,7 +9525,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>På en lutande krokig sälg.</t>
+          <t>Färska och äldre ringhack/savhack.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9540,22 +9544,22 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9573,10 +9577,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122697966</v>
+        <v>122695492</v>
       </c>
       <c r="B68" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9589,21 +9593,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -9618,10 +9622,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>479660</v>
+        <v>479770</v>
       </c>
       <c r="R68" t="n">
-        <v>7027363</v>
+        <v>7027300</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9656,6 +9660,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Växer på en lite smalare sälg intill lunglav.</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -9672,12 +9681,12 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM68" t="inlineStr">
@@ -9687,7 +9696,7 @@
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9705,10 +9714,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122695492</v>
+        <v>122698085</v>
       </c>
       <c r="B69" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9721,39 +9730,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>479770</v>
+        <v>479659</v>
       </c>
       <c r="R69" t="n">
-        <v>7027300</v>
+        <v>7027303</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9788,11 +9792,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Växer på en lite smalare sälg intill lunglav.</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -9809,22 +9808,22 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9842,7 +9841,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122695101</v>
+        <v>122696111</v>
       </c>
       <c r="B70" t="n">
         <v>78766</v>
@@ -9882,10 +9881,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>479696</v>
+        <v>479694</v>
       </c>
       <c r="R70" t="n">
-        <v>7027544</v>
+        <v>7027236</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9918,11 +9917,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9974,10 +9968,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122695682</v>
+        <v>122697882</v>
       </c>
       <c r="B71" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9990,42 +9984,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>479763</v>
+        <v>479664</v>
       </c>
       <c r="R71" t="n">
-        <v>7027300</v>
+        <v>7027326</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -10059,7 +10048,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På en smal krokig sälg.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -10078,22 +10067,22 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -10111,10 +10100,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122696111</v>
+        <v>122697286</v>
       </c>
       <c r="B72" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -10127,34 +10116,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>479694</v>
+        <v>479663</v>
       </c>
       <c r="R72" t="n">
-        <v>7027236</v>
+        <v>7027246</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -10205,22 +10199,22 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -10238,7 +10232,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122698232</v>
+        <v>122698275</v>
       </c>
       <c r="B73" t="n">
         <v>78766</v>
@@ -10278,10 +10272,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>479698</v>
+        <v>479734</v>
       </c>
       <c r="R73" t="n">
-        <v>7027368</v>
+        <v>7027357</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -10314,6 +10308,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10365,7 +10364,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122697534</v>
+        <v>122697862</v>
       </c>
       <c r="B74" t="n">
         <v>78766</v>
@@ -10405,10 +10404,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>479644</v>
+        <v>479630</v>
       </c>
       <c r="R74" t="n">
-        <v>7027243</v>
+        <v>7027362</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10454,7 +10453,7 @@
       </c>
       <c r="AH74" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ74" t="inlineStr">
@@ -10492,10 +10491,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122695011</v>
+        <v>122696876</v>
       </c>
       <c r="B75" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10508,37 +10507,47 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>479729</v>
+        <v>479628</v>
       </c>
       <c r="R75" t="n">
-        <v>7027486</v>
+        <v>7027133</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -10572,7 +10581,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Färska och äldre ringhack på stambasen av en gran. I äldre granskog med minst medelhöga till höga livsmiljövärden för tretåig hackspett. Även gott om liggande död ved här. Finns även skalade döda granar här som indikerar potentiella födosökspår efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10601,12 +10610,12 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -10624,10 +10633,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122695655</v>
+        <v>122697666</v>
       </c>
       <c r="B76" t="n">
-        <v>79847</v>
+        <v>90962</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10640,27 +10649,36 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -10669,13 +10687,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>479759</v>
+        <v>479632</v>
       </c>
       <c r="R76" t="n">
-        <v>7027292</v>
+        <v>7027297</v>
       </c>
       <c r="S76" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -10707,11 +10725,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Växer på två granar intill en sälg med ymnig påväxt av lunglav.</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -10738,12 +10751,12 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -10761,10 +10774,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122696057</v>
+        <v>122695752</v>
       </c>
       <c r="B77" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10777,42 +10790,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>479675</v>
+        <v>479748</v>
       </c>
       <c r="R77" t="n">
-        <v>7027261</v>
+        <v>7027283</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -10844,11 +10852,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>På flera aspar.</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -10865,22 +10868,22 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10898,10 +10901,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122697773</v>
+        <v>122695354</v>
       </c>
       <c r="B78" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10914,21 +10917,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10938,10 +10941,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>479617</v>
+        <v>479765</v>
       </c>
       <c r="R78" t="n">
-        <v>7027326</v>
+        <v>7027389</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10978,7 +10981,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Enstaka bålar.</t>
+          <t>På en lutande krokig sälg.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -11030,10 +11033,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122696426</v>
+        <v>122695655</v>
       </c>
       <c r="B79" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -11046,32 +11049,27 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -11080,13 +11078,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>479685</v>
+        <v>479759</v>
       </c>
       <c r="R79" t="n">
-        <v>7027127</v>
+        <v>7027292</v>
       </c>
       <c r="S79" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -11120,7 +11118,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack/savhack.</t>
+          <t>Växer på två granar intill en sälg med ymnig påväxt av lunglav.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -11149,12 +11147,12 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -11172,10 +11170,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122696521</v>
+        <v>122697690</v>
       </c>
       <c r="B80" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -11188,47 +11186,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>479674</v>
+        <v>479640</v>
       </c>
       <c r="R80" t="n">
-        <v>7027109</v>
+        <v>7027281</v>
       </c>
       <c r="S80" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -11260,11 +11248,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Färska hackspår i stambasen av en smal gran i granskog med stora mängder liggande död ved.</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -11291,12 +11274,12 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -11314,10 +11297,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122697757</v>
+        <v>122696014</v>
       </c>
       <c r="B81" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -11330,39 +11313,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>479615</v>
+        <v>479718</v>
       </c>
       <c r="R81" t="n">
-        <v>7027315</v>
+        <v>7027277</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -11413,22 +11391,22 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -11588,10 +11566,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122696471</v>
+        <v>122698232</v>
       </c>
       <c r="B83" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -11604,47 +11582,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>479681</v>
+        <v>479698</v>
       </c>
       <c r="R83" t="n">
-        <v>7027123</v>
+        <v>7027368</v>
       </c>
       <c r="S83" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -11676,11 +11644,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på stambasen.</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -11707,12 +11670,12 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -11730,7 +11693,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122695926</v>
+        <v>122695703</v>
       </c>
       <c r="B84" t="n">
         <v>79847</v>
@@ -11775,13 +11738,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>479752</v>
+        <v>479753</v>
       </c>
       <c r="R84" t="n">
-        <v>7027344</v>
+        <v>7027296</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -11815,7 +11778,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Ymnigt med lunglav på en gammal sälg.</t>
+          <t>Rikligt med lunglav på två knäckta sälgar.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11867,10 +11830,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122696290</v>
+        <v>122695273</v>
       </c>
       <c r="B85" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11883,31 +11846,27 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -11921,10 +11880,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>479695</v>
+        <v>479770</v>
       </c>
       <c r="R85" t="n">
-        <v>7027185</v>
+        <v>7027401</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11961,7 +11920,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Observerad i flerskiktad äldre granskog.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11976,6 +11935,26 @@
       <c r="AH85" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -11993,7 +11972,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122697352</v>
+        <v>122695101</v>
       </c>
       <c r="B86" t="n">
         <v>78766</v>
@@ -12033,10 +12012,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>479674</v>
+        <v>479696</v>
       </c>
       <c r="R86" t="n">
-        <v>7027178</v>
+        <v>7027544</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -12069,6 +12048,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -12120,10 +12104,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122697690</v>
+        <v>122697966</v>
       </c>
       <c r="B87" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -12136,34 +12120,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>479640</v>
+        <v>479660</v>
       </c>
       <c r="R87" t="n">
-        <v>7027281</v>
+        <v>7027363</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -12214,22 +12203,22 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -12247,10 +12236,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122695669</v>
+        <v>122697534</v>
       </c>
       <c r="B88" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -12263,21 +12252,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -12287,13 +12276,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>479761</v>
+        <v>479644</v>
       </c>
       <c r="R88" t="n">
-        <v>7027298</v>
+        <v>7027243</v>
       </c>
       <c r="S88" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -12336,7 +12325,7 @@
       </c>
       <c r="AH88" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ88" t="inlineStr">
@@ -12374,7 +12363,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122695752</v>
+        <v>122696303</v>
       </c>
       <c r="B89" t="n">
         <v>78766</v>
@@ -12414,10 +12403,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>479748</v>
+        <v>479685</v>
       </c>
       <c r="R89" t="n">
-        <v>7027283</v>
+        <v>7027165</v>
       </c>
       <c r="S89" t="n">
         <v>12</v>
@@ -12501,10 +12490,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122697666</v>
+        <v>122696521</v>
       </c>
       <c r="B90" t="n">
-        <v>90962</v>
+        <v>57494</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -12517,36 +12506,32 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -12555,13 +12540,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>479632</v>
+        <v>479674</v>
       </c>
       <c r="R90" t="n">
-        <v>7027297</v>
+        <v>7027109</v>
       </c>
       <c r="S90" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -12593,6 +12578,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Färska hackspår i stambasen av en smal gran i granskog med stora mängder liggande död ved.</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
@@ -12619,12 +12609,12 @@
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -12642,10 +12632,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122696303</v>
+        <v>122695516</v>
       </c>
       <c r="B91" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -12658,37 +12648,42 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>479685</v>
+        <v>479766</v>
       </c>
       <c r="R91" t="n">
-        <v>7027165</v>
+        <v>7027310</v>
       </c>
       <c r="S91" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -12720,6 +12715,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Växer på en lite smalare sälg intill skrovellav.</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
@@ -12736,22 +12736,22 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>

--- a/artfynd/A 60372-2024 artfynd.xlsx
+++ b/artfynd/A 60372-2024 artfynd.xlsx
@@ -3471,7 +3471,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122607115</v>
+        <v>122607124</v>
       </c>
       <c r="B23" t="n">
         <v>57478</v>
@@ -3507,7 +3507,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3521,13 +3521,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>479652</v>
+        <v>479654</v>
       </c>
       <c r="R23" t="n">
-        <v>7027551</v>
+        <v>7027561</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Både färska och äldre ringhack på stambasen. I skogsbeståndet runt fyndplatsen finns medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Både äldre och färska ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3613,10 +3613,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122607124</v>
+        <v>122609837</v>
       </c>
       <c r="B24" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3629,44 +3629,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>479654</v>
+        <v>479643</v>
       </c>
       <c r="R24" t="n">
-        <v>7027561</v>
+        <v>7027326</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3703,7 +3693,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Både äldre och färska ringhack på stambasen.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3732,12 +3722,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3755,10 +3745,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122609837</v>
+        <v>122607115</v>
       </c>
       <c r="B25" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3771,37 +3761,47 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>479643</v>
+        <v>479652</v>
       </c>
       <c r="R25" t="n">
-        <v>7027326</v>
+        <v>7027551</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Både färska och äldre ringhack på stambasen. I skogsbeståndet runt fyndplatsen finns medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3887,10 +3887,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122606649</v>
+        <v>122606431</v>
       </c>
       <c r="B26" t="n">
-        <v>79883</v>
+        <v>78766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3899,43 +3899,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>479715</v>
+        <v>479711</v>
       </c>
       <c r="R26" t="n">
-        <v>7027462</v>
+        <v>7027387</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3972,7 +3967,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>En samling bålar på ca 2 meters höjd på aspens stam.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3986,27 +3981,27 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4024,10 +4019,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122613090</v>
+        <v>122606649</v>
       </c>
       <c r="B27" t="n">
-        <v>79847</v>
+        <v>79883</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4036,48 +4031,46 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>479694</v>
+        <v>479715</v>
       </c>
       <c r="R27" t="n">
-        <v>7027295</v>
+        <v>7027462</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4111,7 +4104,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ett gäng "knippen" med stora lunglavsbålar på en asp.</t>
+          <t>En samling bålar på ca 2 meters höjd på aspens stam.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4120,18 +4113,12 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -4169,7 +4156,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122609496</v>
+        <v>122613090</v>
       </c>
       <c r="B28" t="n">
         <v>79847</v>
@@ -4203,24 +4190,26 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>med soral</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>479735</v>
+        <v>479694</v>
       </c>
       <c r="R28" t="n">
-        <v>7027318</v>
+        <v>7027295</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4252,12 +4241,18 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ett gäng "knippen" med stora lunglavsbålar på en asp.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4266,24 +4261,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+        </is>
+      </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4301,10 +4301,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122606431</v>
+        <v>122609496</v>
       </c>
       <c r="B29" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4317,37 +4317,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>479711</v>
+        <v>479735</v>
       </c>
       <c r="R29" t="n">
-        <v>7027387</v>
+        <v>7027318</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4379,11 +4384,6 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4395,7 +4395,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -8624,10 +8624,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122695602</v>
+        <v>122696471</v>
       </c>
       <c r="B61" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8640,27 +8640,32 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -8669,13 +8674,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>479774</v>
+        <v>479681</v>
       </c>
       <c r="R61" t="n">
-        <v>7027322</v>
+        <v>7027123</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8709,7 +8714,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ymnigt med lunglav på en gammal sälg med fårad bark.</t>
+          <t>Äldre ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8728,22 +8733,22 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8761,10 +8766,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122696471</v>
+        <v>122695602</v>
       </c>
       <c r="B62" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8777,32 +8782,27 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -8811,13 +8811,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>479681</v>
+        <v>479774</v>
       </c>
       <c r="R62" t="n">
-        <v>7027123</v>
+        <v>7027322</v>
       </c>
       <c r="S62" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen.</t>
+          <t>Ymnigt med lunglav på en gammal sälg med fårad bark.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8870,22 +8870,22 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -9435,10 +9435,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122696426</v>
+        <v>122695492</v>
       </c>
       <c r="B67" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9451,32 +9451,27 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -9485,13 +9480,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>479685</v>
+        <v>479770</v>
       </c>
       <c r="R67" t="n">
-        <v>7027127</v>
+        <v>7027300</v>
       </c>
       <c r="S67" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -9525,7 +9520,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack/savhack.</t>
+          <t>Växer på en lite smalare sälg intill lunglav.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9544,22 +9539,22 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9577,10 +9572,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122695492</v>
+        <v>122698085</v>
       </c>
       <c r="B68" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9593,39 +9588,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>479770</v>
+        <v>479659</v>
       </c>
       <c r="R68" t="n">
-        <v>7027300</v>
+        <v>7027303</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9660,11 +9650,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Växer på en lite smalare sälg intill lunglav.</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -9681,22 +9666,22 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9714,7 +9699,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122698085</v>
+        <v>122696111</v>
       </c>
       <c r="B69" t="n">
         <v>78766</v>
@@ -9754,10 +9739,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>479659</v>
+        <v>479694</v>
       </c>
       <c r="R69" t="n">
-        <v>7027303</v>
+        <v>7027236</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9841,7 +9826,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122696111</v>
+        <v>122697882</v>
       </c>
       <c r="B70" t="n">
         <v>78766</v>
@@ -9881,13 +9866,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>479694</v>
+        <v>479664</v>
       </c>
       <c r="R70" t="n">
-        <v>7027236</v>
+        <v>7027326</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9917,6 +9902,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9968,10 +9958,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122697882</v>
+        <v>122697286</v>
       </c>
       <c r="B71" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9984,37 +9974,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>479664</v>
+        <v>479663</v>
       </c>
       <c r="R71" t="n">
-        <v>7027326</v>
+        <v>7027246</v>
       </c>
       <c r="S71" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -10046,11 +10041,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -10067,22 +10057,22 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -10100,10 +10090,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122697286</v>
+        <v>122698275</v>
       </c>
       <c r="B72" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -10116,39 +10106,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>479663</v>
+        <v>479734</v>
       </c>
       <c r="R72" t="n">
-        <v>7027246</v>
+        <v>7027357</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -10183,6 +10168,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -10199,22 +10189,22 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -10232,10 +10222,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122698275</v>
+        <v>122696876</v>
       </c>
       <c r="B73" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -10248,37 +10238,47 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>479734</v>
+        <v>479628</v>
       </c>
       <c r="R73" t="n">
-        <v>7027357</v>
+        <v>7027133</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -10312,7 +10312,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Färska och äldre ringhack på stambasen av en gran. I äldre granskog med minst medelhöga till höga livsmiljövärden för tretåig hackspett. Även gott om liggande död ved här. Finns även skalade döda granar här som indikerar potentiella födosökspår efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10341,12 +10341,12 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -10491,10 +10491,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122696876</v>
+        <v>122695752</v>
       </c>
       <c r="B75" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10507,47 +10507,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>479628</v>
+        <v>479748</v>
       </c>
       <c r="R75" t="n">
-        <v>7027133</v>
+        <v>7027283</v>
       </c>
       <c r="S75" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -10579,11 +10569,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på stambasen av en gran. I äldre granskog med minst medelhöga till höga livsmiljövärden för tretåig hackspett. Även gott om liggande död ved här. Finns även skalade döda granar här som indikerar potentiella födosökspår efter tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -10610,12 +10595,12 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -10774,10 +10759,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122695752</v>
+        <v>122695354</v>
       </c>
       <c r="B77" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10790,21 +10775,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -10814,13 +10799,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>479748</v>
+        <v>479765</v>
       </c>
       <c r="R77" t="n">
-        <v>7027283</v>
+        <v>7027389</v>
       </c>
       <c r="S77" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -10852,6 +10837,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>På en lutande krokig sälg.</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -10868,22 +10858,22 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10901,10 +10891,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122695354</v>
+        <v>122695655</v>
       </c>
       <c r="B78" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10917,37 +10907,42 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>479765</v>
+        <v>479759</v>
       </c>
       <c r="R78" t="n">
-        <v>7027389</v>
+        <v>7027292</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10981,7 +10976,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På en lutande krokig sälg.</t>
+          <t>Växer på två granar intill en sälg med ymnig påväxt av lunglav.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -11000,22 +10995,22 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -11033,10 +11028,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122695655</v>
+        <v>122697690</v>
       </c>
       <c r="B79" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -11049,42 +11044,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>479759</v>
+        <v>479640</v>
       </c>
       <c r="R79" t="n">
-        <v>7027292</v>
+        <v>7027281</v>
       </c>
       <c r="S79" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -11114,11 +11104,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Växer på två granar intill en sälg med ymnig påväxt av lunglav.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -11170,7 +11155,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122697690</v>
+        <v>122696014</v>
       </c>
       <c r="B80" t="n">
         <v>78766</v>
@@ -11210,10 +11195,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>479640</v>
+        <v>479718</v>
       </c>
       <c r="R80" t="n">
-        <v>7027281</v>
+        <v>7027277</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -11297,10 +11282,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122696014</v>
+        <v>122696537</v>
       </c>
       <c r="B81" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -11313,37 +11298,47 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>479718</v>
+        <v>479669</v>
       </c>
       <c r="R81" t="n">
-        <v>7027277</v>
+        <v>7027116</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -11375,6 +11370,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -11424,10 +11424,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122696537</v>
+        <v>122698232</v>
       </c>
       <c r="B82" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -11440,47 +11440,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>479669</v>
+        <v>479698</v>
       </c>
       <c r="R82" t="n">
-        <v>7027116</v>
+        <v>7027368</v>
       </c>
       <c r="S82" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -11512,11 +11502,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -11543,12 +11528,12 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -11566,10 +11551,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122698232</v>
+        <v>122695703</v>
       </c>
       <c r="B83" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -11582,37 +11567,42 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>479698</v>
+        <v>479753</v>
       </c>
       <c r="R83" t="n">
-        <v>7027368</v>
+        <v>7027296</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -11644,6 +11634,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglav på två knäckta sälgar.</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -11660,22 +11655,22 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -11693,10 +11688,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122695703</v>
+        <v>122695273</v>
       </c>
       <c r="B84" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11709,27 +11704,32 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -11738,13 +11738,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>479753</v>
+        <v>479770</v>
       </c>
       <c r="R84" t="n">
-        <v>7027296</v>
+        <v>7027401</v>
       </c>
       <c r="S84" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -11778,7 +11778,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på två knäckta sälgar.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11797,22 +11797,22 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -11830,10 +11830,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122695273</v>
+        <v>122695101</v>
       </c>
       <c r="B85" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11846,44 +11846,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>479770</v>
+        <v>479696</v>
       </c>
       <c r="R85" t="n">
-        <v>7027401</v>
+        <v>7027544</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11920,7 +11910,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11949,12 +11939,12 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -11972,10 +11962,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122695101</v>
+        <v>122697966</v>
       </c>
       <c r="B86" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11988,34 +11978,39 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>479696</v>
+        <v>479660</v>
       </c>
       <c r="R86" t="n">
-        <v>7027544</v>
+        <v>7027363</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -12050,11 +12045,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -12071,22 +12061,22 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -12104,10 +12094,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122697966</v>
+        <v>122697534</v>
       </c>
       <c r="B87" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -12120,39 +12110,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>479660</v>
+        <v>479644</v>
       </c>
       <c r="R87" t="n">
-        <v>7027363</v>
+        <v>7027243</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -12198,27 +12183,27 @@
       </c>
       <c r="AH87" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -12236,7 +12221,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122697534</v>
+        <v>122696303</v>
       </c>
       <c r="B88" t="n">
         <v>78766</v>
@@ -12276,13 +12261,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>479644</v>
+        <v>479685</v>
       </c>
       <c r="R88" t="n">
-        <v>7027243</v>
+        <v>7027165</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -12325,7 +12310,7 @@
       </c>
       <c r="AH88" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ88" t="inlineStr">
@@ -12363,10 +12348,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122696303</v>
+        <v>122696521</v>
       </c>
       <c r="B89" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -12379,37 +12364,47 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>479685</v>
+        <v>479674</v>
       </c>
       <c r="R89" t="n">
-        <v>7027165</v>
+        <v>7027109</v>
       </c>
       <c r="S89" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -12441,6 +12436,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Färska hackspår i stambasen av en smal gran i granskog med stora mängder liggande död ved.</t>
+        </is>
+      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
@@ -12467,12 +12467,12 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -12490,10 +12490,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122696521</v>
+        <v>122695516</v>
       </c>
       <c r="B90" t="n">
-        <v>57494</v>
+        <v>79847</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -12506,32 +12506,27 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -12540,13 +12535,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>479674</v>
+        <v>479766</v>
       </c>
       <c r="R90" t="n">
-        <v>7027109</v>
+        <v>7027310</v>
       </c>
       <c r="S90" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -12580,7 +12575,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Färska hackspår i stambasen av en smal gran i granskog med stora mängder liggande död ved.</t>
+          <t>Växer på en lite smalare sälg intill skrovellav.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -12599,22 +12594,22 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -12632,10 +12627,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122695516</v>
+        <v>122696426</v>
       </c>
       <c r="B91" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -12648,27 +12643,32 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -12677,13 +12677,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>479766</v>
+        <v>479685</v>
       </c>
       <c r="R91" t="n">
-        <v>7027310</v>
+        <v>7027127</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -12717,7 +12717,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Växer på en lite smalare sälg intill skrovellav.</t>
+          <t>Färska och äldre ringhack/savhack.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12736,22 +12736,22 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>

--- a/artfynd/A 60372-2024 artfynd.xlsx
+++ b/artfynd/A 60372-2024 artfynd.xlsx
@@ -3071,10 +3071,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122609386</v>
+        <v>122607246</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3087,27 +3087,36 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3116,10 +3125,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>479699</v>
+        <v>479659</v>
       </c>
       <c r="R20" t="n">
-        <v>7027340</v>
+        <v>7027556</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3156,7 +3165,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen av en stående död gran. Volym stående död ved här som ger medelhögt till högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Observerades i flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3171,26 +3180,6 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3208,10 +3197,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122607246</v>
+        <v>122609386</v>
       </c>
       <c r="B21" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3224,36 +3213,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3262,10 +3242,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>479659</v>
+        <v>479699</v>
       </c>
       <c r="R21" t="n">
-        <v>7027556</v>
+        <v>7027340</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3302,7 +3282,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Observerades i flerskiktad granskog.</t>
+          <t>Äldre ringhack på stambasen av en stående död gran. Volym stående död ved här som ger medelhögt till högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3317,6 +3297,26 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -4433,10 +4433,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122607565</v>
+        <v>122613066</v>
       </c>
       <c r="B30" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4449,37 +4449,44 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>479638</v>
+        <v>479702</v>
       </c>
       <c r="R30" t="n">
-        <v>7027601</v>
+        <v>7027288</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4513,7 +4520,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>Lunglav på en grovbarkad asp.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4522,6 +4529,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4530,24 +4538,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+        </is>
+      </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Populus tremula</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4565,10 +4578,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122606273</v>
+        <v>122606631</v>
       </c>
       <c r="B31" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4581,21 +4594,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4610,13 +4623,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>479698</v>
+        <v>479711</v>
       </c>
       <c r="R31" t="n">
-        <v>7027398</v>
+        <v>7027473</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4650,7 +4663,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Skrovellav på en undertryck gran intill en gammal grov sälg.</t>
+          <t>Enstaka bålar på en asp.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4664,27 +4677,27 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4702,10 +4715,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122613066</v>
+        <v>122606273</v>
       </c>
       <c r="B32" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4718,44 +4731,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
           <t>med soral</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>479702</v>
+        <v>479698</v>
       </c>
       <c r="R32" t="n">
-        <v>7027288</v>
+        <v>7027398</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4789,7 +4800,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Lunglav på en grovbarkad asp.</t>
+          <t>Skrovellav på en undertryck gran intill en gammal grov sälg.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4798,38 +4809,32 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4847,10 +4852,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122606631</v>
+        <v>122607565</v>
       </c>
       <c r="B33" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4863,39 +4868,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>479711</v>
+        <v>479638</v>
       </c>
       <c r="R33" t="n">
-        <v>7027473</v>
+        <v>7027601</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4932,7 +4932,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en asp.</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4951,22 +4951,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -8624,10 +8624,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122696471</v>
+        <v>122695602</v>
       </c>
       <c r="B61" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8640,32 +8640,27 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -8674,13 +8669,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>479681</v>
+        <v>479774</v>
       </c>
       <c r="R61" t="n">
-        <v>7027123</v>
+        <v>7027322</v>
       </c>
       <c r="S61" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8714,7 +8709,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen.</t>
+          <t>Ymnigt med lunglav på en gammal sälg med fårad bark.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8733,22 +8728,22 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8766,10 +8761,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122695602</v>
+        <v>122696471</v>
       </c>
       <c r="B62" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8782,27 +8777,32 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -8811,13 +8811,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>479774</v>
+        <v>479681</v>
       </c>
       <c r="R62" t="n">
-        <v>7027322</v>
+        <v>7027123</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ymnigt med lunglav på en gammal sälg med fårad bark.</t>
+          <t>Äldre ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8870,22 +8870,22 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -9029,10 +9029,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122695075</v>
+        <v>122695492</v>
       </c>
       <c r="B64" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -9045,34 +9045,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>479699</v>
+        <v>479770</v>
       </c>
       <c r="R64" t="n">
-        <v>7027521</v>
+        <v>7027300</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -9109,7 +9114,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Växer på en lite smalare sälg intill lunglav.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9128,22 +9133,22 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -9161,10 +9166,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122696057</v>
+        <v>122695075</v>
       </c>
       <c r="B65" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9177,39 +9182,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>479675</v>
+        <v>479699</v>
       </c>
       <c r="R65" t="n">
-        <v>7027261</v>
+        <v>7027521</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På flera aspar.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9265,22 +9265,22 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9298,7 +9298,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122695926</v>
+        <v>122696057</v>
       </c>
       <c r="B66" t="n">
         <v>79847</v>
@@ -9343,10 +9343,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>479752</v>
+        <v>479675</v>
       </c>
       <c r="R66" t="n">
-        <v>7027344</v>
+        <v>7027261</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9383,7 +9383,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ymnigt med lunglav på en gammal sälg.</t>
+          <t>På flera aspar.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9402,12 +9402,12 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM66" t="inlineStr">
@@ -9417,7 +9417,7 @@
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9435,10 +9435,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122695492</v>
+        <v>122695926</v>
       </c>
       <c r="B67" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9451,21 +9451,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -9480,10 +9480,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>479770</v>
+        <v>479752</v>
       </c>
       <c r="R67" t="n">
-        <v>7027300</v>
+        <v>7027344</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9520,7 +9520,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Växer på en lite smalare sälg intill lunglav.</t>
+          <t>Ymnigt med lunglav på en gammal sälg.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9699,10 +9699,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122696111</v>
+        <v>122697286</v>
       </c>
       <c r="B69" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9715,34 +9715,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>479694</v>
+        <v>479663</v>
       </c>
       <c r="R69" t="n">
-        <v>7027236</v>
+        <v>7027246</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9793,22 +9798,22 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9826,7 +9831,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122697882</v>
+        <v>122696111</v>
       </c>
       <c r="B70" t="n">
         <v>78766</v>
@@ -9866,13 +9871,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>479664</v>
+        <v>479694</v>
       </c>
       <c r="R70" t="n">
-        <v>7027326</v>
+        <v>7027236</v>
       </c>
       <c r="S70" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9902,11 +9907,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9958,10 +9958,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122697286</v>
+        <v>122697882</v>
       </c>
       <c r="B71" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9974,42 +9974,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>479663</v>
+        <v>479664</v>
       </c>
       <c r="R71" t="n">
-        <v>7027246</v>
+        <v>7027326</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -10041,6 +10036,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -10057,22 +10057,22 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -10491,10 +10491,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122695752</v>
+        <v>122697666</v>
       </c>
       <c r="B75" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10507,37 +10507,51 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>479748</v>
+        <v>479632</v>
       </c>
       <c r="R75" t="n">
-        <v>7027283</v>
+        <v>7027297</v>
       </c>
       <c r="S75" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -10595,12 +10609,12 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -10618,10 +10632,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122697666</v>
+        <v>122695752</v>
       </c>
       <c r="B76" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10634,51 +10648,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>479632</v>
+        <v>479748</v>
       </c>
       <c r="R76" t="n">
-        <v>7027297</v>
+        <v>7027283</v>
       </c>
       <c r="S76" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -10736,12 +10736,12 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>

--- a/artfynd/A 60372-2024 artfynd.xlsx
+++ b/artfynd/A 60372-2024 artfynd.xlsx
@@ -2007,10 +2007,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122609753</v>
+        <v>122609468</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2023,34 +2023,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>479670</v>
+        <v>479731</v>
       </c>
       <c r="R12" t="n">
-        <v>7027294</v>
+        <v>7027323</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2085,6 +2090,11 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ymnigt med lunglav längs 7 meter på en något smalare sälg.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2101,22 +2111,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2134,10 +2144,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122606026</v>
+        <v>122609753</v>
       </c>
       <c r="B13" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2150,39 +2160,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>479756</v>
+        <v>479670</v>
       </c>
       <c r="R13" t="n">
-        <v>7027477</v>
+        <v>7027294</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2243,12 +2248,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2266,10 +2271,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122609468</v>
+        <v>122606026</v>
       </c>
       <c r="B14" t="n">
-        <v>79847</v>
+        <v>90962</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2282,27 +2287,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2311,10 +2316,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>479731</v>
+        <v>479756</v>
       </c>
       <c r="R14" t="n">
-        <v>7027323</v>
+        <v>7027477</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2349,11 +2354,6 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ymnigt med lunglav längs 7 meter på en något smalare sälg.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2370,22 +2370,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -9699,10 +9699,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122697286</v>
+        <v>122696111</v>
       </c>
       <c r="B69" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9715,39 +9715,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>479663</v>
+        <v>479694</v>
       </c>
       <c r="R69" t="n">
-        <v>7027246</v>
+        <v>7027236</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9798,22 +9793,22 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9831,7 +9826,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122696111</v>
+        <v>122697882</v>
       </c>
       <c r="B70" t="n">
         <v>78766</v>
@@ -9871,13 +9866,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>479694</v>
+        <v>479664</v>
       </c>
       <c r="R70" t="n">
-        <v>7027236</v>
+        <v>7027326</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9907,6 +9902,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9958,10 +9958,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122697882</v>
+        <v>122697286</v>
       </c>
       <c r="B71" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9974,37 +9974,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>479664</v>
+        <v>479663</v>
       </c>
       <c r="R71" t="n">
-        <v>7027326</v>
+        <v>7027246</v>
       </c>
       <c r="S71" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -10036,11 +10041,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -10057,22 +10057,22 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>

--- a/artfynd/A 60372-2024 artfynd.xlsx
+++ b/artfynd/A 60372-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122607879</v>
+        <v>122609468</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>479622</v>
+        <v>479731</v>
       </c>
       <c r="R2" t="n">
-        <v>7027648</v>
+        <v>7027323</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +760,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ymnigt med lunglav längs 7 meter på en något smalare sälg.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,22 +779,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -807,10 +812,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122613058</v>
+        <v>122606273</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,40 +828,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479722</v>
+        <v>479698</v>
       </c>
       <c r="R3" t="n">
-        <v>7027290</v>
+        <v>7027398</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,24 +895,23 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Skrovellav på en undertryck gran intill en gammal grov sälg.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -943,10 +949,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122609281</v>
+        <v>122606026</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -959,37 +965,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479698</v>
+        <v>479756</v>
       </c>
       <c r="R4" t="n">
-        <v>7027342</v>
+        <v>7027477</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1021,11 +1032,6 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flera granar.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1052,12 +1058,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1075,10 +1081,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122606280</v>
+        <v>122607620</v>
       </c>
       <c r="B5" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1091,21 +1097,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1115,10 +1121,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>479693</v>
+        <v>479635</v>
       </c>
       <c r="R5" t="n">
-        <v>7027399</v>
+        <v>7027621</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1155,7 +1161,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Skrovellav på en gammal grov sälg med 54 cm i brösthöjdsdiameter.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1169,17 +1175,17 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1189,7 +1195,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1207,10 +1213,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122608509</v>
+        <v>122606232</v>
       </c>
       <c r="B6" t="n">
-        <v>79751</v>
+        <v>79847</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1219,38 +1225,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>479617</v>
+        <v>479707</v>
       </c>
       <c r="R6" t="n">
-        <v>7027598</v>
+        <v>7027397</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1285,6 +1296,11 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på en undertryck gran intill en gammal grov sälg.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1296,27 +1312,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1334,7 +1350,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122606696</v>
+        <v>122607263</v>
       </c>
       <c r="B7" t="n">
         <v>78766</v>
@@ -1374,10 +1390,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>479678</v>
+        <v>479655</v>
       </c>
       <c r="R7" t="n">
-        <v>7027508</v>
+        <v>7027573</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1461,7 +1477,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122607620</v>
+        <v>122608228</v>
       </c>
       <c r="B8" t="n">
         <v>78766</v>
@@ -1497,14 +1513,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Kvarnbäcken, Kvarnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>479635</v>
+        <v>479594</v>
       </c>
       <c r="R8" t="n">
-        <v>7027621</v>
+        <v>7027696</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1593,7 +1609,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122612982</v>
+        <v>122613090</v>
       </c>
       <c r="B9" t="n">
         <v>79847</v>
@@ -1640,13 +1656,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>479738</v>
+        <v>479694</v>
       </c>
       <c r="R9" t="n">
-        <v>7027319</v>
+        <v>7027295</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1680,7 +1696,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Grova gamla lunglavsbålar på en lutande sälg.</t>
+          <t>Ett gäng "knippen" med stora lunglavsbålar på en asp.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1705,17 +1721,12 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>En smal lutande sälg.</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -1725,7 +1736,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En smal lutande sälg.</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1743,7 +1754,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122605930</v>
+        <v>122609281</v>
       </c>
       <c r="B10" t="n">
         <v>78766</v>
@@ -1783,13 +1794,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>479743</v>
+        <v>479698</v>
       </c>
       <c r="R10" t="n">
-        <v>7027472</v>
+        <v>7027342</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1823,7 +1834,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera träd.</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1875,10 +1886,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122608228</v>
+        <v>122612982</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1891,34 +1902,41 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kvarnbäcken, Kvarnbäcken, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>479594</v>
+        <v>479738</v>
       </c>
       <c r="R11" t="n">
-        <v>7027696</v>
+        <v>7027319</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1955,7 +1973,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Grova gamla lunglavsbålar på en lutande sälg.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1964,6 +1982,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1972,24 +1991,34 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+        </is>
+      </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>En smal lutande sälg.</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En smal lutande sälg.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2007,10 +2036,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122609468</v>
+        <v>122608343</v>
       </c>
       <c r="B12" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2023,42 +2052,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Kvarnbäcken, Kvarnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>479731</v>
+        <v>479569</v>
       </c>
       <c r="R12" t="n">
-        <v>7027323</v>
+        <v>7027674</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2092,7 +2116,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ymnigt med lunglav längs 7 meter på en något smalare sälg.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2111,22 +2135,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2144,10 +2168,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122609753</v>
+        <v>122609496</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2160,37 +2184,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>479670</v>
+        <v>479735</v>
       </c>
       <c r="R13" t="n">
-        <v>7027294</v>
+        <v>7027318</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2271,10 +2300,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122606026</v>
+        <v>122613032</v>
       </c>
       <c r="B14" t="n">
-        <v>90962</v>
+        <v>79847</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2287,42 +2316,44 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>479756</v>
+        <v>479731</v>
       </c>
       <c r="R14" t="n">
-        <v>7027477</v>
+        <v>7027291</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2354,12 +2385,18 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>En hel del bålar på en skadad sälg.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2368,24 +2405,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+        </is>
+      </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2403,7 +2445,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122606169</v>
+        <v>122609424</v>
       </c>
       <c r="B15" t="n">
         <v>79847</v>
@@ -2448,13 +2490,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>479698</v>
+        <v>479729</v>
       </c>
       <c r="R15" t="n">
-        <v>7027398</v>
+        <v>7027353</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2488,7 +2530,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav där vissa bålar är fertila med apothecier. På en gammal grovbarkad sälg med 54 cm i brösthöjdsdiameter.</t>
+          <t>Fertila bålar på en smal böjd sälg.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2502,7 +2544,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -2540,7 +2582,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122607162</v>
+        <v>122607879</v>
       </c>
       <c r="B16" t="n">
         <v>78766</v>
@@ -2580,13 +2622,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>479650</v>
+        <v>479622</v>
       </c>
       <c r="R16" t="n">
-        <v>7027549</v>
+        <v>7027648</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2672,10 +2714,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122613032</v>
+        <v>122609837</v>
       </c>
       <c r="B17" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2688,44 +2730,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>479731</v>
+        <v>479643</v>
       </c>
       <c r="R17" t="n">
-        <v>7027291</v>
+        <v>7027326</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2759,7 +2794,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>En hel del bålar på en skadad sälg.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2768,7 +2803,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2777,29 +2811,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
-        </is>
-      </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2817,10 +2846,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122607263</v>
+        <v>122609386</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2833,34 +2862,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>479655</v>
+        <v>479699</v>
       </c>
       <c r="R18" t="n">
-        <v>7027573</v>
+        <v>7027340</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2895,6 +2929,11 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på stambasen av en stående död gran. Volym stående död ved här som ger medelhögt till högt livsmiljövärde för tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2921,12 +2960,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2944,10 +2983,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122609252</v>
+        <v>122606649</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>79883</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2956,38 +2995,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>479714</v>
+        <v>479715</v>
       </c>
       <c r="R19" t="n">
-        <v>7027356</v>
+        <v>7027462</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3022,6 +3066,11 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>En samling bålar på ca 2 meters höjd på aspens stam.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -3038,22 +3087,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3071,10 +3120,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122607246</v>
+        <v>122613066</v>
       </c>
       <c r="B20" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3087,51 +3136,44 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>479659</v>
+        <v>479702</v>
       </c>
       <c r="R20" t="n">
-        <v>7027556</v>
+        <v>7027288</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3165,7 +3207,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Observerades i flerskiktad granskog.</t>
+          <t>Lunglav på en grovbarkad asp.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3174,12 +3216,38 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Grov bark. # Populus tremula</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3197,10 +3265,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122609386</v>
+        <v>122606631</v>
       </c>
       <c r="B21" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3213,27 +3281,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3242,10 +3310,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>479699</v>
+        <v>479711</v>
       </c>
       <c r="R21" t="n">
-        <v>7027340</v>
+        <v>7027473</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3282,7 +3350,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen av en stående död gran. Volym stående död ved här som ger medelhögt till högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Enstaka bålar på en asp.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3301,22 +3369,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3334,10 +3402,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122609424</v>
+        <v>122606334</v>
       </c>
       <c r="B22" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3350,39 +3418,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>479729</v>
+        <v>479692</v>
       </c>
       <c r="R22" t="n">
-        <v>7027353</v>
+        <v>7027424</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3417,11 +3480,6 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Fertila bålar på en smal böjd sälg.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3433,27 +3491,27 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3471,10 +3529,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122607124</v>
+        <v>122605930</v>
       </c>
       <c r="B23" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3487,44 +3545,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>479654</v>
+        <v>479743</v>
       </c>
       <c r="R23" t="n">
-        <v>7027561</v>
+        <v>7027472</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3561,7 +3609,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Både äldre och färska ringhack på stambasen.</t>
+          <t>Långväxta bålar på flera träd.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3590,12 +3638,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3613,10 +3661,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122609837</v>
+        <v>122607246</v>
       </c>
       <c r="B24" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3629,34 +3677,48 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>479643</v>
+        <v>479659</v>
       </c>
       <c r="R24" t="n">
-        <v>7027326</v>
+        <v>7027556</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3693,7 +3755,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Observerades i flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3708,26 +3770,6 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3745,10 +3787,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122607115</v>
+        <v>122609753</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3761,47 +3803,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>479652</v>
+        <v>479670</v>
       </c>
       <c r="R25" t="n">
-        <v>7027551</v>
+        <v>7027294</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3833,11 +3865,6 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Både färska och äldre ringhack på stambasen. I skogsbeståndet runt fyndplatsen finns medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3864,12 +3891,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3887,10 +3914,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122606431</v>
+        <v>122606169</v>
       </c>
       <c r="B26" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3903,37 +3930,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>479711</v>
+        <v>479698</v>
       </c>
       <c r="R26" t="n">
-        <v>7027387</v>
+        <v>7027398</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3967,7 +3999,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Rikligt med lunglav där vissa bålar är fertila med apothecier. På en gammal grovbarkad sälg med 54 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3986,22 +4018,22 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4019,10 +4051,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122606649</v>
+        <v>122613055</v>
       </c>
       <c r="B27" t="n">
-        <v>79883</v>
+        <v>79847</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4031,46 +4063,44 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>479715</v>
+        <v>479722</v>
       </c>
       <c r="R27" t="n">
-        <v>7027462</v>
+        <v>7027290</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4104,7 +4134,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>En samling bålar på ca 2 meters höjd på aspens stam.</t>
+          <t>Enstaka små bålar på en grov gammal asp.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4113,6 +4143,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -4121,6 +4152,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+        </is>
+      </c>
       <c r="AJ27" t="inlineStr">
         <is>
           <t>asp</t>
@@ -4138,7 +4174,7 @@
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Grov bark. # Populus tremula</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4156,10 +4192,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122613090</v>
+        <v>122606696</v>
       </c>
       <c r="B28" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4172,44 +4208,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>479694</v>
+        <v>479678</v>
       </c>
       <c r="R28" t="n">
-        <v>7027295</v>
+        <v>7027508</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4241,18 +4270,12 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ett gäng "knippen" med stora lunglavsbålar på en asp.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4261,29 +4284,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
-        </is>
-      </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4301,10 +4319,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122609496</v>
+        <v>122607115</v>
       </c>
       <c r="B29" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4317,27 +4335,32 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4346,13 +4369,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>479735</v>
+        <v>479652</v>
       </c>
       <c r="R29" t="n">
-        <v>7027318</v>
+        <v>7027551</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4384,6 +4407,11 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Både färska och äldre ringhack på stambasen. I skogsbeståndet runt fyndplatsen finns medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4410,12 +4438,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4433,10 +4461,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122613066</v>
+        <v>122607124</v>
       </c>
       <c r="B30" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4449,44 +4477,47 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>479702</v>
+        <v>479654</v>
       </c>
       <c r="R30" t="n">
-        <v>7027288</v>
+        <v>7027561</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4520,7 +4551,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Lunglav på en grovbarkad asp.</t>
+          <t>Både äldre och färska ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4529,7 +4560,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4538,29 +4568,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
-        </is>
-      </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4578,10 +4603,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122606631</v>
+        <v>122609252</v>
       </c>
       <c r="B31" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4594,39 +4619,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>479711</v>
+        <v>479714</v>
       </c>
       <c r="R31" t="n">
-        <v>7027473</v>
+        <v>7027356</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4661,11 +4681,6 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på en asp.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4682,22 +4697,22 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4715,10 +4730,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122606273</v>
+        <v>122606868</v>
       </c>
       <c r="B32" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4731,42 +4746,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>479698</v>
+        <v>479661</v>
       </c>
       <c r="R32" t="n">
-        <v>7027398</v>
+        <v>7027516</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4796,11 +4806,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Skrovellav på en undertryck gran intill en gammal grov sälg.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4852,10 +4857,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122607565</v>
+        <v>122606280</v>
       </c>
       <c r="B33" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4868,21 +4873,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4892,10 +4897,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>479638</v>
+        <v>479693</v>
       </c>
       <c r="R33" t="n">
-        <v>7027601</v>
+        <v>7027399</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4932,7 +4937,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>Skrovellav på en gammal grov sälg med 54 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4946,17 +4951,17 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
@@ -4966,7 +4971,7 @@
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Branch on living tree # Salix caprea</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4984,10 +4989,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122606232</v>
+        <v>122606431</v>
       </c>
       <c r="B34" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5000,39 +5005,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>479707</v>
+        <v>479711</v>
       </c>
       <c r="R34" t="n">
-        <v>7027397</v>
+        <v>7027387</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5069,7 +5069,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Fertil lunglav på en undertryck gran intill en gammal grov sälg.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5121,7 +5121,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122606868</v>
+        <v>122613058</v>
       </c>
       <c r="B35" t="n">
         <v>78766</v>
@@ -5155,19 +5155,22 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>479661</v>
+        <v>479722</v>
       </c>
       <c r="R35" t="n">
-        <v>7027516</v>
+        <v>7027290</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5205,12 +5208,18 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -5248,10 +5257,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122613055</v>
+        <v>122608462</v>
       </c>
       <c r="B36" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5264,40 +5273,47 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Kvarnbäcken, Kvarnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>479722</v>
+        <v>479583</v>
       </c>
       <c r="R36" t="n">
-        <v>7027290</v>
+        <v>7027629</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5331,7 +5347,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Enstaka små bålar på en grov gammal asp.</t>
+          <t>Äldre ringhack som bedöms vara 5-10 år gamla. På en gran med tydliga kådaflöden. Hyfsat gott om död ved här.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5340,7 +5356,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -5349,29 +5364,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
-        </is>
-      </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5389,7 +5399,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122608343</v>
+        <v>122607565</v>
       </c>
       <c r="B37" t="n">
         <v>78766</v>
@@ -5425,17 +5435,17 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kvarnbäcken, Kvarnbäcken, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>479569</v>
+        <v>479638</v>
       </c>
       <c r="R37" t="n">
-        <v>7027674</v>
+        <v>7027601</v>
       </c>
       <c r="S37" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5469,7 +5479,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5521,10 +5531,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122606334</v>
+        <v>122608509</v>
       </c>
       <c r="B38" t="n">
-        <v>78766</v>
+        <v>79751</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5533,25 +5543,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5561,10 +5571,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>479692</v>
+        <v>479617</v>
       </c>
       <c r="R38" t="n">
-        <v>7027424</v>
+        <v>7027598</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5610,27 +5620,27 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5648,10 +5658,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122608462</v>
+        <v>122607162</v>
       </c>
       <c r="B39" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5664,47 +5674,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Kvarnbäcken, Kvarnbäcken, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>479583</v>
+        <v>479650</v>
       </c>
       <c r="R39" t="n">
-        <v>7027629</v>
+        <v>7027549</v>
       </c>
       <c r="S39" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Äldre ringhack som bedöms vara 5-10 år gamla. På en gran med tydliga kådaflöden. Hyfsat gott om död ved här.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5790,7 +5790,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122613271</v>
+        <v>122613145</v>
       </c>
       <c r="B40" t="n">
         <v>79847</v>
@@ -5837,13 +5837,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>479628</v>
+        <v>479634</v>
       </c>
       <c r="R40" t="n">
-        <v>7027338</v>
+        <v>7027302</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Riklig påväxt av lunglavsbålar på en gammal sälg. Vissa bålar är fertila med apothecier. Här växer även rikligt med lunglav på gran.</t>
+          <t>Ymnig påväxt av lunglav längs flera meter på en sälgstam. Vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="AL40" t="inlineStr">
         <is>
-          <t>En gammal grov sälg.</t>
+          <t>En svagt lutande sälg.</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea # En gammal grov sälg.</t>
+          <t>Bark on living woody plant # Salix caprea # En svagt lutande sälg.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5940,7 +5940,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122609140</v>
+        <v>122608974</v>
       </c>
       <c r="B41" t="n">
         <v>79847</v>
@@ -5976,7 +5976,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5985,13 +5985,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>479723</v>
+        <v>479682</v>
       </c>
       <c r="R41" t="n">
-        <v>7027396</v>
+        <v>7027484</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -6023,11 +6023,6 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ymnig påväxt av lunglav längs flera meter på en gammal sälg. Fertila bålar med apothecier.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -6044,12 +6039,12 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
@@ -6059,7 +6054,7 @@
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6077,10 +6072,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122609073</v>
+        <v>122609714</v>
       </c>
       <c r="B42" t="n">
-        <v>79847</v>
+        <v>57631</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6093,42 +6088,49 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>479738</v>
+        <v>479677</v>
       </c>
       <c r="R42" t="n">
-        <v>7027404</v>
+        <v>7027303</v>
       </c>
       <c r="S42" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6162,7 +6164,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På en smal sälg.</t>
+          <t>Observation i flerskiktad granskog med stående murkna björkhögstubbar som är gynnsamt för talltitans häckning.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6179,24 +6181,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6214,10 +6201,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122607364</v>
+        <v>122608090</v>
       </c>
       <c r="B43" t="n">
-        <v>57478</v>
+        <v>79751</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6226,46 +6213,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>479644</v>
+        <v>479602</v>
       </c>
       <c r="R43" t="n">
-        <v>7027599</v>
+        <v>7027640</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6297,11 +6279,6 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Både färska och äldre ringhack på stambasen. I skogsbeståndet runt fyndplatsen finns medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -6318,22 +6295,22 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6351,10 +6328,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122613281</v>
+        <v>122609140</v>
       </c>
       <c r="B44" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6367,40 +6344,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>479628</v>
+        <v>479723</v>
       </c>
       <c r="R44" t="n">
-        <v>7027338</v>
+        <v>7027396</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6434,7 +6413,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Med långväxta bålar och på flera granar.</t>
+          <t>Ymnig påväxt av lunglav längs flera meter på en gammal sälg. Fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6443,7 +6422,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6452,29 +6430,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
-        </is>
-      </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6492,10 +6465,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122613145</v>
+        <v>122607410</v>
       </c>
       <c r="B45" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6508,41 +6481,44 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>479634</v>
+        <v>479644</v>
       </c>
       <c r="R45" t="n">
-        <v>7027302</v>
+        <v>7027599</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6579,7 +6555,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ymnig påväxt av lunglav längs flera meter på en sälgstam. Vissa bålar är fertila med apothecier.</t>
+          <t>Både äldre och färska ringhack på stambasen. I skogsbeståndet runt fyndplatsen finns medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6588,7 +6564,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6597,34 +6572,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
-        </is>
-      </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL45" t="inlineStr">
-        <is>
-          <t>En svagt lutande sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En svagt lutande sälg.</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6642,10 +6607,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122608974</v>
+        <v>122613280</v>
       </c>
       <c r="B46" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6658,42 +6623,44 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
           <t>med soral</t>
         </is>
       </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>479682</v>
+        <v>479628</v>
       </c>
       <c r="R46" t="n">
-        <v>7027484</v>
+        <v>7027338</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6725,12 +6692,18 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På renar av gran blandat med lunglav.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6739,24 +6712,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+        </is>
+      </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6774,10 +6752,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122613280</v>
+        <v>122613281</v>
       </c>
       <c r="B47" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6790,30 +6768,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6861,7 +6835,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På renar av gran blandat med lunglav.</t>
+          <t>Med långväxta bålar och på flera granar.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6919,10 +6893,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122607746</v>
+        <v>122609073</v>
       </c>
       <c r="B48" t="n">
-        <v>79751</v>
+        <v>79847</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6931,48 +6905,46 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>479627</v>
+        <v>479738</v>
       </c>
       <c r="R48" t="n">
-        <v>7027656</v>
+        <v>7027404</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -7006,7 +6978,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Skinnlav på asp där flertalet bålar är fertila med apothecier.</t>
+          <t>På en smal sälg.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7015,7 +6987,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -7024,19 +6995,14 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>Flerskiktad kontinuitetsskog dominerad av gran och med återkommande inslag av asp.</t>
-        </is>
-      </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
@@ -7046,7 +7012,7 @@
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -7064,10 +7030,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122609714</v>
+        <v>122613271</v>
       </c>
       <c r="B49" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -7080,49 +7046,44 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>479677</v>
+        <v>479628</v>
       </c>
       <c r="R49" t="n">
-        <v>7027303</v>
+        <v>7027338</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -7156,7 +7117,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Observation i flerskiktad granskog med stående murkna björkhögstubbar som är gynnsamt för talltitans häckning.</t>
+          <t>Riklig påväxt av lunglavsbålar på en gammal sälg. Vissa bålar är fertila med apothecier. Här växer även rikligt med lunglav på gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7165,6 +7126,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -7176,6 +7138,31 @@
       <c r="AI49" t="inlineStr">
         <is>
           <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL49" t="inlineStr">
+        <is>
+          <t>En gammal grov sälg.</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea # En gammal grov sälg.</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7193,7 +7180,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122608090</v>
+        <v>122607746</v>
       </c>
       <c r="B50" t="n">
         <v>79751</v>
@@ -7227,19 +7214,26 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>479602</v>
+        <v>479627</v>
       </c>
       <c r="R50" t="n">
-        <v>7027640</v>
+        <v>7027656</v>
       </c>
       <c r="S50" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7271,18 +7265,29 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Skinnlav på asp där flertalet bålar är fertila med apothecier.</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Flerskiktad kontinuitetsskog dominerad av gran och med återkommande inslag av asp.</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -7320,7 +7325,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122695943</v>
+        <v>122698085</v>
       </c>
       <c r="B51" t="n">
         <v>78766</v>
@@ -7360,10 +7365,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>479756</v>
+        <v>479659</v>
       </c>
       <c r="R51" t="n">
-        <v>7027364</v>
+        <v>7027303</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7447,7 +7452,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122695322</v>
+        <v>122695682</v>
       </c>
       <c r="B52" t="n">
         <v>79847</v>
@@ -7492,10 +7497,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>479771</v>
+        <v>479763</v>
       </c>
       <c r="R52" t="n">
-        <v>7027387</v>
+        <v>7027300</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7532,7 +7537,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På en lutande krokig sälg.</t>
+          <t>På en smal krokig sälg.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7584,10 +7589,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122697757</v>
+        <v>122698275</v>
       </c>
       <c r="B53" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7600,39 +7605,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>479615</v>
+        <v>479734</v>
       </c>
       <c r="R53" t="n">
-        <v>7027315</v>
+        <v>7027357</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7667,6 +7667,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -7683,22 +7688,22 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7716,7 +7721,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122697352</v>
+        <v>122695075</v>
       </c>
       <c r="B54" t="n">
         <v>78766</v>
@@ -7756,10 +7761,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>479674</v>
+        <v>479699</v>
       </c>
       <c r="R54" t="n">
-        <v>7027178</v>
+        <v>7027521</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7792,6 +7797,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7843,10 +7853,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122695669</v>
+        <v>122696876</v>
       </c>
       <c r="B55" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7859,37 +7869,47 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>479761</v>
+        <v>479628</v>
       </c>
       <c r="R55" t="n">
-        <v>7027298</v>
+        <v>7027133</v>
       </c>
       <c r="S55" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7921,6 +7941,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på stambasen av en gran. I äldre granskog med minst medelhöga till höga livsmiljövärden för tretåig hackspett. Även gott om liggande död ved här. Finns även skalade döda granar här som indikerar potentiella födosökspår efter tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -7947,12 +7972,12 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7970,10 +7995,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122697455</v>
+        <v>122697690</v>
       </c>
       <c r="B56" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7986,51 +8011,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>479680</v>
+        <v>479640</v>
       </c>
       <c r="R56" t="n">
-        <v>7027206</v>
+        <v>7027281</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -8062,11 +8073,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Observation av en spillkråka som gav ifrån sig två olika lockläten. I gammal granskog med gott om asp och tall som utgör lämpliga substrat för bohål. Även bitvis relativt gott om död ved här.</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -8079,6 +8085,26 @@
       <c r="AH56" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -8096,10 +8122,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122697773</v>
+        <v>122695011</v>
       </c>
       <c r="B57" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -8112,21 +8138,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -8136,10 +8162,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>479617</v>
+        <v>479729</v>
       </c>
       <c r="R57" t="n">
-        <v>7027326</v>
+        <v>7027486</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -8176,7 +8202,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Enstaka bålar.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8195,22 +8221,22 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8228,10 +8254,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122695011</v>
+        <v>122695602</v>
       </c>
       <c r="B58" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8244,34 +8270,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>479729</v>
+        <v>479774</v>
       </c>
       <c r="R58" t="n">
-        <v>7027486</v>
+        <v>7027322</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8308,7 +8339,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ymnigt med lunglav på en gammal sälg med fårad bark.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8327,22 +8358,22 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8360,10 +8391,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122695682</v>
+        <v>122696537</v>
       </c>
       <c r="B59" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8376,27 +8407,32 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -8405,13 +8441,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>479763</v>
+        <v>479669</v>
       </c>
       <c r="R59" t="n">
-        <v>7027300</v>
+        <v>7027116</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8445,7 +8481,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På en smal krokig sälg.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8464,22 +8500,22 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8497,10 +8533,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122698247</v>
+        <v>122695273</v>
       </c>
       <c r="B60" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8513,34 +8549,44 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>479696</v>
+        <v>479770</v>
       </c>
       <c r="R60" t="n">
-        <v>7027370</v>
+        <v>7027401</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8575,6 +8621,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -8601,12 +8652,12 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8624,10 +8675,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122695602</v>
+        <v>122697534</v>
       </c>
       <c r="B61" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8640,39 +8691,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>479774</v>
+        <v>479644</v>
       </c>
       <c r="R61" t="n">
-        <v>7027322</v>
+        <v>7027243</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8707,11 +8753,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ymnigt med lunglav på en gammal sälg med fårad bark.</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -8723,27 +8764,27 @@
       </c>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8761,10 +8802,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122696471</v>
+        <v>122695101</v>
       </c>
       <c r="B62" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8777,47 +8818,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>479681</v>
+        <v>479696</v>
       </c>
       <c r="R62" t="n">
-        <v>7027123</v>
+        <v>7027544</v>
       </c>
       <c r="S62" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8851,7 +8882,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8880,12 +8911,12 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8903,10 +8934,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122696290</v>
+        <v>122696111</v>
       </c>
       <c r="B63" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8919,48 +8950,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>479695</v>
+        <v>479694</v>
       </c>
       <c r="R63" t="n">
-        <v>7027185</v>
+        <v>7027236</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8995,11 +9012,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Observerad i flerskiktad äldre granskog.</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -9012,6 +9024,26 @@
       <c r="AH63" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -9029,10 +9061,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122695492</v>
+        <v>122695516</v>
       </c>
       <c r="B64" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -9045,21 +9077,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -9074,10 +9106,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>479770</v>
+        <v>479766</v>
       </c>
       <c r="R64" t="n">
-        <v>7027300</v>
+        <v>7027310</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -9114,7 +9146,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Växer på en lite smalare sälg intill lunglav.</t>
+          <t>Växer på en lite smalare sälg intill skrovellav.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9166,10 +9198,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122695075</v>
+        <v>122695322</v>
       </c>
       <c r="B65" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9182,34 +9214,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>479699</v>
+        <v>479771</v>
       </c>
       <c r="R65" t="n">
-        <v>7027521</v>
+        <v>7027387</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -9246,7 +9283,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På en lutande krokig sälg.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9265,22 +9302,22 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9298,7 +9335,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122696057</v>
+        <v>122695926</v>
       </c>
       <c r="B66" t="n">
         <v>79847</v>
@@ -9343,10 +9380,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>479675</v>
+        <v>479752</v>
       </c>
       <c r="R66" t="n">
-        <v>7027261</v>
+        <v>7027344</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9383,7 +9420,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>På flera aspar.</t>
+          <t>Ymnigt med lunglav på en gammal sälg.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9402,12 +9439,12 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM66" t="inlineStr">
@@ -9417,7 +9454,7 @@
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9435,7 +9472,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122695926</v>
+        <v>122695703</v>
       </c>
       <c r="B67" t="n">
         <v>79847</v>
@@ -9480,13 +9517,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>479752</v>
+        <v>479753</v>
       </c>
       <c r="R67" t="n">
-        <v>7027344</v>
+        <v>7027296</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -9520,7 +9557,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ymnigt med lunglav på en gammal sälg.</t>
+          <t>Rikligt med lunglav på två knäckta sälgar.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9572,7 +9609,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122698085</v>
+        <v>122697352</v>
       </c>
       <c r="B68" t="n">
         <v>78766</v>
@@ -9612,10 +9649,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>479659</v>
+        <v>479674</v>
       </c>
       <c r="R68" t="n">
-        <v>7027303</v>
+        <v>7027178</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9699,7 +9736,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122696111</v>
+        <v>122698232</v>
       </c>
       <c r="B69" t="n">
         <v>78766</v>
@@ -9739,10 +9776,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>479694</v>
+        <v>479698</v>
       </c>
       <c r="R69" t="n">
-        <v>7027236</v>
+        <v>7027368</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9826,10 +9863,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122697882</v>
+        <v>122695655</v>
       </c>
       <c r="B70" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9842,37 +9879,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>479664</v>
+        <v>479759</v>
       </c>
       <c r="R70" t="n">
-        <v>7027326</v>
+        <v>7027292</v>
       </c>
       <c r="S70" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9906,7 +9948,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Växer på två granar intill en sälg med ymnig påväxt av lunglav.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9958,10 +10000,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122697286</v>
+        <v>122697882</v>
       </c>
       <c r="B71" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9974,42 +10016,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>479663</v>
+        <v>479664</v>
       </c>
       <c r="R71" t="n">
-        <v>7027246</v>
+        <v>7027326</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -10041,6 +10078,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -10057,22 +10099,22 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -10090,10 +10132,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122698275</v>
+        <v>122697773</v>
       </c>
       <c r="B72" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -10106,21 +10148,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -10130,10 +10172,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>479734</v>
+        <v>479617</v>
       </c>
       <c r="R72" t="n">
-        <v>7027357</v>
+        <v>7027326</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -10170,7 +10212,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -10189,22 +10231,22 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -10222,10 +10264,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122696876</v>
+        <v>122695752</v>
       </c>
       <c r="B73" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -10238,47 +10280,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>479628</v>
+        <v>479748</v>
       </c>
       <c r="R73" t="n">
-        <v>7027133</v>
+        <v>7027283</v>
       </c>
       <c r="S73" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -10310,11 +10342,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på stambasen av en gran. I äldre granskog med minst medelhöga till höga livsmiljövärden för tretåig hackspett. Även gott om liggande död ved här. Finns även skalade döda granar här som indikerar potentiella födosökspår efter tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -10341,12 +10368,12 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -10364,10 +10391,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122697862</v>
+        <v>122695354</v>
       </c>
       <c r="B74" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10380,21 +10407,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -10404,10 +10431,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>479630</v>
+        <v>479765</v>
       </c>
       <c r="R74" t="n">
-        <v>7027362</v>
+        <v>7027389</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10442,6 +10469,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>På en lutande krokig sälg.</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -10458,22 +10490,22 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10491,10 +10523,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122697666</v>
+        <v>122696290</v>
       </c>
       <c r="B75" t="n">
-        <v>90962</v>
+        <v>57631</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10507,36 +10539,36 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -10545,13 +10577,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>479632</v>
+        <v>479695</v>
       </c>
       <c r="R75" t="n">
-        <v>7027297</v>
+        <v>7027185</v>
       </c>
       <c r="S75" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -10583,6 +10615,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Observerad i flerskiktad äldre granskog.</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -10595,26 +10632,6 @@
       <c r="AH75" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -10632,10 +10649,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122695752</v>
+        <v>122697286</v>
       </c>
       <c r="B76" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10648,37 +10665,42 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>479748</v>
+        <v>479663</v>
       </c>
       <c r="R76" t="n">
-        <v>7027283</v>
+        <v>7027246</v>
       </c>
       <c r="S76" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -10726,22 +10748,22 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -10759,10 +10781,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122695354</v>
+        <v>122697862</v>
       </c>
       <c r="B77" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10775,21 +10797,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -10799,10 +10821,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>479765</v>
+        <v>479630</v>
       </c>
       <c r="R77" t="n">
-        <v>7027389</v>
+        <v>7027362</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10837,11 +10859,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>På en lutande krokig sälg.</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -10858,22 +10875,22 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10891,7 +10908,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122695655</v>
+        <v>122696057</v>
       </c>
       <c r="B78" t="n">
         <v>79847</v>
@@ -10936,13 +10953,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>479759</v>
+        <v>479675</v>
       </c>
       <c r="R78" t="n">
-        <v>7027292</v>
+        <v>7027261</v>
       </c>
       <c r="S78" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10976,7 +10993,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Växer på två granar intill en sälg med ymnig påväxt av lunglav.</t>
+          <t>På flera aspar.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10995,22 +11012,22 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -11028,7 +11045,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122697690</v>
+        <v>122698247</v>
       </c>
       <c r="B79" t="n">
         <v>78766</v>
@@ -11068,10 +11085,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>479640</v>
+        <v>479696</v>
       </c>
       <c r="R79" t="n">
-        <v>7027281</v>
+        <v>7027370</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -11155,7 +11172,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122696014</v>
+        <v>122695943</v>
       </c>
       <c r="B80" t="n">
         <v>78766</v>
@@ -11195,10 +11212,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>479718</v>
+        <v>479756</v>
       </c>
       <c r="R80" t="n">
-        <v>7027277</v>
+        <v>7027364</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -11282,7 +11299,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122696537</v>
+        <v>122696471</v>
       </c>
       <c r="B81" t="n">
         <v>57478</v>
@@ -11332,10 +11349,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>479669</v>
+        <v>479681</v>
       </c>
       <c r="R81" t="n">
-        <v>7027116</v>
+        <v>7027123</v>
       </c>
       <c r="S81" t="n">
         <v>8</v>
@@ -11372,7 +11389,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Äldre ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -11424,10 +11441,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122698232</v>
+        <v>122697666</v>
       </c>
       <c r="B82" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -11440,37 +11457,51 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>479698</v>
+        <v>479632</v>
       </c>
       <c r="R82" t="n">
-        <v>7027368</v>
+        <v>7027297</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -11528,12 +11559,12 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -11551,7 +11582,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122695703</v>
+        <v>122697966</v>
       </c>
       <c r="B83" t="n">
         <v>79847</v>
@@ -11596,13 +11627,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>479753</v>
+        <v>479660</v>
       </c>
       <c r="R83" t="n">
-        <v>7027296</v>
+        <v>7027363</v>
       </c>
       <c r="S83" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -11634,11 +11665,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglav på två knäckta sälgar.</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -11655,12 +11681,12 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM83" t="inlineStr">
@@ -11670,7 +11696,7 @@
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -11688,10 +11714,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122695273</v>
+        <v>122695669</v>
       </c>
       <c r="B84" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11704,47 +11730,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>479770</v>
+        <v>479761</v>
       </c>
       <c r="R84" t="n">
-        <v>7027401</v>
+        <v>7027298</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -11776,11 +11792,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -11807,12 +11818,12 @@
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -11830,7 +11841,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122695101</v>
+        <v>122696014</v>
       </c>
       <c r="B85" t="n">
         <v>78766</v>
@@ -11870,10 +11881,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>479696</v>
+        <v>479718</v>
       </c>
       <c r="R85" t="n">
-        <v>7027544</v>
+        <v>7027277</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11906,11 +11917,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11962,10 +11968,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122697966</v>
+        <v>122696303</v>
       </c>
       <c r="B86" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11978,42 +11984,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>479660</v>
+        <v>479685</v>
       </c>
       <c r="R86" t="n">
-        <v>7027363</v>
+        <v>7027165</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -12061,22 +12062,22 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -12094,10 +12095,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122697534</v>
+        <v>122696521</v>
       </c>
       <c r="B87" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -12110,37 +12111,47 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>479644</v>
+        <v>479674</v>
       </c>
       <c r="R87" t="n">
-        <v>7027243</v>
+        <v>7027109</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -12172,6 +12183,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Färska hackspår i stambasen av en smal gran i granskog med stora mängder liggande död ved.</t>
+        </is>
+      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
@@ -12183,7 +12199,7 @@
       </c>
       <c r="AH87" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ87" t="inlineStr">
@@ -12198,12 +12214,12 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -12221,10 +12237,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122696303</v>
+        <v>122697757</v>
       </c>
       <c r="B88" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -12237,37 +12253,42 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>479685</v>
+        <v>479615</v>
       </c>
       <c r="R88" t="n">
-        <v>7027165</v>
+        <v>7027315</v>
       </c>
       <c r="S88" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -12315,22 +12336,22 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -12348,10 +12369,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122696521</v>
+        <v>122695492</v>
       </c>
       <c r="B89" t="n">
-        <v>57494</v>
+        <v>79848</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -12364,32 +12385,27 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -12398,13 +12414,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>479674</v>
+        <v>479770</v>
       </c>
       <c r="R89" t="n">
-        <v>7027109</v>
+        <v>7027300</v>
       </c>
       <c r="S89" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -12438,7 +12454,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Färska hackspår i stambasen av en smal gran i granskog med stora mängder liggande död ved.</t>
+          <t>Växer på en lite smalare sälg intill lunglav.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -12457,22 +12473,22 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -12490,10 +12506,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122695516</v>
+        <v>122697455</v>
       </c>
       <c r="B90" t="n">
-        <v>79847</v>
+        <v>57494</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -12506,27 +12522,36 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>med soral</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -12535,13 +12560,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>479766</v>
+        <v>479680</v>
       </c>
       <c r="R90" t="n">
-        <v>7027310</v>
+        <v>7027206</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -12575,7 +12600,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Växer på en lite smalare sälg intill skrovellav.</t>
+          <t>Observation av en spillkråka som gav ifrån sig två olika lockläten. I gammal granskog med gott om asp och tall som utgör lämpliga substrat för bohål. Även bitvis relativt gott om död ved här.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -12590,26 +12615,6 @@
       <c r="AH90" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>

--- a/artfynd/A 60372-2024 artfynd.xlsx
+++ b/artfynd/A 60372-2024 artfynd.xlsx
@@ -2846,10 +2846,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122609386</v>
+        <v>122606649</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>79883</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2858,31 +2858,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>479699</v>
+        <v>479715</v>
       </c>
       <c r="R18" t="n">
-        <v>7027340</v>
+        <v>7027462</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen av en stående död gran. Volym stående död ved här som ger medelhögt till högt livsmiljövärde för tretåig hackspett.</t>
+          <t>En samling bålar på ca 2 meters höjd på aspens stam.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2950,22 +2950,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2983,10 +2983,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122606649</v>
+        <v>122609386</v>
       </c>
       <c r="B19" t="n">
-        <v>79883</v>
+        <v>57478</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2995,31 +2995,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -3028,10 +3028,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>479715</v>
+        <v>479699</v>
       </c>
       <c r="R19" t="n">
-        <v>7027462</v>
+        <v>7027340</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>En samling bålar på ca 2 meters höjd på aspens stam.</t>
+          <t>Äldre ringhack på stambasen av en stående död gran. Volym stående död ved här som ger medelhögt till högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3087,22 +3087,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3787,10 +3787,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122609753</v>
+        <v>122606169</v>
       </c>
       <c r="B25" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3803,37 +3803,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>479670</v>
+        <v>479698</v>
       </c>
       <c r="R25" t="n">
-        <v>7027294</v>
+        <v>7027398</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3865,6 +3870,11 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglav där vissa bålar är fertila med apothecier. På en gammal grovbarkad sälg med 54 cm i brösthöjdsdiameter.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3876,27 +3886,27 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3914,7 +3924,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122606169</v>
+        <v>122613055</v>
       </c>
       <c r="B26" t="n">
         <v>79847</v>
@@ -3948,24 +3958,22 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>479698</v>
+        <v>479722</v>
       </c>
       <c r="R26" t="n">
-        <v>7027398</v>
+        <v>7027290</v>
       </c>
       <c r="S26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3999,7 +4007,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav där vissa bålar är fertila med apothecier. På en gammal grovbarkad sälg med 54 cm i brösthöjdsdiameter.</t>
+          <t>Enstaka små bålar på en grov gammal asp.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4008,22 +4016,28 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
@@ -4033,7 +4047,7 @@
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Grov bark. # Populus tremula</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4051,10 +4065,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122613055</v>
+        <v>122609753</v>
       </c>
       <c r="B27" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4067,40 +4081,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>479722</v>
+        <v>479670</v>
       </c>
       <c r="R27" t="n">
-        <v>7027290</v>
+        <v>7027294</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4132,18 +4143,12 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Enstaka små bålar på en grov gammal asp.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -4152,29 +4157,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
-        </is>
-      </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4192,7 +4192,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122606696</v>
+        <v>122609252</v>
       </c>
       <c r="B28" t="n">
         <v>78766</v>
@@ -4232,10 +4232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>479678</v>
+        <v>479714</v>
       </c>
       <c r="R28" t="n">
-        <v>7027508</v>
+        <v>7027356</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4319,10 +4319,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122607115</v>
+        <v>122606696</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4335,47 +4335,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>479652</v>
+        <v>479678</v>
       </c>
       <c r="R29" t="n">
-        <v>7027551</v>
+        <v>7027508</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4407,11 +4397,6 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Både färska och äldre ringhack på stambasen. I skogsbeståndet runt fyndplatsen finns medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4438,12 +4423,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4603,10 +4588,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122609252</v>
+        <v>122607115</v>
       </c>
       <c r="B31" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4619,37 +4604,47 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>479714</v>
+        <v>479652</v>
       </c>
       <c r="R31" t="n">
-        <v>7027356</v>
+        <v>7027551</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4681,6 +4676,11 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Både färska och äldre ringhack på stambasen. I skogsbeståndet runt fyndplatsen finns medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4707,12 +4707,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4857,10 +4857,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122606280</v>
+        <v>122608462</v>
       </c>
       <c r="B33" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4873,37 +4873,47 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Kvarnbäcken, Kvarnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>479693</v>
+        <v>479583</v>
       </c>
       <c r="R33" t="n">
-        <v>7027399</v>
+        <v>7027629</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4937,7 +4947,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Skrovellav på en gammal grov sälg med 54 cm i brösthöjdsdiameter.</t>
+          <t>Äldre ringhack som bedöms vara 5-10 år gamla. På en gran med tydliga kådaflöden. Hyfsat gott om död ved här.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4951,27 +4961,27 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Branch on living tree # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5257,10 +5267,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122608462</v>
+        <v>122606280</v>
       </c>
       <c r="B36" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5273,47 +5283,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kvarnbäcken, Kvarnbäcken, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>479583</v>
+        <v>479693</v>
       </c>
       <c r="R36" t="n">
-        <v>7027629</v>
+        <v>7027399</v>
       </c>
       <c r="S36" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Äldre ringhack som bedöms vara 5-10 år gamla. På en gran med tydliga kådaflöden. Hyfsat gott om död ved här.</t>
+          <t>Skrovellav på en gammal grov sälg med 54 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5361,27 +5361,27 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Salix caprea</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>

--- a/artfynd/A 60372-2024 artfynd.xlsx
+++ b/artfynd/A 60372-2024 artfynd.xlsx
@@ -2846,10 +2846,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122606649</v>
+        <v>122609386</v>
       </c>
       <c r="B18" t="n">
-        <v>79883</v>
+        <v>57478</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2858,31 +2858,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>479715</v>
+        <v>479699</v>
       </c>
       <c r="R18" t="n">
-        <v>7027462</v>
+        <v>7027340</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>En samling bålar på ca 2 meters höjd på aspens stam.</t>
+          <t>Äldre ringhack på stambasen av en stående död gran. Volym stående död ved här som ger medelhögt till högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2950,22 +2950,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2983,10 +2983,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122609386</v>
+        <v>122606649</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>79883</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2995,31 +2995,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -3028,10 +3028,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>479699</v>
+        <v>479715</v>
       </c>
       <c r="R19" t="n">
-        <v>7027340</v>
+        <v>7027462</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen av en stående död gran. Volym stående död ved här som ger medelhögt till högt livsmiljövärde för tretåig hackspett.</t>
+          <t>En samling bålar på ca 2 meters höjd på aspens stam.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3087,22 +3087,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -4192,7 +4192,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122609252</v>
+        <v>122606696</v>
       </c>
       <c r="B28" t="n">
         <v>78766</v>
@@ -4232,10 +4232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>479714</v>
+        <v>479678</v>
       </c>
       <c r="R28" t="n">
-        <v>7027356</v>
+        <v>7027508</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4319,10 +4319,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122606696</v>
+        <v>122607115</v>
       </c>
       <c r="B29" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4335,37 +4335,47 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>479678</v>
+        <v>479652</v>
       </c>
       <c r="R29" t="n">
-        <v>7027508</v>
+        <v>7027551</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4397,6 +4407,11 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Både färska och äldre ringhack på stambasen. I skogsbeståndet runt fyndplatsen finns medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4423,12 +4438,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4588,10 +4603,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122607115</v>
+        <v>122609252</v>
       </c>
       <c r="B31" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4604,47 +4619,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>479652</v>
+        <v>479714</v>
       </c>
       <c r="R31" t="n">
-        <v>7027551</v>
+        <v>7027356</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4676,11 +4681,6 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Både färska och äldre ringhack på stambasen. I skogsbeståndet runt fyndplatsen finns medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4707,12 +4707,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>

--- a/artfynd/A 60372-2024 artfynd.xlsx
+++ b/artfynd/A 60372-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122609468</v>
+        <v>122613090</v>
       </c>
       <c r="B2" t="n">
         <v>79847</v>
@@ -709,24 +709,26 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>med soral</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>479731</v>
+        <v>479694</v>
       </c>
       <c r="R2" t="n">
-        <v>7027323</v>
+        <v>7027295</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,7 +762,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ymnigt med lunglav längs 7 meter på en något smalare sälg.</t>
+          <t>Ett gäng "knippen" med stora lunglavsbålar på en asp.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,6 +771,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,14 +780,19 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+        </is>
+      </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -794,7 +802,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -812,10 +820,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122606273</v>
+        <v>122609753</v>
       </c>
       <c r="B3" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,42 +836,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479698</v>
+        <v>479670</v>
       </c>
       <c r="R3" t="n">
-        <v>7027398</v>
+        <v>7027294</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -895,11 +898,6 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Skrovellav på en undertryck gran intill en gammal grov sälg.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -911,7 +909,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -949,10 +947,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122606026</v>
+        <v>122606696</v>
       </c>
       <c r="B4" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -965,39 +963,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479756</v>
+        <v>479678</v>
       </c>
       <c r="R4" t="n">
-        <v>7027477</v>
+        <v>7027508</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1058,12 +1051,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1081,10 +1074,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122607620</v>
+        <v>122609468</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1097,34 +1090,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>479635</v>
+        <v>479731</v>
       </c>
       <c r="R5" t="n">
-        <v>7027621</v>
+        <v>7027323</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1161,7 +1159,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ymnigt med lunglav längs 7 meter på en något smalare sälg.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1180,22 +1178,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1213,7 +1211,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122606232</v>
+        <v>122613066</v>
       </c>
       <c r="B6" t="n">
         <v>79847</v>
@@ -1247,24 +1245,26 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>479707</v>
+        <v>479702</v>
       </c>
       <c r="R6" t="n">
-        <v>7027397</v>
+        <v>7027288</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Fertil lunglav på en undertryck gran intill en gammal grov sälg.</t>
+          <t>Lunglav på en grovbarkad asp.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1307,32 +1307,38 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Populus tremula</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1350,7 +1356,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122607263</v>
+        <v>122607565</v>
       </c>
       <c r="B7" t="n">
         <v>78766</v>
@@ -1390,10 +1396,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>479655</v>
+        <v>479638</v>
       </c>
       <c r="R7" t="n">
-        <v>7027573</v>
+        <v>7027601</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1426,6 +1432,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1609,10 +1620,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122613090</v>
+        <v>122609386</v>
       </c>
       <c r="B9" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1625,44 +1636,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>479694</v>
+        <v>479699</v>
       </c>
       <c r="R9" t="n">
-        <v>7027295</v>
+        <v>7027340</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1696,7 +1705,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ett gäng "knippen" med stora lunglavsbålar på en asp.</t>
+          <t>Äldre ringhack på stambasen av en stående död gran. Volym stående död ved här som ger medelhögt till högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1705,7 +1714,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1714,29 +1722,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
-        </is>
-      </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1754,10 +1757,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122609281</v>
+        <v>122613032</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1770,37 +1773,44 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>479698</v>
+        <v>479731</v>
       </c>
       <c r="R10" t="n">
-        <v>7027342</v>
+        <v>7027291</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1834,7 +1844,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>En hel del bålar på en skadad sälg.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1843,6 +1853,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1851,24 +1862,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+        </is>
+      </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1886,10 +1902,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122612982</v>
+        <v>122607124</v>
       </c>
       <c r="B11" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1902,41 +1918,44 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>479738</v>
+        <v>479654</v>
       </c>
       <c r="R11" t="n">
-        <v>7027319</v>
+        <v>7027561</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1973,7 +1992,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Grova gamla lunglavsbålar på en lutande sälg.</t>
+          <t>Både äldre och färska ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1982,7 +2001,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1991,34 +2009,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
-        </is>
-      </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>En smal lutande sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En smal lutande sälg.</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2036,7 +2044,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122608343</v>
+        <v>122605930</v>
       </c>
       <c r="B12" t="n">
         <v>78766</v>
@@ -2072,17 +2080,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kvarnbäcken, Kvarnbäcken, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>479569</v>
+        <v>479743</v>
       </c>
       <c r="R12" t="n">
-        <v>7027674</v>
+        <v>7027472</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2116,7 +2124,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Långväxta bålar på flera träd.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2168,10 +2176,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122609496</v>
+        <v>122609837</v>
       </c>
       <c r="B13" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2184,42 +2192,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>479735</v>
+        <v>479643</v>
       </c>
       <c r="R13" t="n">
-        <v>7027318</v>
+        <v>7027326</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2249,6 +2252,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2300,7 +2308,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122613032</v>
+        <v>122606169</v>
       </c>
       <c r="B14" t="n">
         <v>79847</v>
@@ -2334,26 +2342,24 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>479731</v>
+        <v>479698</v>
       </c>
       <c r="R14" t="n">
-        <v>7027291</v>
+        <v>7027398</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2387,7 +2393,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>En hel del bålar på en skadad sälg.</t>
+          <t>Rikligt med lunglav där vissa bålar är fertila med apothecier. På en gammal grovbarkad sälg med 54 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2396,18 +2402,12 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2582,7 +2582,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122607879</v>
+        <v>122608343</v>
       </c>
       <c r="B16" t="n">
         <v>78766</v>
@@ -2618,17 +2618,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Kvarnbäcken, Kvarnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>479622</v>
+        <v>479569</v>
       </c>
       <c r="R16" t="n">
-        <v>7027648</v>
+        <v>7027674</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2714,7 +2714,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122609837</v>
+        <v>122613058</v>
       </c>
       <c r="B17" t="n">
         <v>78766</v>
@@ -2748,19 +2748,22 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>479643</v>
+        <v>479722</v>
       </c>
       <c r="R17" t="n">
-        <v>7027326</v>
+        <v>7027290</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2792,23 +2795,24 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -2846,7 +2850,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122609386</v>
+        <v>122608462</v>
       </c>
       <c r="B18" t="n">
         <v>57478</v>
@@ -2885,19 +2889,24 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Kvarnbäcken, Kvarnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>479699</v>
+        <v>479583</v>
       </c>
       <c r="R18" t="n">
-        <v>7027340</v>
+        <v>7027629</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2931,7 +2940,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen av en stående död gran. Volym stående död ved här som ger medelhögt till högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Äldre ringhack som bedöms vara 5-10 år gamla. På en gran med tydliga kådaflöden. Hyfsat gott om död ved här.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2960,12 +2969,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2983,10 +2992,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122606649</v>
+        <v>122613055</v>
       </c>
       <c r="B19" t="n">
-        <v>79883</v>
+        <v>79847</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2995,46 +3004,44 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>479715</v>
+        <v>479722</v>
       </c>
       <c r="R19" t="n">
-        <v>7027462</v>
+        <v>7027290</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3068,7 +3075,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>En samling bålar på ca 2 meters höjd på aspens stam.</t>
+          <t>Enstaka små bålar på en grov gammal asp.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3077,6 +3084,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3085,6 +3093,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+        </is>
+      </c>
       <c r="AJ19" t="inlineStr">
         <is>
           <t>asp</t>
@@ -3102,7 +3115,7 @@
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Grov bark. # Populus tremula</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3120,10 +3133,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122613066</v>
+        <v>122607620</v>
       </c>
       <c r="B20" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3136,44 +3149,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>479702</v>
+        <v>479635</v>
       </c>
       <c r="R20" t="n">
-        <v>7027288</v>
+        <v>7027621</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3207,7 +3213,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Lunglav på en grovbarkad asp.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3216,7 +3222,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3225,29 +3230,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
-        </is>
-      </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122606631</v>
+        <v>122606431</v>
       </c>
       <c r="B21" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3281,29 +3281,24 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
@@ -3313,7 +3308,7 @@
         <v>479711</v>
       </c>
       <c r="R21" t="n">
-        <v>7027473</v>
+        <v>7027387</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3350,7 +3345,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en asp.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3364,27 +3359,27 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3402,7 +3397,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122606334</v>
+        <v>122609252</v>
       </c>
       <c r="B22" t="n">
         <v>78766</v>
@@ -3442,10 +3437,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>479692</v>
+        <v>479714</v>
       </c>
       <c r="R22" t="n">
-        <v>7027424</v>
+        <v>7027356</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3491,7 +3486,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -3529,10 +3524,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122605930</v>
+        <v>122606273</v>
       </c>
       <c r="B23" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3545,37 +3540,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>479743</v>
+        <v>479698</v>
       </c>
       <c r="R23" t="n">
-        <v>7027472</v>
+        <v>7027398</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera träd.</t>
+          <t>Skrovellav på en undertryck gran intill en gammal grov sälg.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -3661,10 +3661,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122607246</v>
+        <v>122606232</v>
       </c>
       <c r="B24" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3677,36 +3677,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3715,10 +3706,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>479659</v>
+        <v>479707</v>
       </c>
       <c r="R24" t="n">
-        <v>7027556</v>
+        <v>7027397</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3755,7 +3746,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Observerades i flerskiktad granskog.</t>
+          <t>Fertil lunglav på en undertryck gran intill en gammal grov sälg.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3769,7 +3760,27 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3787,7 +3798,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122606169</v>
+        <v>122606631</v>
       </c>
       <c r="B25" t="n">
         <v>79847</v>
@@ -3823,7 +3834,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3832,13 +3843,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>479698</v>
+        <v>479711</v>
       </c>
       <c r="R25" t="n">
-        <v>7027398</v>
+        <v>7027473</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3872,7 +3883,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav där vissa bålar är fertila med apothecier. På en gammal grovbarkad sälg med 54 cm i brösthöjdsdiameter.</t>
+          <t>Enstaka bålar på en asp.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3886,17 +3897,17 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
@@ -3906,7 +3917,7 @@
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3924,10 +3935,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122613055</v>
+        <v>122606649</v>
       </c>
       <c r="B26" t="n">
-        <v>79847</v>
+        <v>79883</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3936,44 +3947,46 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>479722</v>
+        <v>479715</v>
       </c>
       <c r="R26" t="n">
-        <v>7027290</v>
+        <v>7027462</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4007,7 +4020,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Enstaka små bålar på en grov gammal asp.</t>
+          <t>En samling bålar på ca 2 meters höjd på aspens stam.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4016,7 +4029,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -4025,11 +4037,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
-        </is>
-      </c>
       <c r="AJ26" t="inlineStr">
         <is>
           <t>asp</t>
@@ -4047,7 +4054,7 @@
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Populus tremula</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4065,7 +4072,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122609753</v>
+        <v>122609281</v>
       </c>
       <c r="B27" t="n">
         <v>78766</v>
@@ -4105,13 +4112,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>479670</v>
+        <v>479698</v>
       </c>
       <c r="R27" t="n">
-        <v>7027294</v>
+        <v>7027342</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4141,6 +4148,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4192,10 +4204,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122606696</v>
+        <v>122612982</v>
       </c>
       <c r="B28" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4208,34 +4220,41 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>479678</v>
+        <v>479738</v>
       </c>
       <c r="R28" t="n">
-        <v>7027508</v>
+        <v>7027319</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4270,12 +4289,18 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Grova gamla lunglavsbålar på en lutande sälg.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4284,24 +4309,34 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+        </is>
+      </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>En smal lutande sälg.</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En smal lutande sälg.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4319,10 +4354,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122607115</v>
+        <v>122608509</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>79751</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4331,51 +4366,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>479652</v>
+        <v>479617</v>
       </c>
       <c r="R29" t="n">
-        <v>7027551</v>
+        <v>7027598</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4407,11 +4432,6 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Både färska och äldre ringhack på stambasen. I skogsbeståndet runt fyndplatsen finns medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4428,22 +4448,22 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4461,10 +4481,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122607124</v>
+        <v>122606334</v>
       </c>
       <c r="B30" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4477,44 +4497,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>479654</v>
+        <v>479692</v>
       </c>
       <c r="R30" t="n">
-        <v>7027561</v>
+        <v>7027424</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4549,11 +4559,6 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Både äldre och färska ringhack på stambasen.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4565,7 +4570,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4580,12 +4585,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4603,10 +4608,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122609252</v>
+        <v>122607246</v>
       </c>
       <c r="B31" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4619,34 +4624,48 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>479714</v>
+        <v>479659</v>
       </c>
       <c r="R31" t="n">
-        <v>7027356</v>
+        <v>7027556</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4681,6 +4700,11 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Observerades i flerskiktad granskog.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4693,26 +4717,6 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4730,10 +4734,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122606868</v>
+        <v>122606280</v>
       </c>
       <c r="B32" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4746,21 +4750,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4770,10 +4774,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>479661</v>
+        <v>479693</v>
       </c>
       <c r="R32" t="n">
-        <v>7027516</v>
+        <v>7027399</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4808,6 +4812,11 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Skrovellav på en gammal grov sälg med 54 cm i brösthöjdsdiameter.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4824,12 +4833,12 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
@@ -4839,7 +4848,7 @@
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Branch on living tree # Salix caprea</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4857,10 +4866,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122608462</v>
+        <v>122606026</v>
       </c>
       <c r="B33" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4873,47 +4882,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kvarnbäcken, Kvarnbäcken, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>479583</v>
+        <v>479756</v>
       </c>
       <c r="R33" t="n">
-        <v>7027629</v>
+        <v>7027477</v>
       </c>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4943,11 +4947,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack som bedöms vara 5-10 år gamla. På en gran med tydliga kådaflöden. Hyfsat gott om död ved här.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4999,10 +4998,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122606431</v>
+        <v>122609496</v>
       </c>
       <c r="B34" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5015,37 +5014,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>479711</v>
+        <v>479735</v>
       </c>
       <c r="R34" t="n">
-        <v>7027387</v>
+        <v>7027318</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5077,11 +5081,6 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -5093,7 +5092,7 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
@@ -5131,7 +5130,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122613058</v>
+        <v>122607879</v>
       </c>
       <c r="B35" t="n">
         <v>78766</v>
@@ -5165,22 +5164,19 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>479722</v>
+        <v>479622</v>
       </c>
       <c r="R35" t="n">
-        <v>7027290</v>
+        <v>7027648</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5212,24 +5208,23 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -5267,10 +5262,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122606280</v>
+        <v>122606868</v>
       </c>
       <c r="B36" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5283,21 +5278,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5307,10 +5302,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>479693</v>
+        <v>479661</v>
       </c>
       <c r="R36" t="n">
-        <v>7027399</v>
+        <v>7027516</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5345,11 +5340,6 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Skrovellav på en gammal grov sälg med 54 cm i brösthöjdsdiameter.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -5366,12 +5356,12 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
@@ -5381,7 +5371,7 @@
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Branch on living tree # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5399,7 +5389,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122607565</v>
+        <v>122607162</v>
       </c>
       <c r="B37" t="n">
         <v>78766</v>
@@ -5439,10 +5429,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>479638</v>
+        <v>479650</v>
       </c>
       <c r="R37" t="n">
-        <v>7027601</v>
+        <v>7027549</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5479,7 +5469,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5531,10 +5521,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122608509</v>
+        <v>122607263</v>
       </c>
       <c r="B38" t="n">
-        <v>79751</v>
+        <v>78766</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5543,25 +5533,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5571,10 +5561,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>479617</v>
+        <v>479655</v>
       </c>
       <c r="R38" t="n">
-        <v>7027598</v>
+        <v>7027573</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5625,22 +5615,22 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5658,10 +5648,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122607162</v>
+        <v>122607115</v>
       </c>
       <c r="B39" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5674,37 +5664,47 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>479650</v>
+        <v>479652</v>
       </c>
       <c r="R39" t="n">
-        <v>7027549</v>
+        <v>7027551</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Både färska och äldre ringhack på stambasen. I skogsbeståndet runt fyndplatsen finns medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -6072,10 +6072,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122609714</v>
+        <v>122609073</v>
       </c>
       <c r="B42" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6088,49 +6088,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>479677</v>
+        <v>479738</v>
       </c>
       <c r="R42" t="n">
-        <v>7027303</v>
+        <v>7027404</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6164,7 +6157,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Observation i flerskiktad granskog med stående murkna björkhögstubbar som är gynnsamt för talltitans häckning.</t>
+          <t>På en smal sälg.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6181,9 +6174,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6201,10 +6209,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122608090</v>
+        <v>122607410</v>
       </c>
       <c r="B43" t="n">
-        <v>79751</v>
+        <v>57478</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6213,41 +6221,51 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>479602</v>
+        <v>479644</v>
       </c>
       <c r="R43" t="n">
-        <v>7027640</v>
+        <v>7027599</v>
       </c>
       <c r="S43" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6279,6 +6297,11 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Både äldre och färska ringhack på stambasen. I skogsbeståndet runt fyndplatsen finns medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -6295,22 +6318,22 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6328,10 +6351,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122609140</v>
+        <v>122608090</v>
       </c>
       <c r="B44" t="n">
-        <v>79847</v>
+        <v>79751</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6340,46 +6363,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>479723</v>
+        <v>479602</v>
       </c>
       <c r="R44" t="n">
-        <v>7027396</v>
+        <v>7027640</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6411,11 +6429,6 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ymnig påväxt av lunglav längs flera meter på en gammal sälg. Fertila bålar med apothecier.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -6432,12 +6445,12 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
@@ -6447,7 +6460,7 @@
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6465,10 +6478,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122607410</v>
+        <v>122613271</v>
       </c>
       <c r="B45" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6481,47 +6494,44 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>479644</v>
+        <v>479628</v>
       </c>
       <c r="R45" t="n">
-        <v>7027599</v>
+        <v>7027338</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6555,7 +6565,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Både äldre och färska ringhack på stambasen. I skogsbeståndet runt fyndplatsen finns medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Riklig påväxt av lunglavsbålar på en gammal sälg. Vissa bålar är fertila med apothecier. Här växer även rikligt med lunglav på gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6564,6 +6574,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6572,24 +6583,34 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+        </is>
+      </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL45" t="inlineStr">
+        <is>
+          <t>En gammal grov sälg.</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea # En gammal grov sälg.</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6752,10 +6773,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122613281</v>
+        <v>122609714</v>
       </c>
       <c r="B47" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6768,40 +6789,49 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>479628</v>
+        <v>479677</v>
       </c>
       <c r="R47" t="n">
-        <v>7027338</v>
+        <v>7027303</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6835,7 +6865,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Med långväxta bålar och på flera granar.</t>
+          <t>Observation i flerskiktad granskog med stående murkna björkhögstubbar som är gynnsamt för talltitans häckning.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6844,7 +6874,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6856,26 +6885,6 @@
       <c r="AI47" t="inlineStr">
         <is>
           <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6893,10 +6902,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122609073</v>
+        <v>122613281</v>
       </c>
       <c r="B48" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6909,42 +6918,40 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>479738</v>
+        <v>479628</v>
       </c>
       <c r="R48" t="n">
-        <v>7027404</v>
+        <v>7027338</v>
       </c>
       <c r="S48" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6978,7 +6985,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På en smal sälg.</t>
+          <t>Med långväxta bålar och på flera granar.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6987,6 +6994,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6995,24 +7003,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+        </is>
+      </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -7030,7 +7043,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122613271</v>
+        <v>122609140</v>
       </c>
       <c r="B49" t="n">
         <v>79847</v>
@@ -7064,26 +7077,24 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
           <t>med apothecier</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>479628</v>
+        <v>479723</v>
       </c>
       <c r="R49" t="n">
-        <v>7027338</v>
+        <v>7027396</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -7117,7 +7128,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Riklig påväxt av lunglavsbålar på en gammal sälg. Vissa bålar är fertila med apothecier. Här växer även rikligt med lunglav på gran.</t>
+          <t>Ymnig påväxt av lunglav längs flera meter på en gammal sälg. Fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7126,7 +7137,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -7135,11 +7145,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
-        </is>
-      </c>
       <c r="AJ49" t="inlineStr">
         <is>
           <t>sälg</t>
@@ -7150,11 +7155,6 @@
           <t>Salix caprea</t>
         </is>
       </c>
-      <c r="AL49" t="inlineStr">
-        <is>
-          <t>En gammal grov sälg.</t>
-        </is>
-      </c>
       <c r="AM49" t="inlineStr">
         <is>
           <t>Bark på levande träd</t>
@@ -7162,7 +7162,7 @@
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea # En gammal grov sälg.</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7325,7 +7325,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122698085</v>
+        <v>122697690</v>
       </c>
       <c r="B51" t="n">
         <v>78766</v>
@@ -7365,10 +7365,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>479659</v>
+        <v>479640</v>
       </c>
       <c r="R51" t="n">
-        <v>7027303</v>
+        <v>7027281</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7452,10 +7452,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122695682</v>
+        <v>122697352</v>
       </c>
       <c r="B52" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7468,39 +7468,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>479763</v>
+        <v>479674</v>
       </c>
       <c r="R52" t="n">
-        <v>7027300</v>
+        <v>7027178</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7535,11 +7530,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>På en smal krokig sälg.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -7556,22 +7546,22 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7589,10 +7579,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122698275</v>
+        <v>122697773</v>
       </c>
       <c r="B53" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7605,21 +7595,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7629,10 +7619,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>479734</v>
+        <v>479617</v>
       </c>
       <c r="R53" t="n">
-        <v>7027357</v>
+        <v>7027326</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7669,7 +7659,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7688,22 +7678,22 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7721,7 +7711,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122695075</v>
+        <v>122698085</v>
       </c>
       <c r="B54" t="n">
         <v>78766</v>
@@ -7761,10 +7751,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>479699</v>
+        <v>479659</v>
       </c>
       <c r="R54" t="n">
-        <v>7027521</v>
+        <v>7027303</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7797,11 +7787,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7853,10 +7838,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122696876</v>
+        <v>122696521</v>
       </c>
       <c r="B55" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7869,16 +7854,16 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -7903,10 +7888,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>479628</v>
+        <v>479674</v>
       </c>
       <c r="R55" t="n">
-        <v>7027133</v>
+        <v>7027109</v>
       </c>
       <c r="S55" t="n">
         <v>8</v>
@@ -7943,7 +7928,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen av en gran. I äldre granskog med minst medelhöga till höga livsmiljövärden för tretåig hackspett. Även gott om liggande död ved här. Finns även skalade döda granar här som indikerar potentiella födosökspår efter tretåig hackspett.</t>
+          <t>Färska hackspår i stambasen av en smal gran i granskog med stora mängder liggande död ved.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7995,10 +7980,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122697690</v>
+        <v>122695669</v>
       </c>
       <c r="B56" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -8011,21 +7996,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -8035,13 +8020,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>479640</v>
+        <v>479761</v>
       </c>
       <c r="R56" t="n">
-        <v>7027281</v>
+        <v>7027298</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -8122,10 +8107,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122695011</v>
+        <v>122697666</v>
       </c>
       <c r="B57" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -8138,37 +8123,51 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>479729</v>
+        <v>479632</v>
       </c>
       <c r="R57" t="n">
-        <v>7027486</v>
+        <v>7027297</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -8200,11 +8199,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -8231,12 +8225,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8254,10 +8248,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122695602</v>
+        <v>122696303</v>
       </c>
       <c r="B58" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8270,42 +8264,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>479774</v>
+        <v>479685</v>
       </c>
       <c r="R58" t="n">
-        <v>7027322</v>
+        <v>7027165</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8337,11 +8326,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ymnigt med lunglav på en gammal sälg med fårad bark.</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -8358,22 +8342,22 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8391,10 +8375,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122696537</v>
+        <v>122695943</v>
       </c>
       <c r="B59" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8407,47 +8391,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>479669</v>
+        <v>479756</v>
       </c>
       <c r="R59" t="n">
-        <v>7027116</v>
+        <v>7027364</v>
       </c>
       <c r="S59" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8479,11 +8453,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -8510,12 +8479,12 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8533,10 +8502,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122695273</v>
+        <v>122697966</v>
       </c>
       <c r="B60" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8549,32 +8518,27 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -8583,10 +8547,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>479770</v>
+        <v>479660</v>
       </c>
       <c r="R60" t="n">
-        <v>7027401</v>
+        <v>7027363</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8621,11 +8585,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -8642,22 +8601,22 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8675,10 +8634,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122697534</v>
+        <v>122696471</v>
       </c>
       <c r="B61" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8691,37 +8650,47 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>479644</v>
+        <v>479681</v>
       </c>
       <c r="R61" t="n">
-        <v>7027243</v>
+        <v>7027123</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8753,6 +8722,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på stambasen.</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -8764,7 +8738,7 @@
       </c>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ61" t="inlineStr">
@@ -8779,12 +8753,12 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8802,7 +8776,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122695101</v>
+        <v>122695752</v>
       </c>
       <c r="B62" t="n">
         <v>78766</v>
@@ -8842,13 +8816,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>479696</v>
+        <v>479748</v>
       </c>
       <c r="R62" t="n">
-        <v>7027544</v>
+        <v>7027283</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8878,11 +8852,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8934,10 +8903,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122696111</v>
+        <v>122696290</v>
       </c>
       <c r="B63" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8950,34 +8919,48 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>479694</v>
+        <v>479695</v>
       </c>
       <c r="R63" t="n">
-        <v>7027236</v>
+        <v>7027185</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -9012,6 +8995,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Observerad i flerskiktad äldre granskog.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -9024,26 +9012,6 @@
       <c r="AH63" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -9061,10 +9029,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122695516</v>
+        <v>122697455</v>
       </c>
       <c r="B64" t="n">
-        <v>79847</v>
+        <v>57494</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -9077,27 +9045,36 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>med soral</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -9106,13 +9083,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>479766</v>
+        <v>479680</v>
       </c>
       <c r="R64" t="n">
-        <v>7027310</v>
+        <v>7027206</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -9146,7 +9123,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Växer på en lite smalare sälg intill skrovellav.</t>
+          <t>Observation av en spillkråka som gav ifrån sig två olika lockläten. I gammal granskog med gott om asp och tall som utgör lämpliga substrat för bohål. Även bitvis relativt gott om död ved här.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9161,26 +9138,6 @@
       <c r="AH64" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -9198,10 +9155,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122695322</v>
+        <v>122695354</v>
       </c>
       <c r="B65" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9214,39 +9171,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>479771</v>
+        <v>479765</v>
       </c>
       <c r="R65" t="n">
-        <v>7027387</v>
+        <v>7027389</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -9335,10 +9287,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122695926</v>
+        <v>122697757</v>
       </c>
       <c r="B66" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9351,21 +9303,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -9380,10 +9332,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>479752</v>
+        <v>479615</v>
       </c>
       <c r="R66" t="n">
-        <v>7027344</v>
+        <v>7027315</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9416,11 +9368,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ymnigt med lunglav på en gammal sälg.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9472,10 +9419,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122695703</v>
+        <v>122695492</v>
       </c>
       <c r="B67" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9488,21 +9435,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -9517,13 +9464,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>479753</v>
+        <v>479770</v>
       </c>
       <c r="R67" t="n">
-        <v>7027296</v>
+        <v>7027300</v>
       </c>
       <c r="S67" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -9557,7 +9504,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på två knäckta sälgar.</t>
+          <t>Växer på en lite smalare sälg intill lunglav.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9609,7 +9556,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122697352</v>
+        <v>122698232</v>
       </c>
       <c r="B68" t="n">
         <v>78766</v>
@@ -9649,10 +9596,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>479674</v>
+        <v>479698</v>
       </c>
       <c r="R68" t="n">
-        <v>7027178</v>
+        <v>7027368</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9736,10 +9683,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122698232</v>
+        <v>122696537</v>
       </c>
       <c r="B69" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9752,37 +9699,47 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>479698</v>
+        <v>479669</v>
       </c>
       <c r="R69" t="n">
-        <v>7027368</v>
+        <v>7027116</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9814,6 +9771,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -9840,12 +9802,12 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9863,10 +9825,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122695655</v>
+        <v>122697534</v>
       </c>
       <c r="B70" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9879,42 +9841,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>479759</v>
+        <v>479644</v>
       </c>
       <c r="R70" t="n">
-        <v>7027292</v>
+        <v>7027243</v>
       </c>
       <c r="S70" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9946,11 +9903,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Växer på två granar intill en sälg med ymnig påväxt av lunglav.</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -9962,7 +9914,7 @@
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ70" t="inlineStr">
@@ -10000,10 +9952,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122697882</v>
+        <v>122696057</v>
       </c>
       <c r="B71" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -10016,37 +9968,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>479664</v>
+        <v>479675</v>
       </c>
       <c r="R71" t="n">
-        <v>7027326</v>
+        <v>7027261</v>
       </c>
       <c r="S71" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -10080,7 +10037,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På flera aspar.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -10099,22 +10056,22 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -10132,10 +10089,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122697773</v>
+        <v>122698247</v>
       </c>
       <c r="B72" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -10148,21 +10105,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -10172,10 +10129,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>479617</v>
+        <v>479696</v>
       </c>
       <c r="R72" t="n">
-        <v>7027326</v>
+        <v>7027370</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -10210,11 +10167,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -10231,22 +10183,22 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -10264,7 +10216,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122695752</v>
+        <v>122695075</v>
       </c>
       <c r="B73" t="n">
         <v>78766</v>
@@ -10304,13 +10256,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>479748</v>
+        <v>479699</v>
       </c>
       <c r="R73" t="n">
-        <v>7027283</v>
+        <v>7027521</v>
       </c>
       <c r="S73" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -10340,6 +10292,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10391,10 +10348,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122695354</v>
+        <v>122696111</v>
       </c>
       <c r="B74" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10407,21 +10364,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -10431,10 +10388,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>479765</v>
+        <v>479694</v>
       </c>
       <c r="R74" t="n">
-        <v>7027389</v>
+        <v>7027236</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10469,11 +10426,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På en lutande krokig sälg.</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -10490,22 +10442,22 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10523,10 +10475,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122696290</v>
+        <v>122695602</v>
       </c>
       <c r="B75" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10539,36 +10491,27 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -10577,10 +10520,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>479695</v>
+        <v>479774</v>
       </c>
       <c r="R75" t="n">
-        <v>7027185</v>
+        <v>7027322</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10617,7 +10560,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Observerad i flerskiktad äldre granskog.</t>
+          <t>Ymnigt med lunglav på en gammal sälg med fårad bark.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10632,6 +10575,26 @@
       <c r="AH75" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -10649,10 +10612,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122697286</v>
+        <v>122695101</v>
       </c>
       <c r="B76" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10665,39 +10628,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>479663</v>
+        <v>479696</v>
       </c>
       <c r="R76" t="n">
-        <v>7027246</v>
+        <v>7027544</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10732,6 +10690,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -10748,22 +10711,22 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -10781,10 +10744,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122697862</v>
+        <v>122696876</v>
       </c>
       <c r="B77" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10797,37 +10760,47 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>479630</v>
+        <v>479628</v>
       </c>
       <c r="R77" t="n">
-        <v>7027362</v>
+        <v>7027133</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -10859,6 +10832,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på stambasen av en gran. I äldre granskog med minst medelhöga till höga livsmiljövärden för tretåig hackspett. Även gott om liggande död ved här. Finns även skalade döda granar här som indikerar potentiella födosökspår efter tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -10885,12 +10863,12 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10908,10 +10886,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122696057</v>
+        <v>122695011</v>
       </c>
       <c r="B78" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10924,39 +10902,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>479675</v>
+        <v>479729</v>
       </c>
       <c r="R78" t="n">
-        <v>7027261</v>
+        <v>7027486</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10993,7 +10966,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På flera aspar.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -11012,22 +10985,22 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -11045,10 +11018,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122698247</v>
+        <v>122697286</v>
       </c>
       <c r="B79" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -11061,34 +11034,39 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>479696</v>
+        <v>479663</v>
       </c>
       <c r="R79" t="n">
-        <v>7027370</v>
+        <v>7027246</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -11139,22 +11117,22 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -11172,10 +11150,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122695943</v>
+        <v>122695682</v>
       </c>
       <c r="B80" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -11188,34 +11166,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>479756</v>
+        <v>479763</v>
       </c>
       <c r="R80" t="n">
-        <v>7027364</v>
+        <v>7027300</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -11250,6 +11233,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>På en smal krokig sälg.</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -11266,22 +11254,22 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -11299,10 +11287,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122696471</v>
+        <v>122696014</v>
       </c>
       <c r="B81" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -11315,47 +11303,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>479681</v>
+        <v>479718</v>
       </c>
       <c r="R81" t="n">
-        <v>7027123</v>
+        <v>7027277</v>
       </c>
       <c r="S81" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -11387,11 +11365,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på stambasen.</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -11418,12 +11391,12 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -11441,10 +11414,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122697666</v>
+        <v>122697862</v>
       </c>
       <c r="B82" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -11457,51 +11430,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>479632</v>
+        <v>479630</v>
       </c>
       <c r="R82" t="n">
-        <v>7027297</v>
+        <v>7027362</v>
       </c>
       <c r="S82" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -11559,12 +11518,12 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -11582,7 +11541,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122697966</v>
+        <v>122695322</v>
       </c>
       <c r="B83" t="n">
         <v>79847</v>
@@ -11627,10 +11586,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>479660</v>
+        <v>479771</v>
       </c>
       <c r="R83" t="n">
-        <v>7027363</v>
+        <v>7027387</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11665,6 +11624,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>På en lutande krokig sälg.</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -11681,12 +11645,12 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM83" t="inlineStr">
@@ -11696,7 +11660,7 @@
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -11714,10 +11678,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122695669</v>
+        <v>122695273</v>
       </c>
       <c r="B84" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11730,37 +11694,47 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>479761</v>
+        <v>479770</v>
       </c>
       <c r="R84" t="n">
-        <v>7027298</v>
+        <v>7027401</v>
       </c>
       <c r="S84" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -11792,6 +11766,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -11818,12 +11797,12 @@
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -11841,10 +11820,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122696014</v>
+        <v>122695703</v>
       </c>
       <c r="B85" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11857,37 +11836,42 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>479718</v>
+        <v>479753</v>
       </c>
       <c r="R85" t="n">
-        <v>7027277</v>
+        <v>7027296</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -11919,6 +11903,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglav på två knäckta sälgar.</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -11935,22 +11924,22 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -11968,10 +11957,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122696303</v>
+        <v>122695926</v>
       </c>
       <c r="B86" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11984,37 +11973,42 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>479685</v>
+        <v>479752</v>
       </c>
       <c r="R86" t="n">
-        <v>7027165</v>
+        <v>7027344</v>
       </c>
       <c r="S86" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -12046,6 +12040,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Ymnigt med lunglav på en gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -12062,22 +12061,22 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -12095,10 +12094,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122696521</v>
+        <v>122695655</v>
       </c>
       <c r="B87" t="n">
-        <v>57494</v>
+        <v>79847</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -12111,32 +12110,27 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -12145,13 +12139,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>479674</v>
+        <v>479759</v>
       </c>
       <c r="R87" t="n">
-        <v>7027109</v>
+        <v>7027292</v>
       </c>
       <c r="S87" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -12185,7 +12179,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Färska hackspår i stambasen av en smal gran i granskog med stora mängder liggande död ved.</t>
+          <t>Växer på två granar intill en sälg med ymnig påväxt av lunglav.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -12214,12 +12208,12 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -12237,10 +12231,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122697757</v>
+        <v>122697882</v>
       </c>
       <c r="B88" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -12253,42 +12247,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>479615</v>
+        <v>479664</v>
       </c>
       <c r="R88" t="n">
-        <v>7027315</v>
+        <v>7027326</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -12320,6 +12309,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
@@ -12336,22 +12330,22 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -12369,10 +12363,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122695492</v>
+        <v>122695516</v>
       </c>
       <c r="B89" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -12385,21 +12379,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -12414,10 +12408,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>479770</v>
+        <v>479766</v>
       </c>
       <c r="R89" t="n">
-        <v>7027300</v>
+        <v>7027310</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -12454,7 +12448,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Växer på en lite smalare sälg intill lunglav.</t>
+          <t>Växer på en lite smalare sälg intill skrovellav.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -12506,10 +12500,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122697455</v>
+        <v>122698275</v>
       </c>
       <c r="B90" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -12522,51 +12516,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>479680</v>
+        <v>479734</v>
       </c>
       <c r="R90" t="n">
-        <v>7027206</v>
+        <v>7027357</v>
       </c>
       <c r="S90" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -12600,7 +12580,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Observation av en spillkråka som gav ifrån sig två olika lockläten. I gammal granskog med gott om asp och tall som utgör lämpliga substrat för bohål. Även bitvis relativt gott om död ved här.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -12615,6 +12595,26 @@
       <c r="AH90" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM90" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>

--- a/artfynd/A 60372-2024 artfynd.xlsx
+++ b/artfynd/A 60372-2024 artfynd.xlsx
@@ -2176,10 +2176,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122609837</v>
+        <v>122606169</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2192,37 +2192,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>479643</v>
+        <v>479698</v>
       </c>
       <c r="R13" t="n">
-        <v>7027326</v>
+        <v>7027398</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2256,7 +2261,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Rikligt med lunglav där vissa bålar är fertila med apothecier. På en gammal grovbarkad sälg med 54 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2270,27 +2275,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2308,7 +2313,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122606169</v>
+        <v>122609424</v>
       </c>
       <c r="B14" t="n">
         <v>79847</v>
@@ -2353,13 +2358,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>479698</v>
+        <v>479729</v>
       </c>
       <c r="R14" t="n">
-        <v>7027398</v>
+        <v>7027353</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2393,7 +2398,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav där vissa bålar är fertila med apothecier. På en gammal grovbarkad sälg med 54 cm i brösthöjdsdiameter.</t>
+          <t>Fertila bålar på en smal böjd sälg.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2407,7 +2412,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2445,10 +2450,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122609424</v>
+        <v>122609837</v>
       </c>
       <c r="B15" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2461,39 +2466,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>479729</v>
+        <v>479643</v>
       </c>
       <c r="R15" t="n">
-        <v>7027353</v>
+        <v>7027326</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Fertila bålar på en smal böjd sälg.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2549,22 +2549,22 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -4734,10 +4734,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122606280</v>
+        <v>122606026</v>
       </c>
       <c r="B32" t="n">
-        <v>79848</v>
+        <v>90970</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4750,34 +4750,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>479693</v>
+        <v>479756</v>
       </c>
       <c r="R32" t="n">
-        <v>7027399</v>
+        <v>7027477</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4812,11 +4817,6 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Skrovellav på en gammal grov sälg med 54 cm i brösthöjdsdiameter.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4828,27 +4828,27 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Branch on living tree # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4866,10 +4866,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122606026</v>
+        <v>122606280</v>
       </c>
       <c r="B33" t="n">
-        <v>90970</v>
+        <v>79848</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4882,39 +4882,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>479756</v>
+        <v>479693</v>
       </c>
       <c r="R33" t="n">
-        <v>7027477</v>
+        <v>7027399</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4949,6 +4944,11 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Skrovellav på en gammal grov sälg med 54 cm i brösthöjdsdiameter.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4960,27 +4960,27 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Salix caprea</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -7980,10 +7980,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122695669</v>
+        <v>122697666</v>
       </c>
       <c r="B56" t="n">
-        <v>79848</v>
+        <v>90970</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7996,34 +7996,48 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>479761</v>
+        <v>479632</v>
       </c>
       <c r="R56" t="n">
-        <v>7027298</v>
+        <v>7027297</v>
       </c>
       <c r="S56" t="n">
         <v>13</v>
@@ -8084,12 +8098,12 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -8107,10 +8121,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122697666</v>
+        <v>122696303</v>
       </c>
       <c r="B57" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -8123,51 +8137,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>479632</v>
+        <v>479685</v>
       </c>
       <c r="R57" t="n">
-        <v>7027297</v>
+        <v>7027165</v>
       </c>
       <c r="S57" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -8225,12 +8225,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8248,10 +8248,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122696303</v>
+        <v>122695669</v>
       </c>
       <c r="B58" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8264,21 +8264,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -8288,13 +8288,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>479685</v>
+        <v>479761</v>
       </c>
       <c r="R58" t="n">
-        <v>7027165</v>
+        <v>7027298</v>
       </c>
       <c r="S58" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8634,10 +8634,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122696471</v>
+        <v>122695752</v>
       </c>
       <c r="B61" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8650,47 +8650,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>479681</v>
+        <v>479748</v>
       </c>
       <c r="R61" t="n">
-        <v>7027123</v>
+        <v>7027283</v>
       </c>
       <c r="S61" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8722,11 +8712,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på stambasen.</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -8753,12 +8738,12 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8776,10 +8761,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122695752</v>
+        <v>122696471</v>
       </c>
       <c r="B62" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8792,37 +8777,47 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>479748</v>
+        <v>479681</v>
       </c>
       <c r="R62" t="n">
-        <v>7027283</v>
+        <v>7027123</v>
       </c>
       <c r="S62" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8854,6 +8849,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på stambasen.</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -8880,12 +8880,12 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -9556,7 +9556,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122698232</v>
+        <v>122697534</v>
       </c>
       <c r="B68" t="n">
         <v>78766</v>
@@ -9596,10 +9596,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>479698</v>
+        <v>479644</v>
       </c>
       <c r="R68" t="n">
-        <v>7027368</v>
+        <v>7027243</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9645,7 +9645,7 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ68" t="inlineStr">
@@ -9683,10 +9683,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122696537</v>
+        <v>122698232</v>
       </c>
       <c r="B69" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9699,47 +9699,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>479669</v>
+        <v>479698</v>
       </c>
       <c r="R69" t="n">
-        <v>7027116</v>
+        <v>7027368</v>
       </c>
       <c r="S69" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9771,11 +9761,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -9802,12 +9787,12 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9825,10 +9810,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122697534</v>
+        <v>122696537</v>
       </c>
       <c r="B70" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9841,37 +9826,47 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>479644</v>
+        <v>479669</v>
       </c>
       <c r="R70" t="n">
-        <v>7027243</v>
+        <v>7027116</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9903,6 +9898,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -9914,7 +9914,7 @@
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ70" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9952,10 +9952,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122696057</v>
+        <v>122698247</v>
       </c>
       <c r="B71" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9968,39 +9968,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>479675</v>
+        <v>479696</v>
       </c>
       <c r="R71" t="n">
-        <v>7027261</v>
+        <v>7027370</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -10035,11 +10030,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>På flera aspar.</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -10056,22 +10046,22 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -10089,10 +10079,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122698247</v>
+        <v>122696057</v>
       </c>
       <c r="B72" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -10105,34 +10095,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>479696</v>
+        <v>479675</v>
       </c>
       <c r="R72" t="n">
-        <v>7027370</v>
+        <v>7027261</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -10167,6 +10162,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På flera aspar.</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -10183,22 +10183,22 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>

--- a/artfynd/A 60372-2024 artfynd.xlsx
+++ b/artfynd/A 60372-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122613090</v>
+        <v>122609753</v>
       </c>
       <c r="B2" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,44 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>479694</v>
+        <v>479670</v>
       </c>
       <c r="R2" t="n">
-        <v>7027295</v>
+        <v>7027294</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,18 +753,12 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ett gäng "knippen" med stora lunglavsbålar på en asp.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -780,29 +767,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
-        </is>
-      </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -820,7 +802,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122609753</v>
+        <v>122609281</v>
       </c>
       <c r="B3" t="n">
         <v>78766</v>
@@ -860,13 +842,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479670</v>
+        <v>479698</v>
       </c>
       <c r="R3" t="n">
-        <v>7027294</v>
+        <v>7027342</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -896,6 +878,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -947,10 +934,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122606696</v>
+        <v>122607124</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -963,34 +950,44 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479678</v>
+        <v>479654</v>
       </c>
       <c r="R4" t="n">
-        <v>7027508</v>
+        <v>7027561</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1025,6 +1022,11 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Både äldre och färska ringhack på stambasen.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1051,12 +1053,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1074,7 +1076,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122609468</v>
+        <v>122613090</v>
       </c>
       <c r="B5" t="n">
         <v>79847</v>
@@ -1108,24 +1110,26 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>med soral</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>479731</v>
+        <v>479694</v>
       </c>
       <c r="R5" t="n">
-        <v>7027323</v>
+        <v>7027295</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1159,7 +1163,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ymnigt med lunglav längs 7 meter på en något smalare sälg.</t>
+          <t>Ett gäng "knippen" med stora lunglavsbålar på en asp.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1168,6 +1172,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1176,14 +1181,19 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+        </is>
+      </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1193,7 +1203,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1211,7 +1221,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122613066</v>
+        <v>122606169</v>
       </c>
       <c r="B6" t="n">
         <v>79847</v>
@@ -1245,26 +1255,24 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>479702</v>
+        <v>479698</v>
       </c>
       <c r="R6" t="n">
-        <v>7027288</v>
+        <v>7027398</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1298,7 +1306,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Lunglav på en grovbarkad asp.</t>
+          <t>Rikligt med lunglav där vissa bålar är fertila med apothecier. På en gammal grovbarkad sälg med 54 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1307,28 +1315,22 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -1338,7 +1340,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1356,7 +1358,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122607565</v>
+        <v>122605930</v>
       </c>
       <c r="B7" t="n">
         <v>78766</v>
@@ -1396,10 +1398,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>479638</v>
+        <v>479743</v>
       </c>
       <c r="R7" t="n">
-        <v>7027601</v>
+        <v>7027472</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1436,7 +1438,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>Långväxta bålar på flera träd.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1488,7 +1490,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122608228</v>
+        <v>122613058</v>
       </c>
       <c r="B8" t="n">
         <v>78766</v>
@@ -1522,19 +1524,22 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kvarnbäcken, Kvarnbäcken, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>479594</v>
+        <v>479722</v>
       </c>
       <c r="R8" t="n">
-        <v>7027696</v>
+        <v>7027290</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1566,23 +1571,24 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1620,10 +1626,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122609386</v>
+        <v>122609468</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1636,27 +1642,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1665,10 +1671,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>479699</v>
+        <v>479731</v>
       </c>
       <c r="R9" t="n">
-        <v>7027340</v>
+        <v>7027323</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1705,7 +1711,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen av en stående död gran. Volym stående död ved här som ger medelhögt till högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ymnigt med lunglav längs 7 meter på en något smalare sälg.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1724,22 +1730,22 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1757,7 +1763,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122613032</v>
+        <v>122609424</v>
       </c>
       <c r="B10" t="n">
         <v>79847</v>
@@ -1791,26 +1797,24 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>479731</v>
+        <v>479729</v>
       </c>
       <c r="R10" t="n">
-        <v>7027291</v>
+        <v>7027353</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1844,7 +1848,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>En hel del bålar på en skadad sälg.</t>
+          <t>Fertila bålar på en smal böjd sälg.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1853,18 +1857,12 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1902,10 +1900,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122607124</v>
+        <v>122606280</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1918,44 +1916,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>479654</v>
+        <v>479693</v>
       </c>
       <c r="R11" t="n">
-        <v>7027561</v>
+        <v>7027399</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1992,7 +1980,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Både äldre och färska ringhack på stambasen.</t>
+          <t>Skrovellav på en gammal grov sälg med 54 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2006,27 +1994,27 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2044,10 +2032,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122605930</v>
+        <v>122613032</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2060,37 +2048,44 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>479743</v>
+        <v>479731</v>
       </c>
       <c r="R12" t="n">
-        <v>7027472</v>
+        <v>7027291</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2124,7 +2119,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera träd.</t>
+          <t>En hel del bålar på en skadad sälg.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2133,6 +2128,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2141,24 +2137,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+        </is>
+      </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2176,10 +2177,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122606169</v>
+        <v>122607620</v>
       </c>
       <c r="B13" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2192,42 +2193,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>479698</v>
+        <v>479635</v>
       </c>
       <c r="R13" t="n">
-        <v>7027398</v>
+        <v>7027621</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2261,7 +2257,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav där vissa bålar är fertila med apothecier. På en gammal grovbarkad sälg med 54 cm i brösthöjdsdiameter.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2275,27 +2271,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2313,7 +2309,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122609424</v>
+        <v>122609496</v>
       </c>
       <c r="B14" t="n">
         <v>79847</v>
@@ -2349,7 +2345,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2358,13 +2354,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>479729</v>
+        <v>479735</v>
       </c>
       <c r="R14" t="n">
-        <v>7027353</v>
+        <v>7027318</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2396,11 +2392,6 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Fertila bålar på en smal böjd sälg.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2417,22 +2408,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2450,10 +2441,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122609837</v>
+        <v>122613066</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2466,37 +2457,44 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>479643</v>
+        <v>479702</v>
       </c>
       <c r="R15" t="n">
-        <v>7027326</v>
+        <v>7027288</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2530,7 +2528,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Lunglav på en grovbarkad asp.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2539,6 +2537,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2547,24 +2546,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+        </is>
+      </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Populus tremula</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2714,7 +2718,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122613058</v>
+        <v>122606334</v>
       </c>
       <c r="B17" t="n">
         <v>78766</v>
@@ -2748,22 +2752,19 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>479722</v>
+        <v>479692</v>
       </c>
       <c r="R17" t="n">
-        <v>7027290</v>
+        <v>7027424</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2801,18 +2802,12 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -2850,10 +2845,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122608462</v>
+        <v>122606273</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2866,44 +2861,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kvarnbäcken, Kvarnbäcken, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>479583</v>
+        <v>479698</v>
       </c>
       <c r="R18" t="n">
-        <v>7027629</v>
+        <v>7027398</v>
       </c>
       <c r="S18" t="n">
         <v>7</v>
@@ -2940,7 +2930,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Äldre ringhack som bedöms vara 5-10 år gamla. På en gran med tydliga kådaflöden. Hyfsat gott om död ved här.</t>
+          <t>Skrovellav på en undertryck gran intill en gammal grov sälg.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2954,7 +2944,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -2969,12 +2959,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2992,10 +2982,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122613055</v>
+        <v>122609837</v>
       </c>
       <c r="B19" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3008,40 +2998,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>479722</v>
+        <v>479643</v>
       </c>
       <c r="R19" t="n">
-        <v>7027290</v>
+        <v>7027326</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3075,7 +3062,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Enstaka små bålar på en grov gammal asp.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3084,7 +3071,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3093,29 +3079,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
-        </is>
-      </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3133,7 +3114,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122607620</v>
+        <v>122606696</v>
       </c>
       <c r="B20" t="n">
         <v>78766</v>
@@ -3173,10 +3154,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>479635</v>
+        <v>479678</v>
       </c>
       <c r="R20" t="n">
-        <v>7027621</v>
+        <v>7027508</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3209,11 +3190,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3265,10 +3241,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122606431</v>
+        <v>122607115</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3281,37 +3257,47 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>479711</v>
+        <v>479652</v>
       </c>
       <c r="R21" t="n">
-        <v>7027387</v>
+        <v>7027551</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3345,7 +3331,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Både färska och äldre ringhack på stambasen. I skogsbeståndet runt fyndplatsen finns medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3359,7 +3345,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -3374,12 +3360,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3397,7 +3383,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122609252</v>
+        <v>122608228</v>
       </c>
       <c r="B22" t="n">
         <v>78766</v>
@@ -3433,14 +3419,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Kvarnbäcken, Kvarnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>479714</v>
+        <v>479594</v>
       </c>
       <c r="R22" t="n">
-        <v>7027356</v>
+        <v>7027696</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3473,6 +3459,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3524,10 +3515,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122606273</v>
+        <v>122612982</v>
       </c>
       <c r="B23" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3540,42 +3531,44 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>med soral</t>
         </is>
       </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>479698</v>
+        <v>479738</v>
       </c>
       <c r="R23" t="n">
-        <v>7027398</v>
+        <v>7027319</v>
       </c>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3609,7 +3602,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Skrovellav på en undertryck gran intill en gammal grov sälg.</t>
+          <t>Grova gamla lunglavsbålar på en lutande sälg.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3618,32 +3611,43 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>En smal lutande sälg.</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En smal lutande sälg.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3661,10 +3665,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122606232</v>
+        <v>122607162</v>
       </c>
       <c r="B24" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3677,39 +3681,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>479707</v>
+        <v>479650</v>
       </c>
       <c r="R24" t="n">
-        <v>7027397</v>
+        <v>7027549</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3746,7 +3745,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Fertil lunglav på en undertryck gran intill en gammal grov sälg.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3760,7 +3759,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -3798,10 +3797,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122606631</v>
+        <v>122607263</v>
       </c>
       <c r="B25" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3814,39 +3813,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>479711</v>
+        <v>479655</v>
       </c>
       <c r="R25" t="n">
-        <v>7027473</v>
+        <v>7027573</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3881,11 +3875,6 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på en asp.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3902,22 +3891,22 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3935,10 +3924,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122606649</v>
+        <v>122607565</v>
       </c>
       <c r="B26" t="n">
-        <v>79883</v>
+        <v>78766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3947,43 +3936,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>479715</v>
+        <v>479638</v>
       </c>
       <c r="R26" t="n">
-        <v>7027462</v>
+        <v>7027601</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -4020,7 +4004,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>En samling bålar på ca 2 meters höjd på aspens stam.</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4039,22 +4023,22 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4072,10 +4056,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122609281</v>
+        <v>122606649</v>
       </c>
       <c r="B27" t="n">
-        <v>78766</v>
+        <v>79883</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4084,41 +4068,46 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>479698</v>
+        <v>479715</v>
       </c>
       <c r="R27" t="n">
-        <v>7027342</v>
+        <v>7027462</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4152,7 +4141,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>En samling bålar på ca 2 meters höjd på aspens stam.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4171,22 +4160,22 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4204,10 +4193,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122612982</v>
+        <v>122606868</v>
       </c>
       <c r="B28" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4220,41 +4209,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>479738</v>
+        <v>479661</v>
       </c>
       <c r="R28" t="n">
-        <v>7027319</v>
+        <v>7027516</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4289,54 +4271,38 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Grova gamla lunglavsbålar på en lutande sälg.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL28" t="inlineStr">
-        <is>
-          <t>En smal lutande sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En smal lutande sälg.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4354,10 +4320,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122608509</v>
+        <v>122606026</v>
       </c>
       <c r="B29" t="n">
-        <v>79751</v>
+        <v>90970</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4366,38 +4332,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>479617</v>
+        <v>479756</v>
       </c>
       <c r="R29" t="n">
-        <v>7027598</v>
+        <v>7027477</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4448,22 +4419,22 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4481,7 +4452,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122606334</v>
+        <v>122606431</v>
       </c>
       <c r="B30" t="n">
         <v>78766</v>
@@ -4521,10 +4492,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>479692</v>
+        <v>479711</v>
       </c>
       <c r="R30" t="n">
-        <v>7027424</v>
+        <v>7027387</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4557,6 +4528,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4608,10 +4584,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122607246</v>
+        <v>122607879</v>
       </c>
       <c r="B31" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4624,51 +4600,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>479659</v>
+        <v>479622</v>
       </c>
       <c r="R31" t="n">
-        <v>7027556</v>
+        <v>7027648</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4702,7 +4664,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Observerades i flerskiktad granskog.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4717,6 +4679,26 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4734,10 +4716,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122606026</v>
+        <v>122609386</v>
       </c>
       <c r="B32" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4750,27 +4732,27 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4779,10 +4761,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>479756</v>
+        <v>479699</v>
       </c>
       <c r="R32" t="n">
-        <v>7027477</v>
+        <v>7027340</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4817,6 +4799,11 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på stambasen av en stående död gran. Volym stående död ved här som ger medelhögt till högt livsmiljövärde för tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4843,12 +4830,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4866,10 +4853,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122606280</v>
+        <v>122613055</v>
       </c>
       <c r="B33" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4882,37 +4869,40 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>479693</v>
+        <v>479722</v>
       </c>
       <c r="R33" t="n">
-        <v>7027399</v>
+        <v>7027290</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4946,7 +4936,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Skrovellav på en gammal grov sälg med 54 cm i brösthöjdsdiameter.</t>
+          <t>Enstaka små bålar på en grov gammal asp.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4955,32 +4945,38 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Branch on living tree # Salix caprea</t>
+          <t>Bark on living woody plant # Grov bark. # Populus tremula</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4998,10 +4994,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122609496</v>
+        <v>122608462</v>
       </c>
       <c r="B34" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5014,39 +5010,44 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Kvarnbäcken, Kvarnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>479735</v>
+        <v>479583</v>
       </c>
       <c r="R34" t="n">
-        <v>7027318</v>
+        <v>7027629</v>
       </c>
       <c r="S34" t="n">
         <v>7</v>
@@ -5081,6 +5082,11 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack som bedöms vara 5-10 år gamla. På en gran med tydliga kådaflöden. Hyfsat gott om död ved här.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -5107,12 +5113,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5130,10 +5136,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122607879</v>
+        <v>122606631</v>
       </c>
       <c r="B35" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5146,37 +5152,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>479622</v>
+        <v>479711</v>
       </c>
       <c r="R35" t="n">
-        <v>7027648</v>
+        <v>7027473</v>
       </c>
       <c r="S35" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5210,7 +5221,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Enstaka bålar på en asp.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5229,22 +5240,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5262,7 +5273,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122606868</v>
+        <v>122609252</v>
       </c>
       <c r="B36" t="n">
         <v>78766</v>
@@ -5302,10 +5313,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>479661</v>
+        <v>479714</v>
       </c>
       <c r="R36" t="n">
-        <v>7027516</v>
+        <v>7027356</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5351,7 +5362,7 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
@@ -5389,10 +5400,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122607162</v>
+        <v>122606232</v>
       </c>
       <c r="B37" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5405,34 +5416,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>479650</v>
+        <v>479707</v>
       </c>
       <c r="R37" t="n">
-        <v>7027549</v>
+        <v>7027397</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5469,7 +5485,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Fertil lunglav på en undertryck gran intill en gammal grov sälg.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5483,7 +5499,7 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -5521,10 +5537,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122607263</v>
+        <v>122608509</v>
       </c>
       <c r="B38" t="n">
-        <v>78766</v>
+        <v>79751</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5533,25 +5549,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5561,10 +5577,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>479655</v>
+        <v>479617</v>
       </c>
       <c r="R38" t="n">
-        <v>7027573</v>
+        <v>7027598</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5615,22 +5631,22 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5648,10 +5664,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122607115</v>
+        <v>122607246</v>
       </c>
       <c r="B39" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5664,27 +5680,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5698,13 +5718,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>479652</v>
+        <v>479659</v>
       </c>
       <c r="R39" t="n">
-        <v>7027551</v>
+        <v>7027556</v>
       </c>
       <c r="S39" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5738,7 +5758,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Både färska och äldre ringhack på stambasen. I skogsbeståndet runt fyndplatsen finns medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Observerades i flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5753,26 +5773,6 @@
       <c r="AH39" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5790,10 +5790,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122613145</v>
+        <v>122608090</v>
       </c>
       <c r="B40" t="n">
-        <v>79847</v>
+        <v>79751</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5802,48 +5802,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>479634</v>
+        <v>479602</v>
       </c>
       <c r="R40" t="n">
-        <v>7027302</v>
+        <v>7027640</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5875,18 +5868,12 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ymnig påväxt av lunglav längs flera meter på en sälgstam. Vissa bålar är fertila med apothecier.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5895,24 +5882,14 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
-        </is>
-      </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL40" t="inlineStr">
-        <is>
-          <t>En svagt lutande sälg.</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
@@ -5922,7 +5899,7 @@
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En svagt lutande sälg.</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5940,7 +5917,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122608974</v>
+        <v>122613145</v>
       </c>
       <c r="B41" t="n">
         <v>79847</v>
@@ -5974,24 +5951,26 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>479682</v>
+        <v>479634</v>
       </c>
       <c r="R41" t="n">
-        <v>7027484</v>
+        <v>7027302</v>
       </c>
       <c r="S41" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -6023,12 +6002,18 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ymnig påväxt av lunglav längs flera meter på en sälgstam. Vissa bålar är fertila med apothecier.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -6037,14 +6022,24 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+        </is>
+      </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL41" t="inlineStr">
+        <is>
+          <t>En svagt lutande sälg.</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
@@ -6054,7 +6049,7 @@
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea # En svagt lutande sälg.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6072,7 +6067,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122609073</v>
+        <v>122609140</v>
       </c>
       <c r="B42" t="n">
         <v>79847</v>
@@ -6108,7 +6103,7 @@
       <c r="I42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -6117,13 +6112,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>479738</v>
+        <v>479723</v>
       </c>
       <c r="R42" t="n">
-        <v>7027404</v>
+        <v>7027396</v>
       </c>
       <c r="S42" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6157,7 +6152,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På en smal sälg.</t>
+          <t>Ymnig påväxt av lunglav längs flera meter på en gammal sälg. Fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6209,10 +6204,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122607410</v>
+        <v>122609714</v>
       </c>
       <c r="B43" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6225,44 +6220,46 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>479644</v>
+        <v>479677</v>
       </c>
       <c r="R43" t="n">
-        <v>7027599</v>
+        <v>7027303</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6299,7 +6296,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Både äldre och färska ringhack på stambasen. I skogsbeståndet runt fyndplatsen finns medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Observation i flerskiktad granskog med stående murkna björkhögstubbar som är gynnsamt för talltitans häckning.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6316,24 +6313,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6351,10 +6333,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122608090</v>
+        <v>122613278</v>
       </c>
       <c r="B44" t="n">
-        <v>79751</v>
+        <v>79847</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6363,41 +6345,48 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>479602</v>
+        <v>479628</v>
       </c>
       <c r="R44" t="n">
-        <v>7027640</v>
+        <v>7027338</v>
       </c>
       <c r="S44" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6429,12 +6418,18 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglavsbålar på gran intill en gammal sälg med lunglav.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6443,24 +6438,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+        </is>
+      </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6478,10 +6478,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122613271</v>
+        <v>122613281</v>
       </c>
       <c r="B45" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6494,30 +6494,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6565,7 +6561,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Riklig påväxt av lunglavsbålar på en gammal sälg. Vissa bålar är fertila med apothecier. Här växer även rikligt med lunglav på gran.</t>
+          <t>Med långväxta bålar och på flera granar.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6590,27 +6586,22 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL45" t="inlineStr">
-        <is>
-          <t>En gammal grov sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea # En gammal grov sälg.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6628,10 +6619,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122613280</v>
+        <v>122607410</v>
       </c>
       <c r="B46" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6644,44 +6635,47 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>479628</v>
+        <v>479644</v>
       </c>
       <c r="R46" t="n">
-        <v>7027338</v>
+        <v>7027599</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6715,7 +6709,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På renar av gran blandat med lunglav.</t>
+          <t>Både äldre och färska ringhack på stambasen. I skogsbeståndet runt fyndplatsen finns medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6724,7 +6718,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6733,11 +6726,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
-        </is>
-      </c>
       <c r="AJ46" t="inlineStr">
         <is>
           <t>gran</t>
@@ -6750,12 +6738,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6773,10 +6761,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122609714</v>
+        <v>122608974</v>
       </c>
       <c r="B47" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6789,49 +6777,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>479677</v>
+        <v>479682</v>
       </c>
       <c r="R47" t="n">
-        <v>7027303</v>
+        <v>7027484</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6863,11 +6844,6 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Observation i flerskiktad granskog med stående murkna björkhögstubbar som är gynnsamt för talltitans häckning.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6882,9 +6858,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6902,10 +6893,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122613281</v>
+        <v>122607746</v>
       </c>
       <c r="B48" t="n">
-        <v>78766</v>
+        <v>79751</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6914,44 +6905,48 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>479628</v>
+        <v>479627</v>
       </c>
       <c r="R48" t="n">
-        <v>7027338</v>
+        <v>7027656</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6985,7 +6980,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Med långväxta bålar och på flera granar.</t>
+          <t>Skinnlav på asp där flertalet bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7005,27 +7000,27 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
+          <t>Flerskiktad kontinuitetsskog dominerad av gran och med återkommande inslag av asp.</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -7043,7 +7038,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122609140</v>
+        <v>122609073</v>
       </c>
       <c r="B49" t="n">
         <v>79847</v>
@@ -7079,7 +7074,7 @@
       <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -7088,13 +7083,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>479723</v>
+        <v>479738</v>
       </c>
       <c r="R49" t="n">
-        <v>7027396</v>
+        <v>7027404</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -7128,7 +7123,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ymnig påväxt av lunglav längs flera meter på en gammal sälg. Fertila bålar med apothecier.</t>
+          <t>På en smal sälg.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7180,10 +7175,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122607746</v>
+        <v>122613280</v>
       </c>
       <c r="B50" t="n">
-        <v>79751</v>
+        <v>79848</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7192,48 +7187,48 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Frankbodarna, Frankbodarna, Jmt</t>
+          <t>Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>479627</v>
+        <v>479628</v>
       </c>
       <c r="R50" t="n">
-        <v>7027656</v>
+        <v>7027338</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7267,7 +7262,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Skinnlav på asp där flertalet bålar är fertila med apothecier.</t>
+          <t>På renar av gran blandat med lunglav.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7287,27 +7282,27 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Flerskiktad kontinuitetsskog dominerad av gran och med återkommande inslag av asp.</t>
+          <t>Flerskiktad grandominerad kontinuitetsskog med olikåldriga träd. Här finns gamla aspar och sälgar och spår efter tidigare brand i form av kolade stubbar. Stående och liggande död ved av olika grovlek.</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7452,10 +7447,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122697352</v>
+        <v>122696057</v>
       </c>
       <c r="B52" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7468,34 +7463,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>479674</v>
+        <v>479675</v>
       </c>
       <c r="R52" t="n">
-        <v>7027178</v>
+        <v>7027261</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7530,6 +7530,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>På flera aspar.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -7546,22 +7551,22 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7579,7 +7584,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122697773</v>
+        <v>122697286</v>
       </c>
       <c r="B53" t="n">
         <v>79847</v>
@@ -7613,16 +7618,21 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>479617</v>
+        <v>479663</v>
       </c>
       <c r="R53" t="n">
-        <v>7027326</v>
+        <v>7027246</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7657,11 +7667,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -7678,12 +7683,12 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
@@ -7693,7 +7698,7 @@
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7711,7 +7716,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122698085</v>
+        <v>122698247</v>
       </c>
       <c r="B54" t="n">
         <v>78766</v>
@@ -7751,10 +7756,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>479659</v>
+        <v>479696</v>
       </c>
       <c r="R54" t="n">
-        <v>7027303</v>
+        <v>7027370</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7838,10 +7843,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122696521</v>
+        <v>122695752</v>
       </c>
       <c r="B55" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7854,47 +7859,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>479674</v>
+        <v>479748</v>
       </c>
       <c r="R55" t="n">
-        <v>7027109</v>
+        <v>7027283</v>
       </c>
       <c r="S55" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7926,11 +7921,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Färska hackspår i stambasen av en smal gran i granskog med stora mängder liggande död ved.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -7957,12 +7947,12 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7980,10 +7970,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122697666</v>
+        <v>122697882</v>
       </c>
       <c r="B56" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7996,51 +7986,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>479632</v>
+        <v>479664</v>
       </c>
       <c r="R56" t="n">
-        <v>7027297</v>
+        <v>7027326</v>
       </c>
       <c r="S56" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -8072,6 +8048,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -8098,12 +8079,12 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -8121,10 +8102,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122696303</v>
+        <v>122695492</v>
       </c>
       <c r="B57" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -8137,37 +8118,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>479685</v>
+        <v>479770</v>
       </c>
       <c r="R57" t="n">
-        <v>7027165</v>
+        <v>7027300</v>
       </c>
       <c r="S57" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -8199,6 +8185,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Växer på en lite smalare sälg intill lunglav.</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -8215,22 +8206,22 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8248,10 +8239,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122695669</v>
+        <v>122696111</v>
       </c>
       <c r="B58" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8264,21 +8255,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -8288,13 +8279,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>479761</v>
+        <v>479694</v>
       </c>
       <c r="R58" t="n">
-        <v>7027298</v>
+        <v>7027236</v>
       </c>
       <c r="S58" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8375,10 +8366,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122695943</v>
+        <v>122695703</v>
       </c>
       <c r="B59" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8391,37 +8382,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>479756</v>
+        <v>479753</v>
       </c>
       <c r="R59" t="n">
-        <v>7027364</v>
+        <v>7027296</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8453,6 +8449,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglav på två knäckta sälgar.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -8469,22 +8470,22 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8502,10 +8503,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122697966</v>
+        <v>122696290</v>
       </c>
       <c r="B60" t="n">
-        <v>79847</v>
+        <v>57631</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8518,27 +8519,36 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>med soral</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -8547,10 +8557,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>479660</v>
+        <v>479695</v>
       </c>
       <c r="R60" t="n">
-        <v>7027363</v>
+        <v>7027185</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8585,6 +8595,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Observerad i flerskiktad äldre granskog.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -8597,26 +8612,6 @@
       <c r="AH60" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8634,10 +8629,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122695752</v>
+        <v>122696876</v>
       </c>
       <c r="B61" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8650,37 +8645,47 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>479748</v>
+        <v>479628</v>
       </c>
       <c r="R61" t="n">
-        <v>7027283</v>
+        <v>7027133</v>
       </c>
       <c r="S61" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8712,6 +8717,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på stambasen av en gran. I äldre granskog med minst medelhöga till höga livsmiljövärden för tretåig hackspett. Även gott om liggande död ved här. Finns även skalade döda granar här som indikerar potentiella födosökspår efter tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -8738,12 +8748,12 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8761,10 +8771,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122696471</v>
+        <v>122695354</v>
       </c>
       <c r="B62" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8777,47 +8787,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>479681</v>
+        <v>479765</v>
       </c>
       <c r="R62" t="n">
-        <v>7027123</v>
+        <v>7027389</v>
       </c>
       <c r="S62" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen.</t>
+          <t>På en lutande krokig sälg.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8870,22 +8870,22 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8903,10 +8903,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122696290</v>
+        <v>122698275</v>
       </c>
       <c r="B63" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8919,48 +8919,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>479695</v>
+        <v>479734</v>
       </c>
       <c r="R63" t="n">
-        <v>7027185</v>
+        <v>7027357</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8997,7 +8983,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Observerad i flerskiktad äldre granskog.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -9012,6 +8998,26 @@
       <c r="AH63" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -9029,10 +9035,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122697455</v>
+        <v>122695273</v>
       </c>
       <c r="B64" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -9045,16 +9051,16 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -9062,14 +9068,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -9083,13 +9085,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>479680</v>
+        <v>479770</v>
       </c>
       <c r="R64" t="n">
-        <v>7027206</v>
+        <v>7027401</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -9123,7 +9125,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Observation av en spillkråka som gav ifrån sig två olika lockläten. I gammal granskog med gott om asp och tall som utgör lämpliga substrat för bohål. Även bitvis relativt gott om död ved här.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9138,6 +9140,26 @@
       <c r="AH64" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -9155,10 +9177,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122695354</v>
+        <v>122695075</v>
       </c>
       <c r="B65" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9171,21 +9193,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -9195,10 +9217,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>479765</v>
+        <v>479699</v>
       </c>
       <c r="R65" t="n">
-        <v>7027389</v>
+        <v>7027521</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -9235,7 +9257,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På en lutande krokig sälg.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9254,22 +9276,22 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9287,10 +9309,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122697757</v>
+        <v>122698232</v>
       </c>
       <c r="B66" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9303,39 +9325,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>479615</v>
+        <v>479698</v>
       </c>
       <c r="R66" t="n">
-        <v>7027315</v>
+        <v>7027368</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9386,22 +9403,22 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9419,7 +9436,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122695492</v>
+        <v>122695669</v>
       </c>
       <c r="B67" t="n">
         <v>79848</v>
@@ -9453,24 +9470,19 @@
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>479770</v>
+        <v>479761</v>
       </c>
       <c r="R67" t="n">
-        <v>7027300</v>
+        <v>7027298</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -9502,11 +9514,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Växer på en lite smalare sälg intill lunglav.</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -9523,22 +9530,22 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9556,7 +9563,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122697534</v>
+        <v>122697862</v>
       </c>
       <c r="B68" t="n">
         <v>78766</v>
@@ -9596,10 +9603,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>479644</v>
+        <v>479630</v>
       </c>
       <c r="R68" t="n">
-        <v>7027243</v>
+        <v>7027362</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9645,7 +9652,7 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ68" t="inlineStr">
@@ -9683,10 +9690,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122698232</v>
+        <v>122695602</v>
       </c>
       <c r="B69" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9699,34 +9706,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>479698</v>
+        <v>479774</v>
       </c>
       <c r="R69" t="n">
-        <v>7027368</v>
+        <v>7027322</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9761,6 +9773,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ymnigt med lunglav på en gammal sälg med fårad bark.</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -9777,22 +9794,22 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9810,10 +9827,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122696537</v>
+        <v>122696303</v>
       </c>
       <c r="B70" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9826,47 +9843,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>479669</v>
+        <v>479685</v>
       </c>
       <c r="R70" t="n">
-        <v>7027116</v>
+        <v>7027165</v>
       </c>
       <c r="S70" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9898,11 +9905,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -9929,12 +9931,12 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9952,10 +9954,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122698247</v>
+        <v>122695516</v>
       </c>
       <c r="B71" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9968,34 +9970,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>479696</v>
+        <v>479766</v>
       </c>
       <c r="R71" t="n">
-        <v>7027370</v>
+        <v>7027310</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -10030,6 +10037,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Växer på en lite smalare sälg intill skrovellav.</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -10046,22 +10058,22 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -10079,10 +10091,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122696057</v>
+        <v>122698085</v>
       </c>
       <c r="B72" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -10095,39 +10107,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>479675</v>
+        <v>479659</v>
       </c>
       <c r="R72" t="n">
-        <v>7027261</v>
+        <v>7027303</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -10162,11 +10169,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>På flera aspar.</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -10183,22 +10185,22 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -10216,10 +10218,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122695075</v>
+        <v>122696537</v>
       </c>
       <c r="B73" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -10232,37 +10234,47 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>479699</v>
+        <v>479669</v>
       </c>
       <c r="R73" t="n">
-        <v>7027521</v>
+        <v>7027116</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -10296,7 +10308,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10325,12 +10337,12 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -10348,7 +10360,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122696111</v>
+        <v>122695101</v>
       </c>
       <c r="B74" t="n">
         <v>78766</v>
@@ -10388,10 +10400,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>479694</v>
+        <v>479696</v>
       </c>
       <c r="R74" t="n">
-        <v>7027236</v>
+        <v>7027544</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10424,6 +10436,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10475,10 +10492,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122695602</v>
+        <v>122697534</v>
       </c>
       <c r="B75" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10491,39 +10508,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>479774</v>
+        <v>479644</v>
       </c>
       <c r="R75" t="n">
-        <v>7027322</v>
+        <v>7027243</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10558,11 +10570,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ymnigt med lunglav på en gammal sälg med fårad bark.</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -10574,27 +10581,27 @@
       </c>
       <c r="AH75" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -10612,10 +10619,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122695101</v>
+        <v>122696471</v>
       </c>
       <c r="B76" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10628,37 +10635,47 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>479696</v>
+        <v>479681</v>
       </c>
       <c r="R76" t="n">
-        <v>7027544</v>
+        <v>7027123</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -10692,7 +10709,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10721,12 +10738,12 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -10744,10 +10761,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122696876</v>
+        <v>122697352</v>
       </c>
       <c r="B77" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10760,47 +10777,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>479628</v>
+        <v>479674</v>
       </c>
       <c r="R77" t="n">
-        <v>7027133</v>
+        <v>7027178</v>
       </c>
       <c r="S77" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -10832,11 +10839,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på stambasen av en gran. I äldre granskog med minst medelhöga till höga livsmiljövärden för tretåig hackspett. Även gott om liggande död ved här. Finns även skalade döda granar här som indikerar potentiella födosökspår efter tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -10863,12 +10865,12 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10886,10 +10888,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122695011</v>
+        <v>122695682</v>
       </c>
       <c r="B78" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10902,34 +10904,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>479729</v>
+        <v>479763</v>
       </c>
       <c r="R78" t="n">
-        <v>7027486</v>
+        <v>7027300</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10966,7 +10973,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På en smal krokig sälg.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10985,22 +10992,22 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -11018,10 +11025,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122697286</v>
+        <v>122697757</v>
       </c>
       <c r="B79" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -11034,21 +11041,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -11063,10 +11070,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>479663</v>
+        <v>479615</v>
       </c>
       <c r="R79" t="n">
-        <v>7027246</v>
+        <v>7027315</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -11117,12 +11124,12 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM79" t="inlineStr">
@@ -11132,7 +11139,7 @@
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -11150,10 +11157,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122695682</v>
+        <v>122695943</v>
       </c>
       <c r="B80" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -11166,39 +11173,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>479763</v>
+        <v>479756</v>
       </c>
       <c r="R80" t="n">
-        <v>7027300</v>
+        <v>7027364</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -11233,11 +11235,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>På en smal krokig sälg.</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -11254,22 +11251,22 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -11287,10 +11284,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122696014</v>
+        <v>122697666</v>
       </c>
       <c r="B81" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -11303,37 +11300,51 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>479718</v>
+        <v>479632</v>
       </c>
       <c r="R81" t="n">
-        <v>7027277</v>
+        <v>7027297</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -11391,12 +11402,12 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -11414,10 +11425,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122697862</v>
+        <v>122696521</v>
       </c>
       <c r="B82" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -11430,37 +11441,47 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>479630</v>
+        <v>479674</v>
       </c>
       <c r="R82" t="n">
-        <v>7027362</v>
+        <v>7027109</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -11492,6 +11513,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Färska hackspår i stambasen av en smal gran i granskog med stora mängder liggande död ved.</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -11518,12 +11544,12 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -11541,7 +11567,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122695322</v>
+        <v>122697966</v>
       </c>
       <c r="B83" t="n">
         <v>79847</v>
@@ -11586,10 +11612,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>479771</v>
+        <v>479660</v>
       </c>
       <c r="R83" t="n">
-        <v>7027387</v>
+        <v>7027363</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11624,11 +11650,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>På en lutande krokig sälg.</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -11645,12 +11666,12 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM83" t="inlineStr">
@@ -11660,7 +11681,7 @@
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -11678,10 +11699,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122695273</v>
+        <v>122695926</v>
       </c>
       <c r="B84" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11694,32 +11715,27 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -11728,10 +11744,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>479770</v>
+        <v>479752</v>
       </c>
       <c r="R84" t="n">
-        <v>7027401</v>
+        <v>7027344</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11768,7 +11784,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Ymnigt med lunglav på en gammal sälg.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11787,22 +11803,22 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -11820,10 +11836,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122695703</v>
+        <v>122696014</v>
       </c>
       <c r="B85" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11836,42 +11852,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>479753</v>
+        <v>479718</v>
       </c>
       <c r="R85" t="n">
-        <v>7027296</v>
+        <v>7027277</v>
       </c>
       <c r="S85" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -11903,11 +11914,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglav på två knäckta sälgar.</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -11924,22 +11930,22 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -11957,7 +11963,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122695926</v>
+        <v>122695655</v>
       </c>
       <c r="B86" t="n">
         <v>79847</v>
@@ -12002,13 +12008,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>479752</v>
+        <v>479759</v>
       </c>
       <c r="R86" t="n">
-        <v>7027344</v>
+        <v>7027292</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -12042,7 +12048,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Ymnigt med lunglav på en gammal sälg.</t>
+          <t>Växer på två granar intill en sälg med ymnig påväxt av lunglav.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -12061,22 +12067,22 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -12094,10 +12100,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122695655</v>
+        <v>122695011</v>
       </c>
       <c r="B87" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -12110,42 +12116,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>479759</v>
+        <v>479729</v>
       </c>
       <c r="R87" t="n">
-        <v>7027292</v>
+        <v>7027486</v>
       </c>
       <c r="S87" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -12179,7 +12180,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Växer på två granar intill en sälg med ymnig påväxt av lunglav.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -12231,10 +12232,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122697882</v>
+        <v>122695322</v>
       </c>
       <c r="B88" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -12247,37 +12248,42 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>479664</v>
+        <v>479771</v>
       </c>
       <c r="R88" t="n">
-        <v>7027326</v>
+        <v>7027387</v>
       </c>
       <c r="S88" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -12311,7 +12317,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På en lutande krokig sälg.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -12330,22 +12336,22 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -12363,7 +12369,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122695516</v>
+        <v>122697773</v>
       </c>
       <c r="B89" t="n">
         <v>79847</v>
@@ -12397,21 +12403,16 @@
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>479766</v>
+        <v>479617</v>
       </c>
       <c r="R89" t="n">
-        <v>7027310</v>
+        <v>7027326</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -12448,7 +12449,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Växer på en lite smalare sälg intill skrovellav.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -12500,10 +12501,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122698275</v>
+        <v>122697455</v>
       </c>
       <c r="B90" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -12516,37 +12517,51 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>479734</v>
+        <v>479680</v>
       </c>
       <c r="R90" t="n">
-        <v>7027357</v>
+        <v>7027206</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -12580,7 +12595,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Observation av en spillkråka som gav ifrån sig två olika lockläten. I gammal granskog med gott om asp och tall som utgör lämpliga substrat för bohål. Även bitvis relativt gott om död ved här.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -12595,26 +12610,6 @@
       <c r="AH90" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>

--- a/artfynd/A 60372-2024 artfynd.xlsx
+++ b/artfynd/A 60372-2024 artfynd.xlsx
@@ -7584,10 +7584,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122697286</v>
+        <v>122698247</v>
       </c>
       <c r="B53" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7600,39 +7600,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>479663</v>
+        <v>479696</v>
       </c>
       <c r="R53" t="n">
-        <v>7027246</v>
+        <v>7027370</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7683,22 +7678,22 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7716,7 +7711,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122698247</v>
+        <v>122695752</v>
       </c>
       <c r="B54" t="n">
         <v>78766</v>
@@ -7756,13 +7751,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>479696</v>
+        <v>479748</v>
       </c>
       <c r="R54" t="n">
-        <v>7027370</v>
+        <v>7027283</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7843,10 +7838,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122695752</v>
+        <v>122697286</v>
       </c>
       <c r="B55" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7859,37 +7854,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>479748</v>
+        <v>479663</v>
       </c>
       <c r="R55" t="n">
-        <v>7027283</v>
+        <v>7027246</v>
       </c>
       <c r="S55" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7937,22 +7937,22 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7970,10 +7970,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122697882</v>
+        <v>122696290</v>
       </c>
       <c r="B56" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7986,37 +7986,51 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>479664</v>
+        <v>479695</v>
       </c>
       <c r="R56" t="n">
-        <v>7027326</v>
+        <v>7027185</v>
       </c>
       <c r="S56" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -8050,7 +8064,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Observerad i flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8065,26 +8079,6 @@
       <c r="AH56" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -8102,10 +8096,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122695492</v>
+        <v>122696111</v>
       </c>
       <c r="B57" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -8118,39 +8112,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>479770</v>
+        <v>479694</v>
       </c>
       <c r="R57" t="n">
-        <v>7027300</v>
+        <v>7027236</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -8185,11 +8174,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Växer på en lite smalare sälg intill lunglav.</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -8206,22 +8190,22 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8239,10 +8223,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122696111</v>
+        <v>122695703</v>
       </c>
       <c r="B58" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8255,37 +8239,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>479694</v>
+        <v>479753</v>
       </c>
       <c r="R58" t="n">
-        <v>7027236</v>
+        <v>7027296</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8317,6 +8306,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglav på två knäckta sälgar.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -8333,22 +8327,22 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8366,10 +8360,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122695703</v>
+        <v>122697882</v>
       </c>
       <c r="B59" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8382,42 +8376,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>479753</v>
+        <v>479664</v>
       </c>
       <c r="R59" t="n">
-        <v>7027296</v>
+        <v>7027326</v>
       </c>
       <c r="S59" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8451,7 +8440,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på två knäckta sälgar.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8470,22 +8459,22 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8503,10 +8492,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122696290</v>
+        <v>122695492</v>
       </c>
       <c r="B60" t="n">
-        <v>57631</v>
+        <v>79848</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8519,36 +8508,27 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -8557,10 +8537,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>479695</v>
+        <v>479770</v>
       </c>
       <c r="R60" t="n">
-        <v>7027185</v>
+        <v>7027300</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8597,7 +8577,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Observerad i flerskiktad äldre granskog.</t>
+          <t>Växer på en lite smalare sälg intill lunglav.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8612,6 +8592,26 @@
       <c r="AH60" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -11425,10 +11425,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122696521</v>
+        <v>122697966</v>
       </c>
       <c r="B82" t="n">
-        <v>57494</v>
+        <v>79847</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -11441,32 +11441,27 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -11475,13 +11470,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>479674</v>
+        <v>479660</v>
       </c>
       <c r="R82" t="n">
-        <v>7027109</v>
+        <v>7027363</v>
       </c>
       <c r="S82" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -11513,11 +11508,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Färska hackspår i stambasen av en smal gran i granskog med stora mängder liggande död ved.</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -11534,22 +11524,22 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -11567,10 +11557,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122697966</v>
+        <v>122696521</v>
       </c>
       <c r="B83" t="n">
-        <v>79847</v>
+        <v>57494</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -11583,27 +11573,32 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -11612,13 +11607,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>479660</v>
+        <v>479674</v>
       </c>
       <c r="R83" t="n">
-        <v>7027363</v>
+        <v>7027109</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -11650,6 +11645,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Färska hackspår i stambasen av en smal gran i granskog med stora mängder liggande död ved.</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -11666,22 +11666,22 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>

--- a/artfynd/A 60372-2024 artfynd.xlsx
+++ b/artfynd/A 60372-2024 artfynd.xlsx
@@ -7584,10 +7584,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122698247</v>
+        <v>122697286</v>
       </c>
       <c r="B53" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7600,34 +7600,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>479696</v>
+        <v>479663</v>
       </c>
       <c r="R53" t="n">
-        <v>7027370</v>
+        <v>7027246</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7678,22 +7683,22 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7711,7 +7716,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122695752</v>
+        <v>122698247</v>
       </c>
       <c r="B54" t="n">
         <v>78766</v>
@@ -7751,13 +7756,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>479748</v>
+        <v>479696</v>
       </c>
       <c r="R54" t="n">
-        <v>7027283</v>
+        <v>7027370</v>
       </c>
       <c r="S54" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7838,10 +7843,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122697286</v>
+        <v>122695752</v>
       </c>
       <c r="B55" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7854,42 +7859,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>479663</v>
+        <v>479748</v>
       </c>
       <c r="R55" t="n">
-        <v>7027246</v>
+        <v>7027283</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7937,22 +7937,22 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>

--- a/artfynd/A 60372-2024 artfynd.xlsx
+++ b/artfynd/A 60372-2024 artfynd.xlsx
@@ -7320,7 +7320,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122697690</v>
+        <v>122695101</v>
       </c>
       <c r="B51" t="n">
         <v>78766</v>
@@ -7360,10 +7360,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>479640</v>
+        <v>479696</v>
       </c>
       <c r="R51" t="n">
-        <v>7027281</v>
+        <v>7027544</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7396,6 +7396,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7447,7 +7452,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122696057</v>
+        <v>122697773</v>
       </c>
       <c r="B52" t="n">
         <v>79847</v>
@@ -7481,21 +7486,16 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>479675</v>
+        <v>479617</v>
       </c>
       <c r="R52" t="n">
-        <v>7027261</v>
+        <v>7027326</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7532,7 +7532,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På flera aspar.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7551,12 +7551,12 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7584,10 +7584,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122697286</v>
+        <v>122696521</v>
       </c>
       <c r="B53" t="n">
-        <v>79847</v>
+        <v>57494</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7600,27 +7600,32 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -7629,13 +7634,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>479663</v>
+        <v>479674</v>
       </c>
       <c r="R53" t="n">
-        <v>7027246</v>
+        <v>7027109</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7667,6 +7672,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Färska hackspår i stambasen av en smal gran i granskog med stora mängder liggande död ved.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -7683,22 +7693,22 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7843,10 +7853,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122695752</v>
+        <v>122697455</v>
       </c>
       <c r="B55" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7859,37 +7869,51 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>479748</v>
+        <v>479680</v>
       </c>
       <c r="R55" t="n">
-        <v>7027283</v>
+        <v>7027206</v>
       </c>
       <c r="S55" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7921,6 +7945,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Observation av en spillkråka som gav ifrån sig två olika lockläten. I gammal granskog med gott om asp och tall som utgör lämpliga substrat för bohål. Även bitvis relativt gott om död ved här.</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -7933,26 +7962,6 @@
       <c r="AH55" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7970,10 +7979,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122696290</v>
+        <v>122697690</v>
       </c>
       <c r="B56" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7986,48 +7995,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>479695</v>
+        <v>479640</v>
       </c>
       <c r="R56" t="n">
-        <v>7027185</v>
+        <v>7027281</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -8062,11 +8057,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Observerad i flerskiktad äldre granskog.</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -8079,6 +8069,26 @@
       <c r="AH56" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -8096,7 +8106,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122696111</v>
+        <v>122697352</v>
       </c>
       <c r="B57" t="n">
         <v>78766</v>
@@ -8136,10 +8146,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>479694</v>
+        <v>479674</v>
       </c>
       <c r="R57" t="n">
-        <v>7027236</v>
+        <v>7027178</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -8223,10 +8233,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122695703</v>
+        <v>122697882</v>
       </c>
       <c r="B58" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8239,42 +8249,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>479753</v>
+        <v>479664</v>
       </c>
       <c r="R58" t="n">
-        <v>7027296</v>
+        <v>7027326</v>
       </c>
       <c r="S58" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8308,7 +8313,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på två knäckta sälgar.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8327,22 +8332,22 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8360,10 +8365,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122697882</v>
+        <v>122695516</v>
       </c>
       <c r="B59" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8376,37 +8381,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>479664</v>
+        <v>479766</v>
       </c>
       <c r="R59" t="n">
-        <v>7027326</v>
+        <v>7027310</v>
       </c>
       <c r="S59" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8440,7 +8450,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Växer på en lite smalare sälg intill skrovellav.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8459,22 +8469,22 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8492,10 +8502,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122695492</v>
+        <v>122695273</v>
       </c>
       <c r="B60" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8508,27 +8518,32 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -8540,7 +8555,7 @@
         <v>479770</v>
       </c>
       <c r="R60" t="n">
-        <v>7027300</v>
+        <v>7027401</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8577,7 +8592,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Växer på en lite smalare sälg intill lunglav.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8596,22 +8611,22 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8629,10 +8644,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122696876</v>
+        <v>122696290</v>
       </c>
       <c r="B61" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8645,27 +8660,31 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -8679,13 +8698,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>479628</v>
+        <v>479695</v>
       </c>
       <c r="R61" t="n">
-        <v>7027133</v>
+        <v>7027185</v>
       </c>
       <c r="S61" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8719,7 +8738,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen av en gran. I äldre granskog med minst medelhöga till höga livsmiljövärden för tretåig hackspett. Även gott om liggande död ved här. Finns även skalade döda granar här som indikerar potentiella födosökspår efter tretåig hackspett.</t>
+          <t>Observerad i flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8734,26 +8753,6 @@
       <c r="AH61" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8903,7 +8902,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122698275</v>
+        <v>122697534</v>
       </c>
       <c r="B63" t="n">
         <v>78766</v>
@@ -8943,10 +8942,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>479734</v>
+        <v>479644</v>
       </c>
       <c r="R63" t="n">
-        <v>7027357</v>
+        <v>7027243</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8981,11 +8980,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -8997,7 +8991,7 @@
       </c>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ63" t="inlineStr">
@@ -9035,10 +9029,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122695273</v>
+        <v>122695322</v>
       </c>
       <c r="B64" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -9051,32 +9045,27 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -9085,10 +9074,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>479770</v>
+        <v>479771</v>
       </c>
       <c r="R64" t="n">
-        <v>7027401</v>
+        <v>7027387</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -9125,7 +9114,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>På en lutande krokig sälg.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9144,22 +9133,22 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -9177,10 +9166,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122695075</v>
+        <v>122697966</v>
       </c>
       <c r="B65" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9193,34 +9182,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>479699</v>
+        <v>479660</v>
       </c>
       <c r="R65" t="n">
-        <v>7027521</v>
+        <v>7027363</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -9255,11 +9249,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -9276,22 +9265,22 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9309,10 +9298,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122698232</v>
+        <v>122695669</v>
       </c>
       <c r="B66" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9325,21 +9314,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -9349,13 +9338,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>479698</v>
+        <v>479761</v>
       </c>
       <c r="R66" t="n">
-        <v>7027368</v>
+        <v>7027298</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -9436,10 +9425,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122695669</v>
+        <v>122695655</v>
       </c>
       <c r="B67" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9452,37 +9441,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>479761</v>
+        <v>479759</v>
       </c>
       <c r="R67" t="n">
-        <v>7027298</v>
+        <v>7027292</v>
       </c>
       <c r="S67" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -9512,6 +9506,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Växer på två granar intill en sälg med ymnig påväxt av lunglav.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9563,7 +9562,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122697862</v>
+        <v>122698232</v>
       </c>
       <c r="B68" t="n">
         <v>78766</v>
@@ -9603,10 +9602,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>479630</v>
+        <v>479698</v>
       </c>
       <c r="R68" t="n">
-        <v>7027362</v>
+        <v>7027368</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9690,10 +9689,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122695602</v>
+        <v>122697757</v>
       </c>
       <c r="B69" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9706,21 +9705,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -9735,10 +9734,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>479774</v>
+        <v>479615</v>
       </c>
       <c r="R69" t="n">
-        <v>7027322</v>
+        <v>7027315</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9771,11 +9770,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ymnigt med lunglav på en gammal sälg med fårad bark.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9827,7 +9821,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122696303</v>
+        <v>122697862</v>
       </c>
       <c r="B70" t="n">
         <v>78766</v>
@@ -9867,13 +9861,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>479685</v>
+        <v>479630</v>
       </c>
       <c r="R70" t="n">
-        <v>7027165</v>
+        <v>7027362</v>
       </c>
       <c r="S70" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9954,7 +9948,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122695516</v>
+        <v>122695703</v>
       </c>
       <c r="B71" t="n">
         <v>79847</v>
@@ -9999,13 +9993,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>479766</v>
+        <v>479753</v>
       </c>
       <c r="R71" t="n">
-        <v>7027310</v>
+        <v>7027296</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -10039,7 +10033,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Växer på en lite smalare sälg intill skrovellav.</t>
+          <t>Rikligt med lunglav på två knäckta sälgar.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -10091,7 +10085,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122698085</v>
+        <v>122695943</v>
       </c>
       <c r="B72" t="n">
         <v>78766</v>
@@ -10131,10 +10125,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>479659</v>
+        <v>479756</v>
       </c>
       <c r="R72" t="n">
-        <v>7027303</v>
+        <v>7027364</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -10218,10 +10212,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122696537</v>
+        <v>122696303</v>
       </c>
       <c r="B73" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -10234,47 +10228,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>479669</v>
+        <v>479685</v>
       </c>
       <c r="R73" t="n">
-        <v>7027116</v>
+        <v>7027165</v>
       </c>
       <c r="S73" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -10306,11 +10290,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -10337,12 +10316,12 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -10360,10 +10339,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122695101</v>
+        <v>122697666</v>
       </c>
       <c r="B74" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10376,37 +10355,51 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>479696</v>
+        <v>479632</v>
       </c>
       <c r="R74" t="n">
-        <v>7027544</v>
+        <v>7027297</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -10438,11 +10431,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -10469,12 +10457,12 @@
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10492,10 +10480,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122697534</v>
+        <v>122697286</v>
       </c>
       <c r="B75" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10508,34 +10496,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>479644</v>
+        <v>479663</v>
       </c>
       <c r="R75" t="n">
-        <v>7027243</v>
+        <v>7027246</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10581,27 +10574,27 @@
       </c>
       <c r="AH75" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -10619,10 +10612,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122696471</v>
+        <v>122696111</v>
       </c>
       <c r="B76" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10635,47 +10628,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>479681</v>
+        <v>479694</v>
       </c>
       <c r="R76" t="n">
-        <v>7027123</v>
+        <v>7027236</v>
       </c>
       <c r="S76" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -10707,11 +10690,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på stambasen.</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -10738,12 +10716,12 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -10761,7 +10739,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122697352</v>
+        <v>122698275</v>
       </c>
       <c r="B77" t="n">
         <v>78766</v>
@@ -10801,10 +10779,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>479674</v>
+        <v>479734</v>
       </c>
       <c r="R77" t="n">
-        <v>7027178</v>
+        <v>7027357</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10837,6 +10815,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10888,10 +10871,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122695682</v>
+        <v>122695075</v>
       </c>
       <c r="B78" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10904,39 +10887,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>479763</v>
+        <v>479699</v>
       </c>
       <c r="R78" t="n">
-        <v>7027300</v>
+        <v>7027521</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10973,7 +10951,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På en smal krokig sälg.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10992,22 +10970,22 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -11025,10 +11003,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122697757</v>
+        <v>122698085</v>
       </c>
       <c r="B79" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -11041,39 +11019,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>479615</v>
+        <v>479659</v>
       </c>
       <c r="R79" t="n">
-        <v>7027315</v>
+        <v>7027303</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -11124,22 +11097,22 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -11157,7 +11130,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122695943</v>
+        <v>122696014</v>
       </c>
       <c r="B80" t="n">
         <v>78766</v>
@@ -11197,10 +11170,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>479756</v>
+        <v>479718</v>
       </c>
       <c r="R80" t="n">
-        <v>7027364</v>
+        <v>7027277</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -11284,10 +11257,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122697666</v>
+        <v>122696471</v>
       </c>
       <c r="B81" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -11300,36 +11273,32 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -11338,13 +11307,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>479632</v>
+        <v>479681</v>
       </c>
       <c r="R81" t="n">
-        <v>7027297</v>
+        <v>7027123</v>
       </c>
       <c r="S81" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -11376,6 +11345,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på stambasen.</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -11402,12 +11376,12 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -11425,7 +11399,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122697966</v>
+        <v>122695682</v>
       </c>
       <c r="B82" t="n">
         <v>79847</v>
@@ -11470,10 +11444,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>479660</v>
+        <v>479763</v>
       </c>
       <c r="R82" t="n">
-        <v>7027363</v>
+        <v>7027300</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -11508,6 +11482,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>På en smal krokig sälg.</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -11524,12 +11503,12 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM82" t="inlineStr">
@@ -11539,7 +11518,7 @@
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -11557,10 +11536,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122696521</v>
+        <v>122696537</v>
       </c>
       <c r="B83" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -11573,16 +11552,16 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -11593,7 +11572,7 @@
       <c r="I83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -11607,10 +11586,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>479674</v>
+        <v>479669</v>
       </c>
       <c r="R83" t="n">
-        <v>7027109</v>
+        <v>7027116</v>
       </c>
       <c r="S83" t="n">
         <v>8</v>
@@ -11647,7 +11626,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Färska hackspår i stambasen av en smal gran i granskog med stora mängder liggande död ved.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11699,7 +11678,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122695926</v>
+        <v>122696057</v>
       </c>
       <c r="B84" t="n">
         <v>79847</v>
@@ -11744,10 +11723,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>479752</v>
+        <v>479675</v>
       </c>
       <c r="R84" t="n">
-        <v>7027344</v>
+        <v>7027261</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11784,7 +11763,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Ymnigt med lunglav på en gammal sälg.</t>
+          <t>På flera aspar.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11803,12 +11782,12 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM84" t="inlineStr">
@@ -11818,7 +11797,7 @@
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -11836,10 +11815,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122696014</v>
+        <v>122695926</v>
       </c>
       <c r="B85" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11852,34 +11831,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>479718</v>
+        <v>479752</v>
       </c>
       <c r="R85" t="n">
-        <v>7027277</v>
+        <v>7027344</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11914,6 +11898,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ymnigt med lunglav på en gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -11930,22 +11919,22 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -11963,10 +11952,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122695655</v>
+        <v>122695752</v>
       </c>
       <c r="B86" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11979,39 +11968,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>479759</v>
+        <v>479748</v>
       </c>
       <c r="R86" t="n">
-        <v>7027292</v>
+        <v>7027283</v>
       </c>
       <c r="S86" t="n">
         <v>12</v>
@@ -12044,11 +12028,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Växer på två granar intill en sälg med ymnig påväxt av lunglav.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -12100,10 +12079,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122695011</v>
+        <v>122695492</v>
       </c>
       <c r="B87" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -12116,34 +12095,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>479729</v>
+        <v>479770</v>
       </c>
       <c r="R87" t="n">
-        <v>7027486</v>
+        <v>7027300</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -12180,7 +12164,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Växer på en lite smalare sälg intill lunglav.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -12199,22 +12183,22 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -12232,10 +12216,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122695322</v>
+        <v>122695011</v>
       </c>
       <c r="B88" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -12248,39 +12232,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>479771</v>
+        <v>479729</v>
       </c>
       <c r="R88" t="n">
-        <v>7027387</v>
+        <v>7027486</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -12317,7 +12296,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>På en lutande krokig sälg.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -12336,22 +12315,22 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -12369,7 +12348,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122697773</v>
+        <v>122695602</v>
       </c>
       <c r="B89" t="n">
         <v>79847</v>
@@ -12403,16 +12382,21 @@
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>479617</v>
+        <v>479774</v>
       </c>
       <c r="R89" t="n">
-        <v>7027326</v>
+        <v>7027322</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -12449,7 +12433,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Enstaka bålar.</t>
+          <t>Ymnigt med lunglav på en gammal sälg med fårad bark.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -12501,10 +12485,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122697455</v>
+        <v>122696876</v>
       </c>
       <c r="B90" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -12517,16 +12501,16 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -12534,14 +12518,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -12555,13 +12535,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>479680</v>
+        <v>479628</v>
       </c>
       <c r="R90" t="n">
-        <v>7027206</v>
+        <v>7027133</v>
       </c>
       <c r="S90" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -12595,7 +12575,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Observation av en spillkråka som gav ifrån sig två olika lockläten. I gammal granskog med gott om asp och tall som utgör lämpliga substrat för bohål. Även bitvis relativt gott om död ved här.</t>
+          <t>Färska och äldre ringhack på stambasen av en gran. I äldre granskog med minst medelhöga till höga livsmiljövärden för tretåig hackspett. Även gott om liggande död ved här. Finns även skalade döda granar här som indikerar potentiella födosökspår efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -12610,6 +12590,26 @@
       <c r="AH90" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM90" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>

--- a/artfynd/A 60372-2024 artfynd.xlsx
+++ b/artfynd/A 60372-2024 artfynd.xlsx
@@ -7320,10 +7320,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122695101</v>
+        <v>122695354</v>
       </c>
       <c r="B51" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7336,21 +7336,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -7360,10 +7360,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>479696</v>
+        <v>479765</v>
       </c>
       <c r="R51" t="n">
-        <v>7027544</v>
+        <v>7027389</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7400,7 +7400,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På en lutande krokig sälg.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7419,22 +7419,22 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7452,10 +7452,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122697773</v>
+        <v>122698232</v>
       </c>
       <c r="B52" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7468,21 +7468,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -7492,10 +7492,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>479617</v>
+        <v>479698</v>
       </c>
       <c r="R52" t="n">
-        <v>7027326</v>
+        <v>7027368</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7530,11 +7530,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -7551,22 +7546,22 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7584,10 +7579,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122696521</v>
+        <v>122696057</v>
       </c>
       <c r="B53" t="n">
-        <v>57494</v>
+        <v>79847</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7600,32 +7595,27 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -7634,13 +7624,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>479674</v>
+        <v>479675</v>
       </c>
       <c r="R53" t="n">
-        <v>7027109</v>
+        <v>7027261</v>
       </c>
       <c r="S53" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7674,7 +7664,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Färska hackspår i stambasen av en smal gran i granskog med stora mängder liggande död ved.</t>
+          <t>På flera aspar.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7693,22 +7683,22 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7726,7 +7716,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122698247</v>
+        <v>122697882</v>
       </c>
       <c r="B54" t="n">
         <v>78766</v>
@@ -7766,13 +7756,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>479696</v>
+        <v>479664</v>
       </c>
       <c r="R54" t="n">
-        <v>7027370</v>
+        <v>7027326</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7802,6 +7792,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7853,10 +7848,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122697455</v>
+        <v>122695602</v>
       </c>
       <c r="B55" t="n">
-        <v>57494</v>
+        <v>79847</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7869,36 +7864,27 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -7907,13 +7893,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>479680</v>
+        <v>479774</v>
       </c>
       <c r="R55" t="n">
-        <v>7027206</v>
+        <v>7027322</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7947,7 +7933,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Observation av en spillkråka som gav ifrån sig två olika lockläten. I gammal granskog med gott om asp och tall som utgör lämpliga substrat för bohål. Även bitvis relativt gott om död ved här.</t>
+          <t>Ymnigt med lunglav på en gammal sälg med fårad bark.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7962,6 +7948,26 @@
       <c r="AH55" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7979,10 +7985,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122697690</v>
+        <v>122695703</v>
       </c>
       <c r="B56" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7995,37 +8001,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>479640</v>
+        <v>479753</v>
       </c>
       <c r="R56" t="n">
-        <v>7027281</v>
+        <v>7027296</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -8057,6 +8068,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglav på två knäckta sälgar.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -8073,22 +8089,22 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -8106,10 +8122,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122697352</v>
+        <v>122695655</v>
       </c>
       <c r="B57" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -8122,37 +8138,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>479674</v>
+        <v>479759</v>
       </c>
       <c r="R57" t="n">
-        <v>7027178</v>
+        <v>7027292</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -8182,6 +8203,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Växer på två granar intill en sälg med ymnig påväxt av lunglav.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8233,10 +8259,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122697882</v>
+        <v>122696471</v>
       </c>
       <c r="B58" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8249,34 +8275,44 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>479664</v>
+        <v>479681</v>
       </c>
       <c r="R58" t="n">
-        <v>7027326</v>
+        <v>7027123</v>
       </c>
       <c r="S58" t="n">
         <v>8</v>
@@ -8313,7 +8349,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8342,12 +8378,12 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8365,10 +8401,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122695516</v>
+        <v>122698085</v>
       </c>
       <c r="B59" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8381,39 +8417,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>479766</v>
+        <v>479659</v>
       </c>
       <c r="R59" t="n">
-        <v>7027310</v>
+        <v>7027303</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8448,11 +8479,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Växer på en lite smalare sälg intill skrovellav.</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -8469,22 +8495,22 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8502,10 +8528,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122695273</v>
+        <v>122697286</v>
       </c>
       <c r="B60" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8518,32 +8544,27 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -8552,10 +8573,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>479770</v>
+        <v>479663</v>
       </c>
       <c r="R60" t="n">
-        <v>7027401</v>
+        <v>7027246</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8590,11 +8611,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -8611,22 +8627,22 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8644,10 +8660,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122696290</v>
+        <v>122695926</v>
       </c>
       <c r="B61" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8660,36 +8676,27 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -8698,10 +8705,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>479695</v>
+        <v>479752</v>
       </c>
       <c r="R61" t="n">
-        <v>7027185</v>
+        <v>7027344</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8738,7 +8745,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Observerad i flerskiktad äldre granskog.</t>
+          <t>Ymnigt med lunglav på en gammal sälg.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8753,6 +8760,26 @@
       <c r="AH61" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8770,10 +8797,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122695354</v>
+        <v>122696014</v>
       </c>
       <c r="B62" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8786,21 +8813,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -8810,10 +8837,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>479765</v>
+        <v>479718</v>
       </c>
       <c r="R62" t="n">
-        <v>7027389</v>
+        <v>7027277</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8848,11 +8875,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>På en lutande krokig sälg.</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -8869,22 +8891,22 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8902,10 +8924,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122697534</v>
+        <v>122696521</v>
       </c>
       <c r="B63" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8918,37 +8940,47 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>479644</v>
+        <v>479674</v>
       </c>
       <c r="R63" t="n">
-        <v>7027243</v>
+        <v>7027109</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8980,6 +9012,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Färska hackspår i stambasen av en smal gran i granskog med stora mängder liggande död ved.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -8991,7 +9028,7 @@
       </c>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ63" t="inlineStr">
@@ -9006,12 +9043,12 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -9029,10 +9066,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122695322</v>
+        <v>122697352</v>
       </c>
       <c r="B64" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -9045,39 +9082,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>479771</v>
+        <v>479674</v>
       </c>
       <c r="R64" t="n">
-        <v>7027387</v>
+        <v>7027178</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -9112,11 +9144,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>På en lutande krokig sälg.</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -9133,22 +9160,22 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -9166,10 +9193,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122697966</v>
+        <v>122695075</v>
       </c>
       <c r="B65" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9182,39 +9209,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>479660</v>
+        <v>479699</v>
       </c>
       <c r="R65" t="n">
-        <v>7027363</v>
+        <v>7027521</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -9249,6 +9271,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -9265,22 +9292,22 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9298,10 +9325,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122695669</v>
+        <v>122695516</v>
       </c>
       <c r="B66" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9314,37 +9341,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>479761</v>
+        <v>479766</v>
       </c>
       <c r="R66" t="n">
-        <v>7027298</v>
+        <v>7027310</v>
       </c>
       <c r="S66" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -9376,6 +9408,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Växer på en lite smalare sälg intill skrovellav.</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -9392,22 +9429,22 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9425,10 +9462,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122695655</v>
+        <v>122696111</v>
       </c>
       <c r="B67" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9441,42 +9478,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>479759</v>
+        <v>479694</v>
       </c>
       <c r="R67" t="n">
-        <v>7027292</v>
+        <v>7027236</v>
       </c>
       <c r="S67" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -9506,11 +9538,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Växer på två granar intill en sälg med ymnig påväxt av lunglav.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9562,10 +9589,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122698232</v>
+        <v>122696876</v>
       </c>
       <c r="B68" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9578,37 +9605,47 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>479698</v>
+        <v>479628</v>
       </c>
       <c r="R68" t="n">
-        <v>7027368</v>
+        <v>7027133</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -9640,6 +9677,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på stambasen av en gran. I äldre granskog med minst medelhöga till höga livsmiljövärden för tretåig hackspett. Även gott om liggande död ved här. Finns även skalade döda granar här som indikerar potentiella födosökspår efter tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -9666,12 +9708,12 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9689,10 +9731,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122697757</v>
+        <v>122695101</v>
       </c>
       <c r="B69" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9705,39 +9747,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>479615</v>
+        <v>479696</v>
       </c>
       <c r="R69" t="n">
-        <v>7027315</v>
+        <v>7027544</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9772,6 +9809,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -9788,22 +9830,22 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9821,7 +9863,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122697862</v>
+        <v>122698247</v>
       </c>
       <c r="B70" t="n">
         <v>78766</v>
@@ -9861,10 +9903,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>479630</v>
+        <v>479696</v>
       </c>
       <c r="R70" t="n">
-        <v>7027362</v>
+        <v>7027370</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9948,7 +9990,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122695703</v>
+        <v>122695322</v>
       </c>
       <c r="B71" t="n">
         <v>79847</v>
@@ -9993,13 +10035,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>479753</v>
+        <v>479771</v>
       </c>
       <c r="R71" t="n">
-        <v>7027296</v>
+        <v>7027387</v>
       </c>
       <c r="S71" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -10033,7 +10075,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på två knäckta sälgar.</t>
+          <t>På en lutande krokig sälg.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -10085,10 +10127,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122695943</v>
+        <v>122695682</v>
       </c>
       <c r="B72" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -10101,34 +10143,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>479756</v>
+        <v>479763</v>
       </c>
       <c r="R72" t="n">
-        <v>7027364</v>
+        <v>7027300</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -10163,6 +10210,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På en smal krokig sälg.</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -10179,22 +10231,22 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -10212,7 +10264,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122696303</v>
+        <v>122695011</v>
       </c>
       <c r="B73" t="n">
         <v>78766</v>
@@ -10252,13 +10304,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>479685</v>
+        <v>479729</v>
       </c>
       <c r="R73" t="n">
-        <v>7027165</v>
+        <v>7027486</v>
       </c>
       <c r="S73" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -10288,6 +10340,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10339,10 +10396,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122697666</v>
+        <v>122698275</v>
       </c>
       <c r="B74" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10355,51 +10412,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>479632</v>
+        <v>479734</v>
       </c>
       <c r="R74" t="n">
-        <v>7027297</v>
+        <v>7027357</v>
       </c>
       <c r="S74" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -10431,6 +10474,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -10457,12 +10505,12 @@
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10480,10 +10528,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122697286</v>
+        <v>122697862</v>
       </c>
       <c r="B75" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10496,39 +10544,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>479663</v>
+        <v>479630</v>
       </c>
       <c r="R75" t="n">
-        <v>7027246</v>
+        <v>7027362</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10579,22 +10622,22 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -10612,7 +10655,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122696111</v>
+        <v>122695752</v>
       </c>
       <c r="B76" t="n">
         <v>78766</v>
@@ -10652,13 +10695,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>479694</v>
+        <v>479748</v>
       </c>
       <c r="R76" t="n">
-        <v>7027236</v>
+        <v>7027283</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -10739,10 +10782,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122698275</v>
+        <v>122696290</v>
       </c>
       <c r="B77" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10755,34 +10798,48 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>479734</v>
+        <v>479695</v>
       </c>
       <c r="R77" t="n">
-        <v>7027357</v>
+        <v>7027185</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10819,7 +10876,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Observerad i flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10834,26 +10891,6 @@
       <c r="AH77" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10871,10 +10908,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122695075</v>
+        <v>122695273</v>
       </c>
       <c r="B78" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10887,34 +10924,44 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>479699</v>
+        <v>479770</v>
       </c>
       <c r="R78" t="n">
-        <v>7027521</v>
+        <v>7027401</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10951,7 +10998,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10980,12 +11027,12 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -11003,10 +11050,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122698085</v>
+        <v>122695669</v>
       </c>
       <c r="B79" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -11019,21 +11066,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -11043,13 +11090,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>479659</v>
+        <v>479761</v>
       </c>
       <c r="R79" t="n">
-        <v>7027303</v>
+        <v>7027298</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -11130,10 +11177,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122696014</v>
+        <v>122695492</v>
       </c>
       <c r="B80" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -11146,34 +11193,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>479718</v>
+        <v>479770</v>
       </c>
       <c r="R80" t="n">
-        <v>7027277</v>
+        <v>7027300</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -11208,6 +11260,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Växer på en lite smalare sälg intill lunglav.</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -11224,22 +11281,22 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -11257,10 +11314,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122696471</v>
+        <v>122697534</v>
       </c>
       <c r="B81" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -11273,47 +11330,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>479681</v>
+        <v>479644</v>
       </c>
       <c r="R81" t="n">
-        <v>7027123</v>
+        <v>7027243</v>
       </c>
       <c r="S81" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -11345,11 +11392,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på stambasen.</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -11361,7 +11403,7 @@
       </c>
       <c r="AH81" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ81" t="inlineStr">
@@ -11376,12 +11418,12 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -11399,10 +11441,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122695682</v>
+        <v>122697757</v>
       </c>
       <c r="B82" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -11415,21 +11457,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -11444,10 +11486,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>479763</v>
+        <v>479615</v>
       </c>
       <c r="R82" t="n">
-        <v>7027300</v>
+        <v>7027315</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -11480,11 +11522,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>På en smal krokig sälg.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11536,10 +11573,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122696537</v>
+        <v>122697690</v>
       </c>
       <c r="B83" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -11552,47 +11589,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>479669</v>
+        <v>479640</v>
       </c>
       <c r="R83" t="n">
-        <v>7027116</v>
+        <v>7027281</v>
       </c>
       <c r="S83" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -11624,11 +11651,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -11655,12 +11677,12 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -11678,10 +11700,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122696057</v>
+        <v>122696303</v>
       </c>
       <c r="B84" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11694,42 +11716,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>479675</v>
+        <v>479685</v>
       </c>
       <c r="R84" t="n">
-        <v>7027261</v>
+        <v>7027165</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -11761,11 +11778,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>På flera aspar.</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -11782,22 +11794,22 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -11815,7 +11827,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122695926</v>
+        <v>122697773</v>
       </c>
       <c r="B85" t="n">
         <v>79847</v>
@@ -11849,21 +11861,16 @@
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>479752</v>
+        <v>479617</v>
       </c>
       <c r="R85" t="n">
-        <v>7027344</v>
+        <v>7027326</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11900,7 +11907,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Ymnigt med lunglav på en gammal sälg.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11952,10 +11959,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122695752</v>
+        <v>122697455</v>
       </c>
       <c r="B86" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11968,37 +11975,51 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>479748</v>
+        <v>479680</v>
       </c>
       <c r="R86" t="n">
-        <v>7027283</v>
+        <v>7027206</v>
       </c>
       <c r="S86" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -12030,6 +12051,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Observation av en spillkråka som gav ifrån sig två olika lockläten. I gammal granskog med gott om asp och tall som utgör lämpliga substrat för bohål. Även bitvis relativt gott om död ved här.</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -12042,26 +12068,6 @@
       <c r="AH86" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -12079,10 +12085,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122695492</v>
+        <v>122697966</v>
       </c>
       <c r="B87" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -12095,21 +12101,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -12124,10 +12130,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>479770</v>
+        <v>479660</v>
       </c>
       <c r="R87" t="n">
-        <v>7027300</v>
+        <v>7027363</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -12162,11 +12168,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Växer på en lite smalare sälg intill lunglav.</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
@@ -12183,12 +12184,12 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM87" t="inlineStr">
@@ -12198,7 +12199,7 @@
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -12216,10 +12217,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122695011</v>
+        <v>122696537</v>
       </c>
       <c r="B88" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -12232,37 +12233,47 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>479729</v>
+        <v>479669</v>
       </c>
       <c r="R88" t="n">
-        <v>7027486</v>
+        <v>7027116</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -12296,7 +12307,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -12325,12 +12336,12 @@
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -12348,10 +12359,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122695602</v>
+        <v>122697666</v>
       </c>
       <c r="B89" t="n">
-        <v>79847</v>
+        <v>90970</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -12364,27 +12375,36 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -12393,13 +12413,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>479774</v>
+        <v>479632</v>
       </c>
       <c r="R89" t="n">
-        <v>7027322</v>
+        <v>7027297</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -12431,11 +12451,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Ymnigt med lunglav på en gammal sälg med fårad bark.</t>
-        </is>
-      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
@@ -12452,22 +12467,22 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -12485,10 +12500,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122696876</v>
+        <v>122695943</v>
       </c>
       <c r="B90" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -12501,47 +12516,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>479628</v>
+        <v>479756</v>
       </c>
       <c r="R90" t="n">
-        <v>7027133</v>
+        <v>7027364</v>
       </c>
       <c r="S90" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -12573,11 +12578,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på stambasen av en gran. I äldre granskog med minst medelhöga till höga livsmiljövärden för tretåig hackspett. Även gott om liggande död ved här. Finns även skalade döda granar här som indikerar potentiella födosökspår efter tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
@@ -12604,12 +12604,12 @@
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>

--- a/artfynd/A 60372-2024 artfynd.xlsx
+++ b/artfynd/A 60372-2024 artfynd.xlsx
@@ -8122,10 +8122,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122695655</v>
+        <v>122696471</v>
       </c>
       <c r="B57" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -8138,27 +8138,32 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -8167,13 +8172,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>479759</v>
+        <v>479681</v>
       </c>
       <c r="R57" t="n">
-        <v>7027292</v>
+        <v>7027123</v>
       </c>
       <c r="S57" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -8207,7 +8212,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Växer på två granar intill en sälg med ymnig påväxt av lunglav.</t>
+          <t>Äldre ringhack på stambasen.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8236,12 +8241,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8259,10 +8264,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122696471</v>
+        <v>122695655</v>
       </c>
       <c r="B58" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8275,32 +8280,27 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -8309,13 +8309,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>479681</v>
+        <v>479759</v>
       </c>
       <c r="R58" t="n">
-        <v>7027123</v>
+        <v>7027292</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8349,7 +8349,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen.</t>
+          <t>Växer på två granar intill en sälg med ymnig påväxt av lunglav.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8378,12 +8378,12 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -10127,10 +10127,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122695682</v>
+        <v>122696290</v>
       </c>
       <c r="B72" t="n">
-        <v>79847</v>
+        <v>57631</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -10143,27 +10143,36 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>med soral</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -10172,10 +10181,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>479763</v>
+        <v>479695</v>
       </c>
       <c r="R72" t="n">
-        <v>7027300</v>
+        <v>7027185</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -10212,7 +10221,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>På en smal krokig sälg.</t>
+          <t>Observerad i flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -10227,26 +10236,6 @@
       <c r="AH72" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -10264,10 +10253,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122695011</v>
+        <v>122695682</v>
       </c>
       <c r="B73" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -10280,34 +10269,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>479729</v>
+        <v>479763</v>
       </c>
       <c r="R73" t="n">
-        <v>7027486</v>
+        <v>7027300</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -10344,7 +10338,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På en smal krokig sälg.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10363,22 +10357,22 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -10396,7 +10390,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122698275</v>
+        <v>122695011</v>
       </c>
       <c r="B74" t="n">
         <v>78766</v>
@@ -10436,10 +10430,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>479734</v>
+        <v>479729</v>
       </c>
       <c r="R74" t="n">
-        <v>7027357</v>
+        <v>7027486</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10528,7 +10522,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122697862</v>
+        <v>122698275</v>
       </c>
       <c r="B75" t="n">
         <v>78766</v>
@@ -10568,10 +10562,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>479630</v>
+        <v>479734</v>
       </c>
       <c r="R75" t="n">
-        <v>7027362</v>
+        <v>7027357</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10604,6 +10598,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10655,7 +10654,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122695752</v>
+        <v>122697862</v>
       </c>
       <c r="B76" t="n">
         <v>78766</v>
@@ -10695,13 +10694,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>479748</v>
+        <v>479630</v>
       </c>
       <c r="R76" t="n">
-        <v>7027283</v>
+        <v>7027362</v>
       </c>
       <c r="S76" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -10782,10 +10781,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122696290</v>
+        <v>122695752</v>
       </c>
       <c r="B77" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10798,51 +10797,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>479695</v>
+        <v>479748</v>
       </c>
       <c r="R77" t="n">
-        <v>7027185</v>
+        <v>7027283</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -10874,11 +10859,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Observerad i flerskiktad äldre granskog.</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -10891,6 +10871,26 @@
       <c r="AH77" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -12359,10 +12359,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122697666</v>
+        <v>122695943</v>
       </c>
       <c r="B89" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -12375,51 +12375,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>479632</v>
+        <v>479756</v>
       </c>
       <c r="R89" t="n">
-        <v>7027297</v>
+        <v>7027364</v>
       </c>
       <c r="S89" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -12477,12 +12463,12 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -12500,10 +12486,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122695943</v>
+        <v>122697666</v>
       </c>
       <c r="B90" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -12516,37 +12502,51 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>479756</v>
+        <v>479632</v>
       </c>
       <c r="R90" t="n">
-        <v>7027364</v>
+        <v>7027297</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -12604,12 +12604,12 @@
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>

--- a/artfynd/A 60372-2024 artfynd.xlsx
+++ b/artfynd/A 60372-2024 artfynd.xlsx
@@ -11050,10 +11050,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122695669</v>
+        <v>122697534</v>
       </c>
       <c r="B79" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -11066,21 +11066,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -11090,13 +11090,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>479761</v>
+        <v>479644</v>
       </c>
       <c r="R79" t="n">
-        <v>7027298</v>
+        <v>7027243</v>
       </c>
       <c r="S79" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
       </c>
       <c r="AH79" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ79" t="inlineStr">
@@ -11177,7 +11177,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122695492</v>
+        <v>122695669</v>
       </c>
       <c r="B80" t="n">
         <v>79848</v>
@@ -11211,24 +11211,19 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>479770</v>
+        <v>479761</v>
       </c>
       <c r="R80" t="n">
-        <v>7027300</v>
+        <v>7027298</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -11260,11 +11255,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Växer på en lite smalare sälg intill lunglav.</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -11281,22 +11271,22 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -11314,10 +11304,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122697534</v>
+        <v>122695492</v>
       </c>
       <c r="B81" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -11330,34 +11320,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>479644</v>
+        <v>479770</v>
       </c>
       <c r="R81" t="n">
-        <v>7027243</v>
+        <v>7027300</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -11392,6 +11387,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Växer på en lite smalare sälg intill lunglav.</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -11403,27 +11403,27 @@
       </c>
       <c r="AH81" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>

--- a/artfynd/A 60372-2024 artfynd.xlsx
+++ b/artfynd/A 60372-2024 artfynd.xlsx
@@ -10127,10 +10127,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122696290</v>
+        <v>122695682</v>
       </c>
       <c r="B72" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -10143,36 +10143,27 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -10181,10 +10172,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>479695</v>
+        <v>479763</v>
       </c>
       <c r="R72" t="n">
-        <v>7027185</v>
+        <v>7027300</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -10221,7 +10212,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Observerad i flerskiktad äldre granskog.</t>
+          <t>På en smal krokig sälg.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -10236,6 +10227,26 @@
       <c r="AH72" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM72" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -10253,10 +10264,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122695682</v>
+        <v>122695011</v>
       </c>
       <c r="B73" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -10269,39 +10280,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>479763</v>
+        <v>479729</v>
       </c>
       <c r="R73" t="n">
-        <v>7027300</v>
+        <v>7027486</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -10338,7 +10344,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>På en smal krokig sälg.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10357,22 +10363,22 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -10390,7 +10396,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122695011</v>
+        <v>122698275</v>
       </c>
       <c r="B74" t="n">
         <v>78766</v>
@@ -10430,10 +10436,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>479729</v>
+        <v>479734</v>
       </c>
       <c r="R74" t="n">
-        <v>7027486</v>
+        <v>7027357</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10522,7 +10528,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122698275</v>
+        <v>122697862</v>
       </c>
       <c r="B75" t="n">
         <v>78766</v>
@@ -10562,10 +10568,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>479734</v>
+        <v>479630</v>
       </c>
       <c r="R75" t="n">
-        <v>7027357</v>
+        <v>7027362</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10598,11 +10604,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10654,7 +10655,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122697862</v>
+        <v>122695752</v>
       </c>
       <c r="B76" t="n">
         <v>78766</v>
@@ -10694,13 +10695,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>479630</v>
+        <v>479748</v>
       </c>
       <c r="R76" t="n">
-        <v>7027362</v>
+        <v>7027283</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -10781,10 +10782,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122695752</v>
+        <v>122696290</v>
       </c>
       <c r="B77" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10797,37 +10798,51 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>479748</v>
+        <v>479695</v>
       </c>
       <c r="R77" t="n">
-        <v>7027283</v>
+        <v>7027185</v>
       </c>
       <c r="S77" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -10859,6 +10874,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Observerad i flerskiktad äldre granskog.</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -10871,26 +10891,6 @@
       <c r="AH77" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -11050,10 +11050,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122697534</v>
+        <v>122695669</v>
       </c>
       <c r="B79" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -11066,21 +11066,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -11090,13 +11090,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>479644</v>
+        <v>479761</v>
       </c>
       <c r="R79" t="n">
-        <v>7027243</v>
+        <v>7027298</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
       </c>
       <c r="AH79" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ79" t="inlineStr">
@@ -11177,7 +11177,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122695669</v>
+        <v>122695492</v>
       </c>
       <c r="B80" t="n">
         <v>79848</v>
@@ -11211,19 +11211,24 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>479761</v>
+        <v>479770</v>
       </c>
       <c r="R80" t="n">
-        <v>7027298</v>
+        <v>7027300</v>
       </c>
       <c r="S80" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -11255,6 +11260,11 @@
           <t>2025-02-21</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Växer på en lite smalare sälg intill lunglav.</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -11271,22 +11281,22 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -11304,10 +11314,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122695492</v>
+        <v>122697534</v>
       </c>
       <c r="B81" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -11320,39 +11330,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Frankbodarna, Frankbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>479770</v>
+        <v>479644</v>
       </c>
       <c r="R81" t="n">
-        <v>7027300</v>
+        <v>7027243</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -11387,11 +11392,6 @@
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Växer på en lite smalare sälg intill lunglav.</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -11403,27 +11403,27 @@
       </c>
       <c r="AH81" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>

--- a/artfynd/A 60372-2024 artfynd.xlsx
+++ b/artfynd/A 60372-2024 artfynd.xlsx
@@ -12630,7 +12630,7 @@
         <v>122696426</v>
       </c>
       <c r="B91" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>

--- a/artfynd/A 60372-2024 artfynd.xlsx
+++ b/artfynd/A 60372-2024 artfynd.xlsx
@@ -12630,7 +12630,7 @@
         <v>122696426</v>
       </c>
       <c r="B91" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
